--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N170"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,27 +530,26 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>primero
-ya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?</t>
+          <t>Vaquita Kefir plus😊</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45902.01054398148</v>
+        <v>45902.03216435185</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>00:15:11</t>
+          <t>00:46:19</t>
         </is>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
@@ -561,7 +560,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545278675375244050', 'createTime': 1756772111, 'createTimeISO': '2025-09-02T00:15:11.000Z', 'text': 'primero\nya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 10, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f60ce9d4&amp;x-expires=1761483600&amp;x-signature=0JDXyALIaJRHS3r4xtJehL7HhNo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545286715469792007', 'createTime': 1756773979, 'createTimeISO': '2025-09-02T00:46:19.000Z', 'text': 'Vaquita Kefir plus😊', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd083daf&amp;x-expires=1761570000&amp;x-signature=Mj60V9kePw%2BGmIXKCvNAf2iQtmM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -617,7 +616,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545316874159293192', 'createTime': 1756780990, 'createTimeISO': '2025-09-02T02:43:10.000Z', 'text': 'Mas videos asiiiii🔥🔥🔥🔥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '178030697805189120', 'uniqueId': 'nico5box', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5a97c5c648a6246f815739afc2a4dd5b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=de9f79b2&amp;x-expires=1761483600&amp;x-signature=zdj5LhC6g8Uq96b5j5ScWQ%2FqseM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545316874159293192', 'createTime': 1756780990, 'createTimeISO': '2025-09-02T02:43:10.000Z', 'text': 'Mas videos asiiiii🔥🔥🔥🔥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '178030697805189120', 'uniqueId': 'nico5box', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5a97c5c648a6246f815739afc2a4dd5b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=075190a7&amp;x-expires=1761570000&amp;x-signature=t8%2BcsXWO%2FZ%2F53LxND0s9yn0O%2B%2Bo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -643,25 +642,26 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaquita Kefir plus😊</t>
+          <t>primero
+ya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45902.03216435185</v>
+        <v>45902.01054398148</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>00:46:19</t>
+          <t>00:15:11</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545286715469792007', 'createTime': 1756773979, 'createTimeISO': '2025-09-02T00:46:19.000Z', 'text': 'Vaquita Kefir plus😊', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4d60aecf&amp;x-expires=1761483600&amp;x-signature=JlQRda01a1IFfhz6peVy%2BwrkX8M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545278675375244050', 'createTime': 1756772111, 'createTimeISO': '2025-09-02T00:15:11.000Z', 'text': 'primero\nya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 10, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c0ba37db&amp;x-expires=1761570000&amp;x-signature=gnODwCkuU4b3Ipg9bhtCBiAGgQI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7550080571285816082', 'createTime': 1757890141, 'createTimeISO': '2025-09-14T22:49:01.000Z', 'text': '😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7469966561530430471', 'uniqueId': 'juangmgm84i', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=54cd3839&amp;x-expires=1761483600&amp;x-signature=t2SXE0TP66XfawbO%2FnTkiB47Miw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7550080571285816082', 'createTime': 1757890141, 'createTimeISO': '2025-09-14T22:49:01.000Z', 'text': '😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7469966561530430471', 'uniqueId': 'juangmgm84i', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7555339654096388871', 'createTime': 1759114604, 'createTimeISO': '2025-09-29T02:56:44.000Z', 'text': 'YO SOY FAN NUMERO UNO DEL KEFIR PLUS DE ALPINA. REALMENTE ES EFECTIVO Y MUY BUENO PARA EL ORGANISMO. Quería escribirles y decirles que el producto es un Hit absoluto. Yo consumo desde hace dos semanas el kefir, y en mi familia ya quedó instalado también 🥰🥰🥰. Y la versión pequeña personal es una maravilla para consumidoras como yo🥰🥰🥰. Bravooooooooooo ALPINA\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6892758040694359046', 'uniqueId': 'yeriname7', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6c41967350ee22b8d1bcb851e47d28c2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ea98e5f8&amp;x-expires=1761483600&amp;x-signature=Bo7aR4EpKT05oTXUymc6p8VBIq4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7555339654096388871', 'createTime': 1759114604, 'createTimeISO': '2025-09-29T02:56:44.000Z', 'text': 'YO SOY FAN NUMERO UNO DEL KEFIR PLUS DE ALPINA. REALMENTE ES EFECTIVO Y MUY BUENO PARA EL ORGANISMO. Quería escribirles y decirles que el producto es un Hit absoluto. Yo consumo desde hace dos semanas el kefir, y en mi familia ya quedó instalado también 🥰🥰🥰. Y la versión pequeña personal es una maravilla para consumidoras como yo🥰🥰🥰. Bravooooooooooo ALPINA\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6892758040694359046', 'uniqueId': 'yeriname7', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6c41967350ee22b8d1bcb851e47d28c2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=481614f8&amp;x-expires=1761570000&amp;x-signature=aICpTkyW%2FMbRbysAZwPIWDQf58E%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547697455086404360', 'createTime': 1757335263, 'createTimeISO': '2025-09-08T12:41:03.000Z', 'text': 'QUEE?? 😭\nYO YA ESTABA EMOCIONADO SI AVISABAN NUEVOS MOCHIS O SUS VIDEOS QUE ME ENTRETIENEN😭😭😭', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f60ce9d4&amp;x-expires=1761483600&amp;x-signature=0JDXyALIaJRHS3r4xtJehL7HhNo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547697455086404360', 'createTime': 1757335263, 'createTimeISO': '2025-09-08T12:41:03.000Z', 'text': 'QUEE?? 😭\nYO YA ESTABA EMOCIONADO SI AVISABAN NUEVOS MOCHIS O SUS VIDEOS QUE ME ENTRETIENEN😭😭😭', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7556668683994727189', 'createTime': 1759424043, 'createTimeISO': '2025-10-02T16:54:03.000Z', 'text': 'NOOO ALPINA XQQQ😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183010536447411205', 'uniqueId': 'isa._.325', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0b16bfa6acc7f2d7dbac5f5945453e19~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bc8d4ecb&amp;x-expires=1761483600&amp;x-signature=oug3qMXqzsC8eKnle4lMUMgAwow%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7556668683994727189', 'createTime': 1759424043, 'createTimeISO': '2025-10-02T16:54:03.000Z', 'text': 'NOOO ALPINA XQQQ😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183010536447411205', 'uniqueId': 'isa._.325', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0b16bfa6acc7f2d7dbac5f5945453e19~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9d6563d5&amp;x-expires=1761570000&amp;x-signature=WAb%2Fnl0sccJbp2EGcQjBqPapAFI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -924,18 +924,18 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Queee ?</t>
+          <t>Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>45905.84496527778</v>
+        <v>45920.12734953704</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>45905</v>
+        <v>45920</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20:16:45</t>
+          <t>03:03:23</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546701614498087688', 'createTime': 1757103405, 'createTimeISO': '2025-09-05T20:16:45.000Z', 'text': 'Queee ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=dde1ef35&amp;x-expires=1761483600&amp;x-signature=OiEWqH9CLSCXIrUF956O1yzchVc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7552001614913356551', 'createTime': 1758337403, 'createTimeISO': '2025-09-20T03:03:23.000Z', 'text': 'Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -980,18 +980,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖</t>
+          <t>Qué? 😭</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45920.12734953704</v>
+        <v>45905.7774074074</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>45920</v>
+        <v>45905</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>03:03:23</t>
+          <t>18:39:28</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7552001614913356551', 'createTime': 1758337403, 'createTimeISO': '2025-09-20T03:03:23.000Z', 'text': 'Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0efc43a6&amp;x-expires=1761483600&amp;x-signature=%2FlzlYaBNjstaHyyaUdQHSXP8y2U%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546676538382746376', 'createTime': 1757097568, 'createTimeISO': '2025-09-05T18:39:28.000Z', 'text': 'Qué? 😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=81414567&amp;x-expires=1761570000&amp;x-signature=dyvbRhF3TGiyo9zL0%2Fd3%2FE%2FecEc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1036,22 +1036,22 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>porqueeee??😭😭😭😭</t>
+          <t>por Dios ahora que pasó. y yo etiquetando Alpina 😂</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45907.57980324074</v>
+        <v>45908.64736111111</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13:54:55</t>
+          <t>15:32:12</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547344669736600338', 'createTime': 1757253295, 'createTimeISO': '2025-09-07T13:54:55.000Z', 'text': 'porqueeee??😭😭😭😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c64de15&amp;x-expires=1761483600&amp;x-signature=yAL7nTMnjZalubnp0HX5xUf%2BhU8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547741547535500049', 'createTime': 1757345532, 'createTimeISO': '2025-09-08T15:32:12.000Z', 'text': 'por Dios ahora que pasó. y yo etiquetando Alpina 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830280708298343430', 'uniqueId': 'andreifyt2025_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ca95b033b49845a0bbb72152f6a7fb22~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3fbdc049&amp;x-expires=1761570000&amp;x-signature=IvN6tuqtWk1WXMvFzUg6OrTc1rM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1092,18 +1092,18 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>por Dios ahora que pasó. y yo etiquetando Alpina 😂</t>
+          <t>Queee ?</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45908.64736111111</v>
+        <v>45905.84496527778</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>45908</v>
+        <v>45905</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15:32:12</t>
+          <t>20:16:45</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547741547535500049', 'createTime': 1757345532, 'createTimeISO': '2025-09-08T15:32:12.000Z', 'text': 'por Dios ahora que pasó. y yo etiquetando Alpina 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830280708298343430', 'uniqueId': 'andreifyt2025_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ca95b033b49845a0bbb72152f6a7fb22~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=77879f84&amp;x-expires=1761483600&amp;x-signature=I1nwO75OriQ1ZBM8m1Kb%2BRqXXho%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546701614498087688', 'createTime': 1757103405, 'createTimeISO': '2025-09-05T20:16:45.000Z', 'text': 'Queee ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d4506b40&amp;x-expires=1761570000&amp;x-signature=uRKVTAtDPvXpUDge3YpkAprFqB8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1148,22 +1148,22 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qué? 😭</t>
+          <t>porqueeee??😭😭😭😭</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>45905.7774074074</v>
+        <v>45907.57980324074</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>45905</v>
+        <v>45907</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18:39:28</t>
+          <t>13:54:55</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546676538382746376', 'createTime': 1757097568, 'createTimeISO': '2025-09-05T18:39:28.000Z', 'text': 'Qué? 😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=50385b9b&amp;x-expires=1761483600&amp;x-signature=3f1U46Lv2URleuxYjNTrAqfoeM8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547344669736600338', 'createTime': 1757253295, 'createTimeISO': '2025-09-07T13:54:55.000Z', 'text': 'porqueeee??😭😭😭😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd681055&amp;x-expires=1761570000&amp;x-signature=wNrNCutAEF%2FapCKk%2F9SDDIPR9A4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547942977034617601', 'createTime': 1757392441, 'createTimeISO': '2025-09-09T04:34:01.000Z', 'text': 'volví, haber cuantos meses me fui, que??!!!, 4 meses 😱', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1520e198&amp;x-expires=1761483600&amp;x-signature=RG02BJPXU1NVHYy8yhGN%2FMY2fJo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547942977034617601', 'createTime': 1757392441, 'createTimeISO': '2025-09-09T04:34:01.000Z', 'text': 'volví, haber cuantos meses me fui, que??!!!, 4 meses 😱', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546705871947072276', 'createTime': 1757104397, 'createTimeISO': '2025-09-05T20:33:17.000Z', 'text': 'Wa hapen', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786334206413177862', 'uniqueId': 'oscardavidaldana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/bc48481fc572183ea9e26aa81964cf2b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b0fd413f&amp;x-expires=1761483600&amp;x-signature=8LRa0Zw95Fpjzsk0RfvEBv6ZPq0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546705871947072276', 'createTime': 1757104397, 'createTimeISO': '2025-09-05T20:33:17.000Z', 'text': 'Wa hapen', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786334206413177862', 'uniqueId': 'oscardavidaldana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/bc48481fc572183ea9e26aa81964cf2b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1527c2ec&amp;x-expires=1761570000&amp;x-signature=gAvWE%2Fb3xcB9cc4zZNaHfvYme4w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546693261533659922', 'createTime': 1757101461, 'createTimeISO': '2025-09-05T19:44:21.000Z', 'text': '👀', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=050fbe84&amp;x-expires=1761483600&amp;x-signature=3UjumxBZ1s1oXtIW%2FrCUnzgNe%2FI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546693261533659922', 'createTime': 1757101461, 'createTimeISO': '2025-09-05T19:44:21.000Z', 'text': '👀', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9244ecc1&amp;x-expires=1761570000&amp;x-signature=NSDDd81hys0wPh8yt0LKPO%2BRR4M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1372,18 +1372,18 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>😂</t>
+          <t>😭😰</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>45913.57261574074</v>
+        <v>45906.49487268519</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>45913</v>
+        <v>45906</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13:44:34</t>
+          <t>11:52:37</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7549569237565211409', 'createTime': 1757771074, 'createTimeISO': '2025-09-13T13:44:34.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7186369712568189957', 'uniqueId': 'luzadrianacanooro', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ba9035ed44089efdd68ad1a325c0409b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=03b40b4b&amp;x-expires=1761483600&amp;x-signature=cHw3DFFMlGGZLOwQfO3l26Mr4OE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546942799272411922', 'createTime': 1757159557, 'createTimeISO': '2025-09-06T11:52:37.000Z', 'text': '😭😰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b9aca162&amp;x-expires=1761570000&amp;x-signature=BQoWCp7S4NBWqkUmIlQfbTGSjSg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1428,18 +1428,18 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>😭😰</t>
+          <t>😂</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>45906.49487268519</v>
+        <v>45913.57261574074</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>45906</v>
+        <v>45913</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11:52:37</t>
+          <t>13:44:34</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546942799272411922', 'createTime': 1757159557, 'createTimeISO': '2025-09-06T11:52:37.000Z', 'text': '😭😰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2f29afec&amp;x-expires=1761483600&amp;x-signature=np27DzwhmUWmAlLnUGkaGK1U2uY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7549569237565211409', 'createTime': 1757771074, 'createTimeISO': '2025-09-13T13:44:34.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7186369712568189957', 'uniqueId': 'luzadrianacanooro', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ba9035ed44089efdd68ad1a325c0409b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0229817e&amp;x-expires=1761570000&amp;x-signature=MSPftVTnJhYKaKfQpXMW%2FHiaMYI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1484,18 +1484,18 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ay y por que alpinita</t>
+          <t>Por qué están en problemas con el ministerio de trabajo @Ministerio de Trabajo -Bolivia por qué sus distribuidores en el país tienen a sus empleados con explotación laboral sobre carga laboral horarios que exceden las 15 horas y no les pagan extras ni recargos donde un empleado hace lo de 3 empleados</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>45905.78563657407</v>
+        <v>45935.23751157407</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>45905</v>
+        <v>45935</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18:51:19</t>
+          <t>05:42:01</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546679584475349768', 'createTime': 1757098279, 'createTimeISO': '2025-09-05T18:51:19.000Z', 'text': 'ay y por que alpinita', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7389831937894843398', 'uniqueId': 'un_emo_amigable', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37bc4cd15dd442f352783fdcce05dfb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9fda9179&amp;x-expires=1761483600&amp;x-signature=1JBHYrd09kBgDOS47%2BRrIzE3%2FXg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7557608767006114567', 'createTime': 1759642921, 'createTimeISO': '2025-10-05T05:42:01.000Z', 'text': 'Por qué están en problemas con el ministerio de trabajo @Ministerio de Trabajo -Bolivia por qué sus distribuidores en el país tienen a sus empleados con explotación laboral sobre carga laboral horarios que exceden las 15 horas y no les pagan extras ni recargos donde un empleado hace lo de 3 empleados', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6954818842602931205', 'uniqueId': 'fabiobedoya1504', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0533c8b2372d1c920dad7ae339c48a3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d0d5f4db&amp;x-expires=1761570000&amp;x-signature=pjSPTHUYXplQ7kWrMUvAgg%2FUpF4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Ministerio de Trabajo -Bolivia'], 'detailedMentions': [{'userId': '6817567040930497541', 'nickName': 'Ministerio de Trabajo -Bolivia', 'profileUrl': 'https://www.tiktok.com/@6817567040930497541', 'secUid': 'MS4wLjABAAAAVga5B9Md-oI5XuH5Ruk5ES1IympOnnPUKuurL6hWMHXQ6hzxZPUYisB2cnA5aPyh'}]}</t>
         </is>
       </c>
     </row>
@@ -1540,18 +1540,18 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Por qué están en problemas con el ministerio de trabajo @Ministerio de Trabajo -Bolivia por qué sus distribuidores en el país tienen a sus empleados con explotación laboral sobre carga laboral horarios que exceden las 15 horas y no les pagan extras ni recargos donde un empleado hace lo de 3 empleados</t>
+          <t>ay y por que alpinita</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>45935.23751157407</v>
+        <v>45905.78563657407</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>45935</v>
+        <v>45905</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>05:42:01</t>
+          <t>18:51:19</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7557608767006114567', 'createTime': 1759642921, 'createTimeISO': '2025-10-05T05:42:01.000Z', 'text': 'Por qué están en problemas con el ministerio de trabajo @Ministerio de Trabajo -Bolivia por qué sus distribuidores en el país tienen a sus empleados con explotación laboral sobre carga laboral horarios que exceden las 15 horas y no les pagan extras ni recargos donde un empleado hace lo de 3 empleados', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6954818842602931205', 'uniqueId': 'fabiobedoya1504', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0533c8b2372d1c920dad7ae339c48a3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2ec7c1c8&amp;x-expires=1761483600&amp;x-signature=i4NUGAfrGA5n7dq%2FCcbc50CiXdA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Ministerio de Trabajo -Bolivia'], 'detailedMentions': [{'userId': '6817567040930497541', 'nickName': 'Ministerio de Trabajo -Bolivia', 'profileUrl': 'https://www.tiktok.com/@6817567040930497541', 'secUid': 'MS4wLjABAAAAVga5B9Md-oI5XuH5Ruk5ES1IympOnnPUKuurL6hWMHXQ6hzxZPUYisB2cnA5aPyh'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546679584475349768', 'createTime': 1757098279, 'createTimeISO': '2025-09-05T18:51:19.000Z', 'text': 'ay y por que alpinita', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7389831937894843398', 'uniqueId': 'un_emo_amigable', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37bc4cd15dd442f352783fdcce05dfb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=55ce5c2e&amp;x-expires=1761570000&amp;x-signature=G1RnXtmDwxKSh3%2BohFQle4lMw28%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1596,25 +1596,25 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>siiii ayudemosle!!!</t>
+          <t>para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>45912.8164699074</v>
+        <v>45942.55431712963</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>45912</v>
+        <v>45942</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19:35:43</t>
+          <t>13:18:13</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549288639830721301', 'createTime': 1757705743, 'createTimeISO': '2025-09-12T19:35:43.000Z', 'text': 'siiii ayudemosle!!!', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3158b83e&amp;x-expires=1761483600&amp;x-signature=b1rjYf14FAtSQp9BfgTNFYSUnAk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7560323939830924039', 'createTime': 1760275093, 'createTimeISO': '2025-10-12T13:18:13.000Z', 'text': 'para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7278338689078658054', 'uniqueId': 'chelo_velez', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/66a0861aa54c87fafc40a21878c5a064~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2d079850&amp;x-expires=1761570000&amp;x-signature=TLlfLihhl3A41kC0EzIGD6Z9DTc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1652,25 +1652,25 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>holitaaaa</t>
+          <t>Ay tan bonitaaaaa mañana nos vemos 🥺</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>45912.04994212963</v>
+        <v>45912.17210648148</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>01:11:55</t>
+          <t>04:07:50</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549004192569525000', 'createTime': 1757639515, 'createTimeISO': '2025-09-12T01:11:55.000Z', 'text': 'holitaaaa', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6982722979595863046', 'uniqueId': 'mrbrawl69', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/38c613c8f3cea66a0a3bfeab34f76e58~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=44e94db5&amp;x-expires=1761483600&amp;x-signature=P6hpZrsiRPw7pB2LRCcjGoBwQn0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549049533700277012', 'createTime': 1757650070, 'createTimeISO': '2025-09-12T04:07:50.000Z', 'text': 'Ay tan bonitaaaaa mañana nos vemos 🥺', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7355258637583844357', 'uniqueId': 'majitouuuuuu0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/dbc73978fd3f05b374910bef0e207b56~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d4f4370a&amp;x-expires=1761570000&amp;x-signature=ZFULCeeUtvywpY8p0JXFHKdLZwg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1708,22 +1708,22 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>jojojo</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>45912.03950231482</v>
+        <v>45935.64364583333</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>45912</v>
+        <v>45935</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>00:56:53</t>
+          <t>15:26:51</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000273060233991', 'createTime': 1757638613, 'createTimeISO': '2025-09-12T00:56:53.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9172a8a8&amp;x-expires=1761483600&amp;x-signature=DEY%2F%2FqVuciP0lvggwKT4xDxwhwE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557758733863387920', 'createTime': 1759678011, 'createTimeISO': '2025-10-05T15:26:51.000Z', 'text': 'jojojo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554795739316306964', 'uniqueId': 'freydermurcia33', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/699d7f94c2d9a0694952663b219cc25f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=347ebf06&amp;x-expires=1761570000&amp;x-signature=ZWtJaxzCTlQSEHkSHN80aU5lotY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1764,25 +1764,25 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>🥰🥰🥰</t>
+          <t>A AYUDAR A ALPINA🩷🩷🩷</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>45912.05922453704</v>
+        <v>45913.64655092593</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>45912</v>
+        <v>45913</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>01:25:17</t>
+          <t>15:31:02</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549007617818559250', 'createTime': 1757640317, 'createTimeISO': '2025-09-12T01:25:17.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6710319884842337285', 'uniqueId': 'itssantiagocelis', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/c17d4d00500c39eed015d9ab552b352a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2241efa4&amp;x-expires=1761483600&amp;x-signature=4d9aKIilpAnVuLYTDxILTpd1ooE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549596693055554311', 'createTime': 1757777462, 'createTimeISO': '2025-09-13T15:31:02.000Z', 'text': 'A AYUDAR A ALPINA\U0001fa77\U0001fa77\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1820,22 +1820,22 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>que vuelvan los gatos porfiiii</t>
+          <t>Siiiii! Ya quiero ver la nueva practicante🎉🎉🎉</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>45940.73591435186</v>
+        <v>45912.6234375</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>45940</v>
+        <v>45912</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17:39:43</t>
+          <t>14:57:45</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7559649133477823253', 'createTime': 1760117983, 'createTimeISO': '2025-10-10T17:39:43.000Z', 'text': 'que vuelvan los gatos porfiiii', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7541238264298357778', 'uniqueId': 'invencible799', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/41228f33689b86eba8bd2b23e2173644~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8d292dc7&amp;x-expires=1761483600&amp;x-signature=904PznRp64Vu7PZhF1%2Fc3BNGrn8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549217011010044692', 'createTime': 1757689065, 'createTimeISO': '2025-09-12T14:57:45.000Z', 'text': 'Siiiii! Ya quiero ver la nueva practicante🎉🎉🎉', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b3df464&amp;x-expires=1761570000&amp;x-signature=%2B5Kjk%2FNsFieX1m07yrNaeC%2FJ6u8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1876,25 +1876,25 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo</t>
+          <t>siiii ayudemosle!!!</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>45942.55431712963</v>
+        <v>45912.8164699074</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>45942</v>
+        <v>45912</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13:18:13</t>
+          <t>19:35:43</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7560323939830924039', 'createTime': 1760275093, 'createTimeISO': '2025-10-12T13:18:13.000Z', 'text': 'para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7278338689078658054', 'uniqueId': 'chelo_velez', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/66a0861aa54c87fafc40a21878c5a064~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e87103a&amp;x-expires=1761483600&amp;x-signature=k5FIwJgSgGv6%2BgYVENF%2B7IioMhg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549288639830721301', 'createTime': 1757705743, 'createTimeISO': '2025-09-12T19:35:43.000Z', 'text': 'siiii ayudemosle!!!', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=109ea6b2&amp;x-expires=1761570000&amp;x-signature=rf95%2BkUaV%2Fv4O%2FPzSATd4vhGdvA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1932,25 +1932,25 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ay tan bonitaaaaa mañana nos vemos 🥺</t>
+          <t>holitaaaa</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>45912.17210648148</v>
+        <v>45912.04994212963</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>04:07:50</t>
+          <t>01:11:55</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549049533700277012', 'createTime': 1757650070, 'createTimeISO': '2025-09-12T04:07:50.000Z', 'text': 'Ay tan bonitaaaaa mañana nos vemos 🥺', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7355258637583844357', 'uniqueId': 'majitouuuuuu0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/dbc73978fd3f05b374910bef0e207b56~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=69ea3a6e&amp;x-expires=1761483600&amp;x-signature=dYX1l5o9gMrtaJvluNH47qUlDzo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549004192569525000', 'createTime': 1757639515, 'createTimeISO': '2025-09-12T01:11:55.000Z', 'text': 'holitaaaa', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6982722979595863046', 'uniqueId': 'mrbrawl69', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/38c613c8f3cea66a0a3bfeab34f76e58~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1a418b44&amp;x-expires=1761570000&amp;x-signature=WLFo72yWWLoKEetm3mEV7eOGtng%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1988,22 +1988,22 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Siiiii! Ya quiero ver la nueva practicante🎉🎉🎉</t>
+          <t>Un concurso de cocina ?</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45912.6234375</v>
+        <v>45912.07991898148</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14:57:45</t>
+          <t>01:55:05</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549217011010044692', 'createTime': 1757689065, 'createTimeISO': '2025-09-12T14:57:45.000Z', 'text': 'Siiiii! Ya quiero ver la nueva practicante🎉🎉🎉', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5da0e43a&amp;x-expires=1761483600&amp;x-signature=vh9rXohTnDZVGLsv3zABlKDCCKk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549015309047710471', 'createTime': 1757642105, 'createTimeISO': '2025-09-12T01:55:05.000Z', 'text': 'Un concurso de cocina ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6790480840596358149', 'uniqueId': 'vivianaospina67', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/34082dcda72461c00ba3d59eb0cda82a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=74b57f0b&amp;x-expires=1761570000&amp;x-signature=zcwwCQymWoyS1rBKkE6Q5sGSl3o%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2044,25 +2044,25 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A AYUDAR A ALPINA🩷🩷🩷</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>45913.64655092593</v>
+        <v>45912.03950231482</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>45913</v>
+        <v>45912</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15:31:02</t>
+          <t>00:56:53</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549596693055554311', 'createTime': 1757777462, 'createTimeISO': '2025-09-13T15:31:02.000Z', 'text': 'A AYUDAR A ALPINA\U0001fa77\U0001fa77\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f60ce9d4&amp;x-expires=1761483600&amp;x-signature=0JDXyALIaJRHS3r4xtJehL7HhNo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000273060233991', 'createTime': 1757638613, 'createTimeISO': '2025-09-12T00:56:53.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e0aba58&amp;x-expires=1761570000&amp;x-signature=OWekD83TiJfQ2m%2B3WwuiT6Ts%2BXI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2100,18 +2100,18 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>jojojo</t>
+          <t>🥰🥰🥰</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>45935.64364583333</v>
+        <v>45912.05922453704</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>45935</v>
+        <v>45912</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15:26:51</t>
+          <t>01:25:17</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557758733863387920', 'createTime': 1759678011, 'createTimeISO': '2025-10-05T15:26:51.000Z', 'text': 'jojojo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554795739316306964', 'uniqueId': 'freydermurcia33', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/699d7f94c2d9a0694952663b219cc25f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fdd81a7b&amp;x-expires=1761483600&amp;x-signature=0zqAsIfIyhu1pqHJrBOP7U%2FQT40%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549007617818559250', 'createTime': 1757640317, 'createTimeISO': '2025-09-12T01:25:17.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6710319884842337285', 'uniqueId': 'itssantiagocelis', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/c17d4d00500c39eed015d9ab552b352a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5962eec2&amp;x-expires=1761570000&amp;x-signature=7Ju8FYMl8%2Fdw4UxwBQXbQQM2rpU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2156,18 +2156,18 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Quien esssss ? 👀</t>
+          <t>😮😮😮</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>45912.81784722222</v>
+        <v>45912.68053240741</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>19:37:42</t>
+          <t>16:19:58</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549289149077979912', 'createTime': 1757705862, 'createTimeISO': '2025-09-12T19:37:42.000Z', 'text': 'Quien esssss ? 👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7255348886041691141', 'uniqueId': 'jholainec21', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/205ba05ede21686eb806965cb40fd502~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bf712bcd&amp;x-expires=1761483600&amp;x-signature=bcTTXQGtoqZNxeDWkbsq82IU3lA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549238211336487681', 'createTime': 1757693998, 'createTimeISO': '2025-09-12T16:19:58.000Z', 'text': '😮😮😮', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6778152010580509702', 'uniqueId': 'esteban_ocampov', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6a63d386d387123e4d61df4e994bb26d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9aea2ee0&amp;x-expires=1761570000&amp;x-signature=lmAxojUE0vMntGdDG%2F3WvYJar1E%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2212,18 +2212,18 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Un concurso de cocina ?</t>
+          <t>🥰😳😁</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45912.07991898148</v>
+        <v>45912.87542824074</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01:55:05</t>
+          <t>21:00:37</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549015309047710471', 'createTime': 1757642105, 'createTimeISO': '2025-09-12T01:55:05.000Z', 'text': 'Un concurso de cocina ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6790480840596358149', 'uniqueId': 'vivianaospina67', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/34082dcda72461c00ba3d59eb0cda82a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=34869815&amp;x-expires=1761483600&amp;x-signature=EqmYvOj95v%2F3V7YZwiW5EG4JZ4M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549310477420708629', 'createTime': 1757710837, 'createTimeISO': '2025-09-12T21:00:37.000Z', 'text': '🥰😳😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7509769410816705544', 'uniqueId': 'user749076194246', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2268,18 +2268,18 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>😮😮😮</t>
+          <t>🗿🗿🗿</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>45912.68053240741</v>
+        <v>45912.03923611111</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16:19:58</t>
+          <t>00:56:30</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549238211336487681', 'createTime': 1757693998, 'createTimeISO': '2025-09-12T16:19:58.000Z', 'text': '😮😮😮', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6778152010580509702', 'uniqueId': 'esteban_ocampov', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6a63d386d387123e4d61df4e994bb26d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a1af8127&amp;x-expires=1761483600&amp;x-signature=DBCnFJ4PLuID4sgho0HEDpMSxa0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000221259399954', 'createTime': 1757638590, 'createTimeISO': '2025-09-12T00:56:30.000Z', 'text': '🗿🗿🗿', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319745287890387973', 'uniqueId': 'matias_8595', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37f085e6cd1478b738e427953d05ecb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b1455c2b&amp;x-expires=1761570000&amp;x-signature=0QmrdHIjL0AlbTctpekJS6qwrmY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2324,18 +2324,18 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>🥰😳😁</t>
+          <t>rgcuhif</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>45912.87542824074</v>
+        <v>45936.01050925926</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>45912</v>
+        <v>45936</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21:00:37</t>
+          <t>00:15:08</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549310477420708629', 'createTime': 1757710837, 'createTimeISO': '2025-09-12T21:00:37.000Z', 'text': '🥰😳😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7509769410816705544', 'uniqueId': 'user749076194246', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=54cd3839&amp;x-expires=1761483600&amp;x-signature=t2SXE0TP66XfawbO%2FnTkiB47Miw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557895538470322945', 'createTime': 1759709708, 'createTimeISO': '2025-10-06T00:15:08.000Z', 'text': 'rgcuhif', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6975369451886593029', 'uniqueId': 'noraortegom', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>🗿🗿🗿</t>
+          <t>que vuelvan los gatos porfiiii</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>45912.03923611111</v>
+        <v>45940.73591435186</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>45912</v>
+        <v>45940</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>00:56:30</t>
+          <t>17:39:43</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000221259399954', 'createTime': 1757638590, 'createTimeISO': '2025-09-12T00:56:30.000Z', 'text': '🗿🗿🗿', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319745287890387973', 'uniqueId': 'matias_8595', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37f085e6cd1478b738e427953d05ecb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bcc66813&amp;x-expires=1761483600&amp;x-signature=fO4uG0iSXN6LqUptZcdt6ERYibM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7559649133477823253', 'createTime': 1760117983, 'createTimeISO': '2025-10-10T17:39:43.000Z', 'text': 'que vuelvan los gatos porfiiii', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7541238264298357778', 'uniqueId': 'invencible799', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/41228f33689b86eba8bd2b23e2173644~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a725470&amp;x-expires=1761570000&amp;x-signature=TmzbHPjb70icT0jmSa2RBd0EwUY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2436,25 +2436,25 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>rgcuhif</t>
+          <t>alpina yo quiero saber si¿la nueva colección de yogo premio se llama mochi saurios????@Alpina 🐮</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>45936.01050925926</v>
+        <v>45912.55510416667</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>45936</v>
+        <v>45912</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>00:15:08</t>
+          <t>13:19:21</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557895538470322945', 'createTime': 1759709708, 'createTimeISO': '2025-10-06T00:15:08.000Z', 'text': 'rgcuhif', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6975369451886593029', 'uniqueId': 'noraortegom', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=54cd3839&amp;x-expires=1761483600&amp;x-signature=t2SXE0TP66XfawbO%2FnTkiB47Miw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549191179351474951', 'createTime': 1757683161, 'createTimeISO': '2025-09-12T13:19:21.000Z', 'text': 'alpina yo quiero saber si¿la nueva colección de yogo premio se llama mochi saurios????@Alpina 🐮', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5e566503&amp;x-expires=1761570000&amp;x-signature=crBApd%2Fd%2FyYfuKhDihwij3EbqYg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -2492,25 +2492,25 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>alpina yo quiero saber si¿la nueva colección de yogo premio se llama mochi saurios????@Alpina 🐮</t>
+          <t>Quien esssss ? 👀</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>45912.55510416667</v>
+        <v>45912.81784722222</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13:19:21</t>
+          <t>19:37:42</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549191179351474951', 'createTime': 1757683161, 'createTimeISO': '2025-09-12T13:19:21.000Z', 'text': 'alpina yo quiero saber si¿la nueva colección de yogo premio se llama mochi saurios????@Alpina 🐮', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e8d8e5ee&amp;x-expires=1761483600&amp;x-signature=9OzrxgEqDqeH6J7e4%2B7%2FjPnIW4I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549289149077979912', 'createTime': 1757705862, 'createTimeISO': '2025-09-12T19:37:42.000Z', 'text': 'Quien esssss ? 👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7255348886041691141', 'uniqueId': 'jholainec21', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/205ba05ede21686eb806965cb40fd502~tplv-tiktokx-cropcenter:100:100.jpg?dr=10399&amp;refresh_token=e9b6b21a&amp;x-expires=1761570000&amp;x-signature=OCr5DmD5DyvV91bBM8%2BPVIhcTq4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=no1a', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2548,22 +2548,22 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗</t>
+          <t>Te amo me encanta Alpina 🥰</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>45917.02540509259</v>
+        <v>45917.01868055556</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>00:36:35</t>
+          <t>00:26:54</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550850431720325905', 'createTime': 1758069395, 'createTimeISO': '2025-09-17T00:36:35.000Z', 'text': 'QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '282408726983028736', 'uniqueId': 'wanna_juana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/17e1ad71c0265acba1716a4696601785~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=28c03aea&amp;x-expires=1761483600&amp;x-signature=bN87eaKj6zdW9jG3abbUvo%2BfA7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550847978996859666', 'createTime': 1758068814, 'createTimeISO': '2025-09-17T00:26:54.000Z', 'text': 'Te amo me encanta Alpina 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6aa5f872&amp;x-expires=1761570000&amp;x-signature=ll%2FiiMVSWZhZEwWV%2BWhvVB5FP18%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2604,25 +2604,25 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭</t>
+          <t>cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>45916.99344907407</v>
+        <v>45922.03340277778</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>45916</v>
+        <v>45922</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>23:50:34</t>
+          <t>00:48:06</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550838637400179464', 'createTime': 1758066634, 'createTimeISO': '2025-09-16T23:50:34.000Z', 'text': 'no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6952624737991443462', 'uniqueId': 'valeria_noo2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1a1431eb5fd2ec2b3db383b2b0e26ac9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d689793b&amp;x-expires=1761483600&amp;x-signature=rpZgcsUgR6sqQSmQbBJQLroxLbk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552707780533863189', 'createTime': 1758502086, 'createTimeISO': '2025-09-22T00:48:06.000Z', 'text': 'cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=196af7c3&amp;x-expires=1761570000&amp;x-signature=mfmJCzSJseg0BUINUmeciufLGgM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2660,22 +2660,22 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amò este Alpina</t>
+          <t>no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>45919.13483796296</v>
+        <v>45916.99344907407</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>45919</v>
+        <v>45916</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>03:14:10</t>
+          <t>23:50:34</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551633311488082696', 'createTime': 1758251650, 'createTimeISO': '2025-09-19T03:14:10.000Z', 'text': 'Amò este Alpina', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6955254769972806662', 'uniqueId': 'santiwhosthat', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9848dac63ccb5eeefc999aaeb526145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0f25d23c&amp;x-expires=1761483600&amp;x-signature=6qoJO66TaS62hpcoMpma097CmZY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550838637400179464', 'createTime': 1758066634, 'createTimeISO': '2025-09-16T23:50:34.000Z', 'text': 'no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6952624737991443462', 'uniqueId': 'valeria_noo2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1a1431eb5fd2ec2b3db383b2b0e26ac9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ab113881&amp;x-expires=1761570000&amp;x-signature=xPForBLlds5o5g4%2Fd9Kh74LuwIM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2716,22 +2716,22 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AMAMOSSSS el contenido de Gabi</t>
+          <t>QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>45917.09577546296</v>
+        <v>45917.02540509259</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>02:17:55</t>
+          <t>00:36:35</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550876642629944071', 'createTime': 1758075475, 'createTimeISO': '2025-09-17T02:17:55.000Z', 'text': 'AMAMOSSSS el contenido de Gabi', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b5b0b9d6&amp;x-expires=1761483600&amp;x-signature=K2niBkst6YFEppgZWaVNSsPScWk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550850431720325905', 'createTime': 1758069395, 'createTimeISO': '2025-09-17T00:36:35.000Z', 'text': 'QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '282408726983028736', 'uniqueId': 'wanna_juana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/17e1ad71c0265acba1716a4696601785~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=88c097fc&amp;x-expires=1761570000&amp;x-signature=MIQ7FC6pR3S7mhDreHpWpiFoOU8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2772,25 +2772,25 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Buen día, aceptan pasantes en área administrativa?😳</t>
+          <t>Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>45924.54788194445</v>
+        <v>45917.05436342592</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13:08:57</t>
+          <t>01:18:17</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553641991944602386', 'createTime': 1758719337, 'createTimeISO': '2025-09-24T13:08:57.000Z', 'text': 'Buen día, aceptan pasantes en área administrativa?😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819016661686453254', 'uniqueId': 'scatalina15', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65616505ecd12a1b5dd469d79ec8a719~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6e8419cc&amp;x-expires=1761483600&amp;x-signature=4R2ZpvxI1RXBxu7KMFrLmKQglbI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550861226680648468', 'createTime': 1758071897, 'createTimeISO': '2025-09-17T01:18:17.000Z', 'text': 'Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f5aece25&amp;x-expires=1761570000&amp;x-signature=Zl4tz07p0ieZ8Pxe8VY0POWecRU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2828,26 +2828,25 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1ro
-alpina te amo!!</t>
+          <t>Amò este Alpina</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>45916.98658564815</v>
+        <v>45919.13483796296</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>45916</v>
+        <v>45919</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>23:40:41</t>
+          <t>03:14:10</t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2859,7 +2858,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550836019215958805', 'createTime': 1758066041, 'createTimeISO': '2025-09-16T23:40:41.000Z', 'text': '1ro\nalpina te amo!!', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452218782174446597', 'uniqueId': 'shidouxsae0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2865ac893335cccef6405d3bf354fedb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=287a81d5&amp;x-expires=1761483600&amp;x-signature=EwKp9%2BGI7AmYZrWTvJh0fQgZDsU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551633311488082696', 'createTime': 1758251650, 'createTimeISO': '2025-09-19T03:14:10.000Z', 'text': 'Amò este Alpina', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6955254769972806662', 'uniqueId': 'santiwhosthat', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9848dac63ccb5eeefc999aaeb526145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=38287148&amp;x-expires=1761570000&amp;x-signature=T36cejv0HS%2FeTrSmbE%2FE6%2FZQyu4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2885,25 +2884,26 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Te amo me encanta Alpina 🥰</t>
+          <t>1ro
+alpina te amo!!</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>45917.01868055556</v>
+        <v>45916.98658564815</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>45917</v>
+        <v>45916</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>00:26:54</t>
+          <t>23:40:41</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550847978996859666', 'createTime': 1758068814, 'createTimeISO': '2025-09-17T00:26:54.000Z', 'text': 'Te amo me encanta Alpina 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0efc43a6&amp;x-expires=1761483600&amp;x-signature=%2FlzlYaBNjstaHyyaUdQHSXP8y2U%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550836019215958805', 'createTime': 1758066041, 'createTimeISO': '2025-09-16T23:40:41.000Z', 'text': '1ro\nalpina te amo!!', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452218782174446597', 'uniqueId': 'shidouxsae0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2865ac893335cccef6405d3bf354fedb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ac44156&amp;x-expires=1761570000&amp;x-signature=leR4FwW%2FIBrxMInIYQmj77K6py8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2941,25 +2941,25 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!</t>
+          <t>pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>45917.58866898148</v>
+        <v>45917.87722222223</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14:07:41</t>
+          <t>21:03:12</t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551059537588929298', 'createTime': 1758118061, 'createTimeISO': '2025-09-17T14:07:41.000Z', 'text': 'Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=50385b9b&amp;x-expires=1761483600&amp;x-signature=3f1U46Lv2URleuxYjNTrAqfoeM8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551166524197077767', 'createTime': 1758142992, 'createTimeISO': '2025-09-17T21:03:12.000Z', 'text': 'pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=26a7ae26&amp;x-expires=1761570000&amp;x-signature=z4Cc6Vhls%2BKFDO7%2FuIUSOXTFj7k%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2997,22 +2997,22 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩</t>
+          <t>si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>45917.05436342592</v>
+        <v>45919.69366898148</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>01:18:17</t>
+          <t>16:38:53</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550861226680648468', 'createTime': 1758071897, 'createTimeISO': '2025-09-17T01:18:17.000Z', 'text': 'Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=12eeeed1&amp;x-expires=1761483600&amp;x-signature=%2FQktCU43siBp5Reu%2B5exdZs22Dw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551840682764829458', 'createTime': 1758299933, 'createTimeISO': '2025-09-19T16:38:53.000Z', 'text': 'si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6885505605576377345', 'uniqueId': 'spaaaak_4.m', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7324800281223364610~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=828a8d27&amp;x-expires=1761570000&amp;x-signature=TXWPVFYwrWbDwSfgjGSmjwn3CVY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3053,22 +3053,22 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mi sueño haciéndose realidad 🥰🥺</t>
+          <t>Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>45918.62016203703</v>
+        <v>45917.58866898148</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14:53:02</t>
+          <t>14:07:41</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551442303657116436', 'createTime': 1758207182, 'createTimeISO': '2025-09-18T14:53:02.000Z', 'text': 'Mi sueño haciéndose realidad 🥰🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6788284872554497030', 'uniqueId': 'anirivera_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c6e77f0d746b65b48a78e1205c8c82~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=342b109f&amp;x-expires=1761483600&amp;x-signature=Un74m5%2F72yXt3NyMOn%2F4W08Wee0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551059537588929298', 'createTime': 1758118061, 'createTimeISO': '2025-09-17T14:07:41.000Z', 'text': 'Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=81414567&amp;x-expires=1761570000&amp;x-signature=dyvbRhF3TGiyo9zL0%2Fd3%2FE%2FecEc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3109,25 +3109,25 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>como se puede conseguir el álbum de mochis</t>
+          <t>AMAMOSSSS el contenido de Gabi</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>45928.17954861111</v>
+        <v>45917.09577546296</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>45928</v>
+        <v>45917</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>04:18:33</t>
+          <t>02:17:55</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554989643563205384', 'createTime': 1759033113, 'createTimeISO': '2025-09-28T04:18:33.000Z', 'text': 'como se puede conseguir el álbum de mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7340762611166299142', 'uniqueId': 'wilson.piraquive5', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/376f70562283aeaeeb98265a1fe54ae8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=39642076&amp;x-expires=1761483600&amp;x-signature=HdSKYvPipgP2SHBcUOt6SYrXClQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550876642629944071', 'createTime': 1758075475, 'createTimeISO': '2025-09-17T02:17:55.000Z', 'text': 'AMAMOSSSS el contenido de Gabi', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bb35b1b1&amp;x-expires=1761570000&amp;x-signature=QjOPv77uCLlckf8dBxpc%2BZwaAdA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3165,25 +3165,25 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)</t>
+          <t>Yo quierooooo✨</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>45922.03340277778</v>
+        <v>45917.00403935185</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>45922</v>
+        <v>45917</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>00:48:06</t>
+          <t>00:05:49</t>
         </is>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552707780533863189', 'createTime': 1758502086, 'createTimeISO': '2025-09-22T00:48:06.000Z', 'text': 'cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=04f10852&amp;x-expires=1761483600&amp;x-signature=gdhh3sdeBOLepBntdkVxrrZGiP0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550842534529860370', 'createTime': 1758067549, 'createTimeISO': '2025-09-17T00:05:49.000Z', 'text': 'Yo quierooooo✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781227104677250053', 'uniqueId': 'lauraleguizamou', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0ac3e8266fc87e3612cd93ce4262beda~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1b54d5d9&amp;x-expires=1761570000&amp;x-signature=ohoskb0UmDbnF6LY7dnFTgKr09c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3221,25 +3221,25 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>estando en etapa lectiva puedo aplicar</t>
+          <t>Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? 🥹</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>45926.77971064814</v>
+        <v>45918.74025462963</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>45926</v>
+        <v>45918</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>18:42:47</t>
+          <t>17:45:58</t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554470184620000018', 'createTime': 1758912167, 'createTimeISO': '2025-09-26T18:42:47.000Z', 'text': 'estando en etapa lectiva puedo aplicar', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d24f6cd8&amp;x-expires=1761483600&amp;x-signature=sASoTG8pBaQDFaH%2B6K2yp1PIU2s%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551486875396948744', 'createTime': 1758217558, 'createTimeISO': '2025-09-18T17:45:58.000Z', 'text': 'Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? \U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6817806087653164037', 'uniqueId': 'brandontarcila_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6b11bf080b10cd0207666b99c05d31b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b39b37b8&amp;x-expires=1761570000&amp;x-signature=aOEiDV7M7bxRKaoH8RSp%2FyuCpMc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3277,18 +3277,18 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>¿Qué tipo de contrato tienen?</t>
+          <t>Buenisimo!!!!!</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>45920.96097222222</v>
+        <v>45919.87149305556</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>45920</v>
+        <v>45919</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>23:03:48</t>
+          <t>20:54:57</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552310929883448084', 'createTime': 1758409428, 'createTimeISO': '2025-09-20T23:03:48.000Z', 'text': '¿Qué tipo de contrato tienen?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856891169080443909', 'uniqueId': 'lourdesbarragan_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e377e28c29d509541307260e66fb275d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7d4366bb&amp;x-expires=1761483600&amp;x-signature=q4G9jnsBK7%2BoWNSjOil5KbQerOo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551906649611830023', 'createTime': 1758315297, 'createTimeISO': '2025-09-19T20:54:57.000Z', 'text': 'Buenisimo!!!!!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7068293195050877957', 'uniqueId': 'mfzamarriego', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5891c8d97d65891a135a4f898bbe9dc6~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b20f8bd2&amp;x-expires=1761570000&amp;x-signature=jT2u9ag7o%2B34ROZjlxknjf6FFHE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3333,18 +3333,18 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Buenisimo!!!!!</t>
+          <t>Buen día, aceptan pasantes en área administrativa?😳</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>45919.87149305556</v>
+        <v>45924.54788194445</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>45919</v>
+        <v>45924</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20:54:57</t>
+          <t>13:08:57</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551906649611830023', 'createTime': 1758315297, 'createTimeISO': '2025-09-19T20:54:57.000Z', 'text': 'Buenisimo!!!!!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7068293195050877957', 'uniqueId': 'mfzamarriego', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5891c8d97d65891a135a4f898bbe9dc6~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2fad436a&amp;x-expires=1761483600&amp;x-signature=SfsY6l%2BGy9QsjE4mSf9SJD42TZM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553641991944602386', 'createTime': 1758719337, 'createTimeISO': '2025-09-24T13:08:57.000Z', 'text': 'Buen día, aceptan pasantes en área administrativa?😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819016661686453254', 'uniqueId': 'scatalina15', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65616505ecd12a1b5dd469d79ec8a719~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=33c13ddb&amp;x-expires=1761570000&amp;x-signature=6n8L8yA8cdrzFEwJqaLjmdUPxNg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3389,25 +3389,25 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema</t>
+          <t>me enteré que ya subieron nuevo video 😍</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>45936.70731481481</v>
+        <v>45917.08885416666</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>45936</v>
+        <v>45917</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>16:58:32</t>
+          <t>02:07:57</t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558154185101247240', 'createTime': 1759769912, 'createTimeISO': '2025-10-06T16:58:32.000Z', 'text': 'Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7005260384655574022', 'uniqueId': 'diegoalejandropat3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327286844337127429~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=37f939ec&amp;x-expires=1761483600&amp;x-signature=zKlUOiGNDt6U12T6ETHuL9NMKJI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550874055755203345', 'createTime': 1758074877, 'createTimeISO': '2025-09-17T02:07:57.000Z', 'text': 'me enteré que ya subieron nuevo video 😍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3445,26 +3445,26 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis</t>
+          <t>Cuando comienzan a dar respuesta si ya apliqué?🥹</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>45917.87722222223</v>
+        <v>45916.99778935185</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>45917</v>
+        <v>45916</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>21:03:12</t>
+          <t>23:56:49</t>
         </is>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="b">
         <v>0</v>
       </c>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551166524197077767', 'createTime': 1758142992, 'createTimeISO': '2025-09-17T21:03:12.000Z', 'text': 'pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6bfac2db&amp;x-expires=1761483600&amp;x-signature=1X08XRVToySKmYLjFbKGNbE08KI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550840242002150162', 'createTime': 1758067009, 'createTimeISO': '2025-09-16T23:56:49.000Z', 'text': 'Cuando comienzan a dar respuesta si ya apliqué?\U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b5403971a2c0063750a9b7140d15458b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7548553e&amp;x-expires=1761570000&amp;x-signature=BlfR6%2B%2FfkD%2BokVL0Mtp6MdOTDUU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3501,25 +3501,25 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? 🥹</t>
+          <t>estando en etapa lectiva puedo aplicar</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>45918.74025462963</v>
+        <v>45926.77971064814</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17:45:58</t>
+          <t>18:42:47</t>
         </is>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551486875396948744', 'createTime': 1758217558, 'createTimeISO': '2025-09-18T17:45:58.000Z', 'text': 'Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? \U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6817806087653164037', 'uniqueId': 'brandontarcila_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6b11bf080b10cd0207666b99c05d31b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c9e97e23&amp;x-expires=1761483600&amp;x-signature=ZXRcWPndw0tTqwXiJSt2339hZic%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554470184620000018', 'createTime': 1758912167, 'createTimeISO': '2025-09-26T18:42:47.000Z', 'text': 'estando en etapa lectiva puedo aplicar', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=30df542e&amp;x-expires=1761570000&amp;x-signature=ePCGB9BrUbZkPVx3h%2BelHiRBM9o%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3557,25 +3557,25 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭</t>
+          <t>como se puede conseguir el álbum de mochis</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>45919.69366898148</v>
+        <v>45928.17954861111</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>45919</v>
+        <v>45928</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16:38:53</t>
+          <t>04:18:33</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551840682764829458', 'createTime': 1758299933, 'createTimeISO': '2025-09-19T16:38:53.000Z', 'text': 'si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6885505605576377345', 'uniqueId': 'spaaaak_4.m', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7324800281223364610~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=38c6eee6&amp;x-expires=1761483600&amp;x-signature=ul8DLo454iG%2BJ1Hbv3wXaJ5vSrk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554989643563205384', 'createTime': 1759033113, 'createTimeISO': '2025-09-28T04:18:33.000Z', 'text': 'como se puede conseguir el álbum de mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7340762611166299142', 'uniqueId': 'wilson.piraquive5', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/376f70562283aeaeeb98265a1fe54ae8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67c5fa42&amp;x-expires=1761570000&amp;x-signature=LwD24MhO3mWnwQhXBJ7z%2FRd%2Biy4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3613,25 +3613,25 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>me enteré que ya subieron nuevo video 😍</t>
+          <t>Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>45917.08885416666</v>
+        <v>45936.70731481481</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>45917</v>
+        <v>45936</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>02:07:57</t>
+          <t>16:58:32</t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550874055755203345', 'createTime': 1758074877, 'createTimeISO': '2025-09-17T02:07:57.000Z', 'text': 'me enteré que ya subieron nuevo video 😍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4d40e4fa&amp;x-expires=1761483600&amp;x-signature=sUzBjSw8%2Bc61kG0ORk9i9C7tLg0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558154185101247240', 'createTime': 1759769912, 'createTimeISO': '2025-10-06T16:58:32.000Z', 'text': 'Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7005260384655574022', 'uniqueId': 'diegoalejandropat3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327286844337127429~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4238950b&amp;x-expires=1761570000&amp;x-signature=o7S3AxC9lgK8KpakZhr%2B5YG%2F8vg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3669,18 +3669,18 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Me salió tarde el vídeo 😟 yo quiero 🥹🙏🏻</t>
+          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>45941.61577546296</v>
+        <v>45950.08646990741</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>45941</v>
+        <v>45950</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>14:46:43</t>
+          <t>02:04:31</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7559975652176577288', 'createTime': 1760194003, 'createTimeISO': '2025-10-11T14:46:43.000Z', 'text': 'Me salió tarde el vídeo 😟 yo quiero \U0001f979🙏🏻', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6670638394765033478', 'uniqueId': 'lindanarino', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/873e52b20a774b09b73f0f0d565e6959~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=680a3458&amp;x-expires=1761483600&amp;x-signature=YdaF%2B6cAoGUbNbzHigBOGF4yAjk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7563119000310334226', 'createTime': 1760925871, 'createTimeISO': '2025-10-20T02:04:31.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ef9ccaf3&amp;x-expires=1761570000&amp;x-signature=OsrEaDn9tPollUWncoSd9dptQY0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3725,25 +3725,25 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Me encantaaaa✨</t>
+          <t>Mi sueño haciéndose realidad 🥰🥺</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>45917.15711805555</v>
+        <v>45918.62016203703</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>03:46:15</t>
+          <t>14:53:02</t>
         </is>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550899370625254165', 'createTime': 1758080775, 'createTimeISO': '2025-09-17T03:46:15.000Z', 'text': 'Me encantaaaa✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e2ecea28&amp;x-expires=1761483600&amp;x-signature=tArHsKRepHCNYaIrczYaox30Ajo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551442303657116436', 'createTime': 1758207182, 'createTimeISO': '2025-09-18T14:53:02.000Z', 'text': 'Mi sueño haciéndose realidad 🥰🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6788284872554497030', 'uniqueId': 'anirivera_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c6e77f0d746b65b48a78e1205c8c82~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=18149634&amp;x-expires=1761570000&amp;x-signature=BoQKp1u0h9cWHHJc2i3Pc6d%2BVB4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3781,18 +3781,18 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
+          <t>Me salió tarde el vídeo 😟 yo quiero 🥹🙏🏻</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>45950.08646990741</v>
+        <v>45941.61577546296</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>45950</v>
+        <v>45941</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>02:04:31</t>
+          <t>14:46:43</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7563119000310334226', 'createTime': 1760925871, 'createTimeISO': '2025-10-20T02:04:31.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9ae9c2d0&amp;x-expires=1761483600&amp;x-signature=R%2BFMtXG%2FtHZBMa%2BGf707mjsjDRc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7559975652176577288', 'createTime': 1760194003, 'createTimeISO': '2025-10-11T14:46:43.000Z', 'text': 'Me salió tarde el vídeo 😟 yo quiero \U0001f979🙏🏻', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6670638394765033478', 'uniqueId': 'lindanarino', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/873e52b20a774b09b73f0f0d565e6959~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=66d1f629&amp;x-expires=1761570000&amp;x-signature=1LsnCvnrmE4%2Ff1aH6soMndEHhAo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3837,25 +3837,25 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cuando comienzan a dar respuesta si ya apliqué?🥹</t>
+          <t>Me encantaaaa✨</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>45916.99778935185</v>
+        <v>45917.15711805555</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>23:56:49</t>
+          <t>03:46:15</t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550840242002150162', 'createTime': 1758067009, 'createTimeISO': '2025-09-16T23:56:49.000Z', 'text': 'Cuando comienzan a dar respuesta si ya apliqué?\U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/dfeff60de882b1c199e34cb77f9557be~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=14e597c8&amp;x-expires=1761483600&amp;x-signature=p9VhhMTfbWYE7NqwzBztk1PcKxQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550899370625254165', 'createTime': 1758080775, 'createTimeISO': '2025-09-17T03:46:15.000Z', 'text': 'Me encantaaaa✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67e127c0&amp;x-expires=1761570000&amp;x-signature=vPwM08FcKecDUNpRacSTSqBH8lw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3893,25 +3893,25 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yo quierooooo✨</t>
+          <t>¿Qué tipo de contrato tienen?</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>45917.00403935185</v>
+        <v>45920.96097222222</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>45917</v>
+        <v>45920</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>00:05:49</t>
+          <t>23:03:48</t>
         </is>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550842534529860370', 'createTime': 1758067549, 'createTimeISO': '2025-09-17T00:05:49.000Z', 'text': 'Yo quierooooo✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781227104677250053', 'uniqueId': 'lauraleguizamou', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/531608b6e17cc4fc3195774b040b1421~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ca79b204&amp;x-expires=1761483600&amp;x-signature=2t4mTN2RlPzjhsYpGir7PaplUrQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552310929883448084', 'createTime': 1758409428, 'createTimeISO': '2025-09-20T23:03:48.000Z', 'text': '¿Qué tipo de contrato tienen?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856891169080443909', 'uniqueId': 'lourdesbarragan_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e377e28c29d509541307260e66fb275d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=439eae03&amp;x-expires=1761570000&amp;x-signature=6eqgGgzpXhGjZA1Amfyx%2FCvDlW8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556399100905341703', 'createTime': 1759361284, 'createTimeISO': '2025-10-01T23:28:04.000Z', 'text': 'hola alpina esta es mi colección de Mochis no es mucha molestia si me envías una caja de Mochisaurios gracias 😃😉', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531368579791438866', 'uniqueId': 'damian.smith.mora', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3106fbebef557d53c4193c9474d4163c~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b268504d&amp;x-expires=1761483600&amp;x-signature=Yj8dww8LJiFbIwlI5mVocWreJjk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556399100905341703', 'createTime': 1759361284, 'createTimeISO': '2025-10-01T23:28:04.000Z', 'text': 'hola alpina esta es mi colección de Mochis no es mucha molestia si me envías una caja de Mochisaurios gracias 😃😉', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531368579791438866', 'uniqueId': 'damian.smith.mora', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3106fbebef557d53c4193c9474d4163c~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bcfbc599&amp;x-expires=1761570000&amp;x-signature=%2BA7cmk5tD0HFBmhoeEkKuxY8WKQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4005,18 +4005,18 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>🫡🫡🫡</t>
+          <t>👍</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>45917.00991898148</v>
+        <v>45936.8365625</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>45917</v>
+        <v>45936</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>00:14:17</t>
+          <t>20:04:39</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550844710467732242', 'createTime': 1758068057, 'createTimeISO': '2025-09-17T00:14:17.000Z', 'text': '\U0001fae1\U0001fae1\U0001fae1', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b5b0b9d6&amp;x-expires=1761483600&amp;x-signature=K2niBkst6YFEppgZWaVNSsPScWk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558202100607091476', 'createTime': 1759781079, 'createTimeISO': '2025-10-06T20:04:39.000Z', 'text': '👍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452056190890116114', 'uniqueId': 'sabeldani10', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4b19cfb39961d6a4eec67ddf6a71ac66~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c6915cd5&amp;x-expires=1761570000&amp;x-signature=fmI7OQhmhKMMJ75bRwg80ZZxTrY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4061,18 +4061,18 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>🫡🫡🫡</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>45936.8365625</v>
+        <v>45917.00991898148</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>45936</v>
+        <v>45917</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20:04:39</t>
+          <t>00:14:17</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558202100607091476', 'createTime': 1759781079, 'createTimeISO': '2025-10-06T20:04:39.000Z', 'text': '👍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452056190890116114', 'uniqueId': 'sabeldani10', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4b19cfb39961d6a4eec67ddf6a71ac66~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f1d50873&amp;x-expires=1761483600&amp;x-signature=svgaE45o84RjGn8o10eSX3khXls%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550844710467732242', 'createTime': 1758068057, 'createTimeISO': '2025-09-17T00:14:17.000Z', 'text': '\U0001fae1\U0001fae1\U0001fae1', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=02da4822&amp;x-expires=1761570000&amp;x-signature=Tabf9cJDwWwdyVqfNIByzzQf6Ks%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4117,18 +4117,18 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>😁</t>
+          <t>😂</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>45932.00375</v>
+        <v>45933.28815972222</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>00:05:24</t>
+          <t>06:54:57</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556408658076435218', 'createTime': 1759363524, 'createTimeISO': '2025-10-02T00:05:24.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7280259132014806022', 'uniqueId': 'matilde.guerrero3', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7280259483488665606~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=04208827&amp;x-expires=1761483600&amp;x-signature=usnN0Dv%2B%2FLTivkodkfk%2FMvshlh8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556885364948173586', 'createTime': 1759474497, 'createTimeISO': '2025-10-03T06:54:57.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7444383176737113144', 'uniqueId': 'lirasa91', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4173,18 +4173,18 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>😂</t>
+          <t>@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>45933.28815972222</v>
+        <v>45920.12986111111</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>45933</v>
+        <v>45920</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>06:54:57</t>
+          <t>03:07:00</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556885364948173586', 'createTime': 1759474497, 'createTimeISO': '2025-10-03T06:54:57.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7444383176737113144', 'uniqueId': 'lirasa91', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=5eb5c316&amp;x-expires=1761483600&amp;x-signature=it42ikWpyJPic3g3ZWVRPx31hMc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552002528465699592', 'createTime': 1758337620, 'createTimeISO': '2025-09-20T03:07:00.000Z', 'text': '@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7382728939964548101', 'uniqueId': 'eve_watajai', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/c9212056428da8609f48a989cd6e9170~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c231ba0c&amp;x-expires=1761570000&amp;x-signature=dXbhER9DncJr0DPG2E7QuRDpet8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@mochis_yogoyogo💗'], 'detailedMentions': [{'userId': '7469144855873651730', 'nickName': 'mochis_yogoyogo💗', 'profileUrl': 'https://www.tiktok.com/@7469144855873651730', 'secUid': 'MS4wLjABAAAAfnDzVmGgNedG0asJ6YoXVgPkaL-69fpJq_hPO_uLHcj8SYDqMhAidX6vu-pf-BmB'}]}</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7555185101043680018', 'createTime': 1759078618, 'createTimeISO': '2025-09-28T16:56:58.000Z', 'text': '😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7475879249447666705', 'uniqueId': 'al454329', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/00eba74212b2c117219704065444145b~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=837aad71&amp;x-expires=1761483600&amp;x-signature=rn9xKx7lBqynkdeCxXTNCqqvNBo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7555185101043680018', 'createTime': 1759078618, 'createTimeISO': '2025-09-28T16:56:58.000Z', 'text': '😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7475879249447666705', 'uniqueId': 'al454329', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/00eba74212b2c117219704065444145b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d093ad88&amp;x-expires=1761570000&amp;x-signature=AKN8KM2vmiV1sO3onQaKKA%2FEYug%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4285,18 +4285,18 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina</t>
+          <t>@Chantal Thorin 😂</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>45920.12986111111</v>
+        <v>45917.01428240741</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>45920</v>
+        <v>45917</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>03:07:00</t>
+          <t>00:20:34</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552002528465699592', 'createTime': 1758337620, 'createTimeISO': '2025-09-20T03:07:00.000Z', 'text': '@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7382728939964548101', 'uniqueId': 'eve_watajai', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/c9212056428da8609f48a989cd6e9170~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=0a810f6c&amp;x-expires=1761483600&amp;x-signature=B50hqXgnZz2gBHWKwN%2F8pRqJhuo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': ['@mochis_yogoyogo💗'], 'detailedMentions': [{'userId': '7469144855873651730', 'nickName': 'mochis_yogoyogo💗', 'profileUrl': 'https://www.tiktok.com/@7469144855873651730', 'secUid': 'MS4wLjABAAAAfnDzVmGgNedG0asJ6YoXVgPkaL-69fpJq_hPO_uLHcj8SYDqMhAidX6vu-pf-BmB'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550846347324130055', 'createTime': 1758068434, 'createTimeISO': '2025-09-17T00:20:34.000Z', 'text': '@Chantal Thorin 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6788904373575074822', 'uniqueId': 'juanolmos023', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/715053c66c983c3c1c50e1eb7df0c471~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cdb6ae97&amp;x-expires=1761570000&amp;x-signature=za8CGAxYdpoFKFN4CSh6gvoIbb0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Chantal Thorin'], 'detailedMentions': [{'userId': '7323823789984531462', 'nickName': 'Chantal Thorin', 'profileUrl': 'https://www.tiktok.com/@7323823789984531462', 'secUid': 'MS4wLjABAAAAeVzy1YXMwyrURUZkWFufcDOQpRrR-rZvvbSNYGZdeSPQL7wiKvQELMaPx312In6i'}]}</t>
         </is>
       </c>
     </row>
@@ -4341,18 +4341,18 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>@Chantal Thorin 😂</t>
+          <t>😁</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>45917.01428240741</v>
+        <v>45932.00375</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>45917</v>
+        <v>45932</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>00:20:34</t>
+          <t>00:05:24</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550846347324130055', 'createTime': 1758068434, 'createTimeISO': '2025-09-17T00:20:34.000Z', 'text': '@Chantal Thorin 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6788904373575074822', 'uniqueId': 'juanolmos023', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/715053c66c983c3c1c50e1eb7df0c471~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=c152a1cb&amp;x-expires=1761483600&amp;x-signature=jGzIOzrvaF9jhIIALws3PaUpKUw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': ['@Chantal Thorin'], 'detailedMentions': [{'userId': '7323823789984531462', 'nickName': 'Chantal Thorin', 'profileUrl': 'https://www.tiktok.com/@7323823789984531462', 'secUid': 'MS4wLjABAAAAeVzy1YXMwyrURUZkWFufcDOQpRrR-rZvvbSNYGZdeSPQL7wiKvQELMaPx312In6i'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556408658076435218', 'createTime': 1759363524, 'createTimeISO': '2025-10-02T00:05:24.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7280259132014806022', 'uniqueId': 'matilde.guerrero3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7280259483488665606~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c7cb0cc3&amp;x-expires=1761570000&amp;x-signature=1fAymO1dwOzmYkcL%2BhDpL2ruHEo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556773829139677960', 'createTime': 1759448545, 'createTimeISO': '2025-10-02T23:42:25.000Z', 'text': 'vuelvan a poner a la banda de gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7338967674703905797', 'uniqueId': 'xa.m25', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/f18aaf30609d233d93d48aaec98bdc23~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=240043a2&amp;x-expires=1761483600&amp;x-signature=dhHVLCGL0okKObggeH4gLVmX2mE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556773829139677960', 'createTime': 1759448545, 'createTimeISO': '2025-10-02T23:42:25.000Z', 'text': 'vuelvan a poner a la banda de gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7338967674703905797', 'uniqueId': 'xa.m25', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f18aaf30609d233d93d48aaec98bdc23~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a0a80b73&amp;x-expires=1761570000&amp;x-signature=H4P5friRQF2vXLO%2Bs332x7GT7nE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4453,18 +4453,18 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>QUE VUELVA ALPILITRO 🙌🙏</t>
+          <t>Amooooo los mochisssssss</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>45923.78733796296</v>
+        <v>45919.10697916667</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>45923</v>
+        <v>45919</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>18:53:46</t>
+          <t>02:34:03</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553359733933458194', 'createTime': 1758653626, 'createTimeISO': '2025-09-23T18:53:46.000Z', 'text': 'QUE VUELVA ALPILITRO 🙌🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=645927f1&amp;x-expires=1761483600&amp;x-signature=245A21v6WMVj8EJHyu18thUJNOQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551622936564073224', 'createTime': 1758249243, 'createTimeISO': '2025-09-19T02:34:03.000Z', 'text': 'Amooooo los mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7c1e60b0&amp;x-expires=1761570000&amp;x-signature=Egj07X6mFOQf%2F9xF%2B3GghWInpO4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4509,18 +4509,18 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Amooooo los mochisssssss</t>
+          <t>QUE VUELVA ALPILITRO 🙌🙏</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>45919.10697916667</v>
+        <v>45923.78733796296</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>02:34:03</t>
+          <t>18:53:46</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551622936564073224', 'createTime': 1758249243, 'createTimeISO': '2025-09-19T02:34:03.000Z', 'text': 'Amooooo los mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=ca913fe5&amp;x-expires=1761483600&amp;x-signature=onpSqas0ZxYt3B%2B%2FtBmv7NKAHpw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553359733933458194', 'createTime': 1758653626, 'createTimeISO': '2025-09-23T18:53:46.000Z', 'text': 'QUE VUELVA ALPILITRO 🙌🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=895ae214&amp;x-expires=1761570000&amp;x-signature=sklHDUPVpgD%2BtJ6ZL2LNVhS9ie0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229830001885973', 'createTime': 1758157724, 'createTimeISO': '2025-09-18T01:08:44.000Z', 'text': 'Hmmm avena saladaaa gabsss?', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5da0e43a&amp;x-expires=1761483600&amp;x-signature=vh9rXohTnDZVGLsv3zABlKDCCKk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229830001885973', 'createTime': 1758157724, 'createTimeISO': '2025-09-18T01:08:44.000Z', 'text': 'Hmmm avena saladaaa gabsss?', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b3df464&amp;x-expires=1761570000&amp;x-signature=%2B5Kjk%2FNsFieX1m07yrNaeC%2FJ6u8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220050720670471', 'createTime': 1758155608, 'createTimeISO': '2025-09-18T00:33:28.000Z', 'text': 'quiero parte 2💙💙💙', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c64de15&amp;x-expires=1761483600&amp;x-signature=yAL7nTMnjZalubnp0HX5xUf%2BhU8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220050720670471', 'createTime': 1758155608, 'createTimeISO': '2025-09-18T00:33:28.000Z', 'text': 'quiero parte 2💙💙💙', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd681055&amp;x-expires=1761570000&amp;x-signature=wNrNCutAEF%2FapCKk%2F9SDDIPR9A4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4677,25 +4677,25 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>chevre el juego</t>
+          <t>jajajajajajajjajajajajajajaja eara miy bueno</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>45919.12591435185</v>
+        <v>45918.76694444445</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>45919</v>
+        <v>45918</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>03:01:19</t>
+          <t>18:24:24</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551629960492106503', 'createTime': 1758250879, 'createTimeISO': '2025-09-19T03:01:19.000Z', 'text': 'chevre el juego', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7428447431131857925', 'uniqueId': 'dario.bermudez.me', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e3f68c187a5bb898072670c79697373f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f685b331&amp;x-expires=1761483600&amp;x-signature=CFBK5MWPkn1mJlHsWTBOyj57lIM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551496749665649415', 'createTime': 1758219864, 'createTimeISO': '2025-09-18T18:24:24.000Z', 'text': 'jajajajajajajjajajajajajajaja eara miy bueno', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7337124256608732166', 'uniqueId': 'nathalye.cruz', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7337124473063407621~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0945d70a&amp;x-expires=1761570000&amp;x-signature=ziCcwA%2BJ6D8TfTk9hFfAz9Bxu%2BY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4733,25 +4733,25 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Viene en varios sabores?</t>
+          <t>chevre el juego</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>45918.12743055556</v>
+        <v>45919.12591435185</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>03:03:30</t>
+          <t>03:01:19</t>
         </is>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551259447134585631', 'createTime': 1758164610, 'createTimeISO': '2025-09-18T03:03:30.000Z', 'text': 'Viene en varios sabores?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '125087857735528448', 'uniqueId': 'camilocc3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-useast8-avt-0068-tx2/24fcb4fdd0b5e8275182d605c3f58355~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7c24735f&amp;x-expires=1761483600&amp;x-signature=qIdl3pkwMjYR%2BL6hs3CFdSJh0qA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551629960492106503', 'createTime': 1758250879, 'createTimeISO': '2025-09-19T03:01:19.000Z', 'text': 'chevre el juego', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7428447431131857925', 'uniqueId': 'dario.bermudez.me', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e3f68c187a5bb898072670c79697373f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=33a6fd4e&amp;x-expires=1761570000&amp;x-signature=9ACe7jD8i4iGnkxDLxSpKNVVSm4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4789,25 +4789,25 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jajajjaajajajjaa buenísimo</t>
+          <t>Viene en varios sabores?</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>45918.04732638889</v>
+        <v>45918.12743055556</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>45918</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>01:08:09</t>
+          <t>03:03:30</t>
         </is>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229700225778453', 'createTime': 1758157689, 'createTimeISO': '2025-09-18T01:08:09.000Z', 'text': 'Jajajjaajajajjaa buenísimo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5da0e43a&amp;x-expires=1761483600&amp;x-signature=vh9rXohTnDZVGLsv3zABlKDCCKk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551259447134585631', 'createTime': 1758164610, 'createTimeISO': '2025-09-18T03:03:30.000Z', 'text': 'Viene en varios sabores?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '125087857735528448', 'uniqueId': 'camilocc3', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-useast8-avt-0068-tx2/24fcb4fdd0b5e8275182d605c3f58355~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f29c1a0f&amp;x-expires=1761570000&amp;x-signature=fMsjDJWGCDRvYUJ%2BAUJicCk9Vw4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4843,23 +4843,27 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Jajajjaajajajjaa buenísimo</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="n">
-        <v>45918.04190972223</v>
+        <v>45918.04732638889</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>45918</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>01:00:21</t>
+          <t>01:08:09</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -4871,7 +4875,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551227674766607120', 'createTime': 1758157221, 'createTimeISO': '2025-09-18T01:00:21.000Z', 'text': '', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1520e198&amp;x-expires=1761483600&amp;x-signature=RG02BJPXU1NVHYy8yhGN%2FMY2fJo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229700225778453', 'createTime': 1758157689, 'createTimeISO': '2025-09-18T01:08:09.000Z', 'text': 'Jajajjaajajajjaa buenísimo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b3df464&amp;x-expires=1761570000&amp;x-signature=%2B5Kjk%2FNsFieX1m07yrNaeC%2FJ6u8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4895,24 +4899,20 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>✨✨</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" s="2" t="n">
-        <v>45918.02032407407</v>
+        <v>45918.04190972223</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>45918</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>00:29:16</t>
+          <t>01:00:21</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551217905787978504', 'createTime': 1758155356, 'createTimeISO': '2025-09-18T00:29:16.000Z', 'text': '✨✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6933232569349653510', 'uniqueId': 'mariangel_alzate01', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6bab063f1c64d97abedc28d75951cd7~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=171b32f5&amp;x-expires=1761483600&amp;x-signature=y9JgflrvkxnzofSNAtcO2eQR0BY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551227674766607120', 'createTime': 1758157221, 'createTimeISO': '2025-09-18T01:00:21.000Z', 'text': '', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4953,22 +4953,22 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>✨✨</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>45918.02133101852</v>
+        <v>45918.02032407407</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>45918</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>00:30:43</t>
+          <t>00:29:16</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220042781573895', 'createTime': 1758155443, 'createTimeISO': '2025-09-18T00:30:43.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7503357568275285010', 'uniqueId': 'mara.alejandra.va13', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b0e9c531aa12326c2c39b489de39faaf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=755b8096&amp;x-expires=1761483600&amp;x-signature=yWaWy%2FbaeSh%2Ffs2pdrQGYqjA%2FD8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551217905787978504', 'createTime': 1758155356, 'createTimeISO': '2025-09-18T00:29:16.000Z', 'text': '✨✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6933232569349653510', 'uniqueId': 'mariangel_alzate01', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6bab063f1c64d97abedc28d75951cd7~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7b547b2b&amp;x-expires=1761570000&amp;x-signature=Ufb6Vi0Zx4XLdTa9jzAUWN3Jbf0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5009,22 +5009,22 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>💗</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>45928.03357638889</v>
+        <v>45918.02133101852</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>45928</v>
+        <v>45918</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>00:48:21</t>
+          <t>00:30:43</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7554935448256398088', 'createTime': 1759020501, 'createTimeISO': '2025-09-28T00:48:21.000Z', 'text': '💗', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452411908450108422', 'uniqueId': 'unatalgaby_17', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d31bb8b63795296e53c4901e56663b5d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e0071dde&amp;x-expires=1761483600&amp;x-signature=SLRUaou58tvlDeTF6tEJ%2BfjMLlU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220042781573895', 'createTime': 1758155443, 'createTimeISO': '2025-09-18T00:30:43.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7503357568275285010', 'uniqueId': 'mara.alejandra.va13', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b0e9c531aa12326c2c39b489de39faaf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bbadeedd&amp;x-expires=1761570000&amp;x-signature=Ki0ovR4frSdtDWWmp5phxRthSG4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5065,18 +5065,18 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>🥰</t>
+          <t>💗</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>45923.90166666666</v>
+        <v>45928.03357638889</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>45923</v>
+        <v>45928</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>21:38:24</t>
+          <t>00:48:21</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7553402143257854727', 'createTime': 1758663504, 'createTimeISO': '2025-09-23T21:38:24.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6979791991334077446', 'uniqueId': 'lala_garzon0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/54f52760d8466c8575be7ac4ca3c5627~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6fc28a43&amp;x-expires=1761483600&amp;x-signature=WssR7YSsxW9X%2F%2B%2BJDe7eHUJ1B0Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7554935448256398088', 'createTime': 1759020501, 'createTimeISO': '2025-09-28T00:48:21.000Z', 'text': '💗', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452411908450108422', 'uniqueId': 'unatalgaby_17', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d31bb8b63795296e53c4901e56663b5d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8c9a8b03&amp;x-expires=1761570000&amp;x-signature=2vWbQGkyK9l26qpZ1OSUmcF60As%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5121,18 +5121,18 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>☺️☺️☺</t>
+          <t>🥰</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>45933.62277777777</v>
+        <v>45923.90166666666</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>45933</v>
+        <v>45923</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>14:56:48</t>
+          <t>21:38:24</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557009575929938696', 'createTime': 1759503408, 'createTimeISO': '2025-10-03T14:56:48.000Z', 'text': '☺️☺️☺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=050fbe84&amp;x-expires=1761483600&amp;x-signature=3UjumxBZ1s1oXtIW%2FrCUnzgNe%2FI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7553402143257854727', 'createTime': 1758663504, 'createTimeISO': '2025-09-23T21:38:24.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6979791991334077446', 'uniqueId': 'lala_garzon0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/54f52760d8466c8575be7ac4ca3c5627~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=490cd65f&amp;x-expires=1761570000&amp;x-signature=xW14ZuCk6hK5%2FKR4OCZ%2BZ3bl2tw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5177,18 +5177,18 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>😁</t>
+          <t>☺️☺️☺</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>45933.99601851852</v>
+        <v>45933.62277777777</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>45933</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>23:54:16</t>
+          <t>14:56:48</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557148031993807634', 'createTime': 1759535656, 'createTimeISO': '2025-10-03T23:54:16.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6927611184364356614', 'uniqueId': 'user0hhptpeva0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=54cd3839&amp;x-expires=1761483600&amp;x-signature=t2SXE0TP66XfawbO%2FnTkiB47Miw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557009575929938696', 'createTime': 1759503408, 'createTimeISO': '2025-10-03T14:56:48.000Z', 'text': '☺️☺️☺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9244ecc1&amp;x-expires=1761570000&amp;x-signature=NSDDd81hys0wPh8yt0LKPO%2BRR4M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5233,18 +5233,18 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>@Alpina 🐮 cuantos comentarios y reacciones y me ayudan a completar la colección de Mochis e ilumimochis (ayuden gente a que lo vean🥺)</t>
+          <t>😁</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>45922.03241898148</v>
+        <v>45933.99601851852</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>45922</v>
+        <v>45933</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>00:46:41</t>
+          <t>23:54:16</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7552707432578876180', 'createTime': 1758502001, 'createTimeISO': '2025-09-22T00:46:41.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones y me ayudan a completar la colección de Mochis e ilumimochis (ayuden gente a que lo vean🥺)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=04f10852&amp;x-expires=1761483600&amp;x-signature=gdhh3sdeBOLepBntdkVxrrZGiP0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557148031993807634', 'createTime': 1759535656, 'createTimeISO': '2025-10-03T23:54:16.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6927611184364356614', 'uniqueId': 'user0hhptpeva0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5289,25 +5289,25 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>jajajajajajajjajajajajajajaja eara miy bueno</t>
+          <t>@Alpina 🐮 cuantos comentarios y reacciones y me ayudan a completar la colección de Mochis e ilumimochis (ayuden gente a que lo vean🥺)</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>45918.76694444445</v>
+        <v>45922.03241898148</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18:24:24</t>
+          <t>00:46:41</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551496749665649415', 'createTime': 1758219864, 'createTimeISO': '2025-09-18T18:24:24.000Z', 'text': 'jajajajajajajjajajajajajajaja eara miy bueno', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7337124256608732166', 'uniqueId': 'nathalye.cruz', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7337124473063407621~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=06d7aaae&amp;x-expires=1761483600&amp;x-signature=9rGlhBwiKOiFo%2FC78xhn1%2F41E9w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7552707432578876180', 'createTime': 1758502001, 'createTimeISO': '2025-09-22T00:46:41.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones y me ayudan a completar la colección de Mochis e ilumimochis (ayuden gente a que lo vean🥺)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=196af7c3&amp;x-expires=1761570000&amp;x-signature=mfmJCzSJseg0BUINUmeciufLGgM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -5345,22 +5345,22 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Súper aprobado jajajaja</t>
+          <t>Tooooooop✨</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>45920.00429398148</v>
+        <v>45920.0344675926</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>00:06:11</t>
+          <t>00:49:38</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551955913683682055', 'createTime': 1758326771, 'createTimeISO': '2025-09-20T00:06:11.000Z', 'text': 'Súper aprobado jajajaja', 'diggCount': 32, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/dfeff60de882b1c199e34cb77f9557be~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=14e597c8&amp;x-expires=1761483600&amp;x-signature=p9VhhMTfbWYE7NqwzBztk1PcKxQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551967111200572161', 'createTime': 1758329378, 'createTimeISO': '2025-09-20T00:49:38.000Z', 'text': 'Tooooooop✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67e127c0&amp;x-expires=1761570000&amp;x-signature=vPwM08FcKecDUNpRacSTSqBH8lw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5401,26 +5401,26 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>alpina q es esta hermosura</t>
+          <t>Súper aprobado jajajaja</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>45923.97987268519</v>
+        <v>45920.00429398148</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>45923</v>
+        <v>45920</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>23:31:01</t>
+          <t>00:06:11</t>
         </is>
       </c>
       <c r="J89" t="n">
+        <v>32</v>
+      </c>
+      <c r="K89" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
       <c r="L89" t="b">
         <v>0</v>
       </c>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553431107175662354', 'createTime': 1758670261, 'createTimeISO': '2025-09-23T23:31:01.000Z', 'text': 'alpina q es esta hermosura', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7246183829702034437', 'uniqueId': '2s_sarah', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a9bc5c82ba1c64cdd2810f102faf0c8f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3998e28e&amp;x-expires=1761483600&amp;x-signature=xcugWiJKwPfD8VLSinXQwCGdQ6I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551955913683682055', 'createTime': 1758326771, 'createTimeISO': '2025-09-20T00:06:11.000Z', 'text': 'Súper aprobado jajajaja', 'diggCount': 32, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b5403971a2c0063750a9b7140d15458b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c8e7250&amp;x-expires=1761570000&amp;x-signature=UQMzZnJ%2FrlFhXJhZnlKl2gUk%2F7c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551953579881202440', 'createTime': 1758326232, 'createTimeISO': '2025-09-19T23:57:12.000Z', 'text': 'Me encantaaa!!!!! Aprobadooo', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6806474480425796614', 'uniqueId': 'lrendon11', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65f278fccdfba09731ee15dda4e3cb13~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cc23e79f&amp;x-expires=1761483600&amp;x-signature=X71U87yIJEzPDDrgq7A9K8%2FMpNc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551953579881202440', 'createTime': 1758326232, 'createTimeISO': '2025-09-19T23:57:12.000Z', 'text': 'Me encantaaa!!!!! Aprobadooo', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6806474480425796614', 'uniqueId': 'lrendon11', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65f278fccdfba09731ee15dda4e3cb13~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=55881956&amp;x-expires=1761570000&amp;x-signature=xm2LUG6oG5vbXC10gDn0cOb2CW4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552550716473639700', 'createTime': 1758465250, 'createTimeISO': '2025-09-21T14:34:10.000Z', 'text': 'Mi primer mandato! Ajajjaa toda dictadora 😂😂', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7127494140724216838', 'uniqueId': 'marlinq23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7127494903172923398~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c83c6c4&amp;x-expires=1761483600&amp;x-signature=RkiF2%2B625nZDlZlfPXD1cpBH%2Fb8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552550716473639700', 'createTime': 1758465250, 'createTimeISO': '2025-09-21T14:34:10.000Z', 'text': 'Mi primer mandato! Ajajjaa toda dictadora 😂😂', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7127494140724216838', 'uniqueId': 'marlinq23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7127494903172923398~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=da07acf4&amp;x-expires=1761570000&amp;x-signature=fRiF7O3JjhNtAgVd5%2FD2F4JDnE4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5569,25 +5569,25 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JAJAJAJAJA muuuuu</t>
+          <t>QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>45920.71737268518</v>
+        <v>45923.78701388889</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>45920</v>
+        <v>45923</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>17:13:01</t>
+          <t>18:53:18</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552220543425413944', 'createTime': 1758388381, 'createTimeISO': '2025-09-20T17:13:01.000Z', 'text': 'JAJAJAJAJA muuuuu', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f51c2dd0&amp;x-expires=1761483600&amp;x-signature=M4UFlJeqIvSMC8UCj5C0QEpYpgY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553359647815484167', 'createTime': 1758653598, 'createTimeISO': '2025-09-23T18:53:18.000Z', 'text': 'QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=895ae214&amp;x-expires=1761570000&amp;x-signature=sklHDUPVpgD%2BtJ6ZL2LNVhS9ie0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5625,22 +5625,22 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏</t>
+          <t>Me encanta</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>45923.78701388889</v>
+        <v>45925.74446759259</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>18:53:18</t>
+          <t>17:52:02</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553359647815484167', 'createTime': 1758653598, 'createTimeISO': '2025-09-23T18:53:18.000Z', 'text': 'QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ba1f6046&amp;x-expires=1761483600&amp;x-signature=4gkQmztoeOylS88uMAR%2ByoRGPe4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554086009761415956', 'createTime': 1758822722, 'createTimeISO': '2025-09-25T17:52:02.000Z', 'text': 'Me encanta', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6824118381916079109', 'uniqueId': 'urg7348', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7333599963433140229~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4f912f19&amp;x-expires=1761570000&amp;x-signature=mmKTApPjoPQDzn8bbD9QJ7Ft%2Fss%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5681,25 +5681,25 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Apoyo muuuuuuuucho jajaja</t>
+          <t>Increíbleeee</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>45920.07915509259</v>
+        <v>45922.29777777778</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>45920</v>
+        <v>45922</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>01:53:59</t>
+          <t>07:08:48</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983682992784136', 'createTime': 1758333239, 'createTimeISO': '2025-09-20T01:53:59.000Z', 'text': 'Apoyo muuuuuuuucho jajaja', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6577436033524727814', 'uniqueId': 'mafelovera', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7dea885196e9f4c245ffd2cb465a4c8a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=92b8ee81&amp;x-expires=1761483600&amp;x-signature=UccBLYyWnABHk2KYby1vn%2BDTKQg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552806947365241622', 'createTime': 1758524928, 'createTimeISO': '2025-09-22T07:08:48.000Z', 'text': 'Increíbleeee', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7251571663123465243', 'uniqueId': 'barbaramayan', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/58ed5201d3060082de17047de0ec72f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0d29e792&amp;x-expires=1761570000&amp;x-signature=4TP5c00vLmAa4zIE8PpmDHXegts%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5737,25 +5737,25 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Empezó mi novela favorita😭😍</t>
+          <t>Me encanta!</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>45922.90943287037</v>
+        <v>45927.95293981482</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>45922</v>
+        <v>45927</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>21:49:35</t>
+          <t>22:52:14</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553033945219810055', 'createTime': 1758577775, 'createTimeISO': '2025-09-22T21:49:35.000Z', 'text': 'Empezó mi novela favorita😭😍', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4d60aecf&amp;x-expires=1761483600&amp;x-signature=JlQRda01a1IFfhz6peVy%2BwrkX8M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554905527273751314', 'createTime': 1759013534, 'createTimeISO': '2025-09-27T22:52:14.000Z', 'text': 'Me encanta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6817121247644124166', 'uniqueId': 'marsd195', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1afb497a92aa0ea23b48a8a687a97094~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=adfdb620&amp;x-expires=1761570000&amp;x-signature=IzG9TEtEJ9qHUW6c%2BoUAK7lRjVQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5793,18 +5793,18 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>hola 😘</t>
+          <t>Empezó mi novela favorita😭😍</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>45919.98998842593</v>
+        <v>45922.90943287037</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>23:45:35</t>
+          <t>21:49:35</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950541917881104', 'createTime': 1758325535, 'createTimeISO': '2025-09-19T23:45:35.000Z', 'text': 'hola 😘', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1520e198&amp;x-expires=1761483600&amp;x-signature=RG02BJPXU1NVHYy8yhGN%2FMY2fJo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553033945219810055', 'createTime': 1758577775, 'createTimeISO': '2025-09-22T21:49:35.000Z', 'text': 'Empezó mi novela favorita😭😍', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd083daf&amp;x-expires=1761570000&amp;x-signature=Mj60V9kePw%2BGmIXKCvNAf2iQtmM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5849,26 +5849,26 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Increíbleeee</t>
+          <t>Apoyo muuuuuuuucho jajaja</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>45922.29777777778</v>
+        <v>45920.07915509259</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>45922</v>
+        <v>45920</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>07:08:48</t>
+          <t>01:53:59</t>
         </is>
       </c>
       <c r="J97" t="n">
+        <v>5</v>
+      </c>
+      <c r="K97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
       <c r="L97" t="b">
         <v>0</v>
       </c>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552806947365241622', 'createTime': 1758524928, 'createTimeISO': '2025-09-22T07:08:48.000Z', 'text': 'Increíbleeee', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7251571663123465243', 'uniqueId': 'barbaramayan', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/58ed5201d3060082de17047de0ec72f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b7c20971&amp;x-expires=1761483600&amp;x-signature=i2Q10TjRoJ0uyzLR%2FouNUUx%2FTwk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983682992784136', 'createTime': 1758333239, 'createTimeISO': '2025-09-20T01:53:59.000Z', 'text': 'Apoyo muuuuuuuucho jajaja', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6577436033524727814', 'uniqueId': 'mafelovera', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7dea885196e9f4c245ffd2cb465a4c8a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ef91bd35&amp;x-expires=1761570000&amp;x-signature=Ur9NQy0qbxMscSdL1dM6GgykKX4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5905,22 +5905,22 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>está kiut</t>
+          <t>hola 😘</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>45920.7575</v>
+        <v>45919.98998842593</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>45920</v>
+        <v>45919</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>18:10:48</t>
+          <t>23:45:35</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552235435209802503', 'createTime': 1758391848, 'createTimeISO': '2025-09-20T18:10:48.000Z', 'text': 'está kiut', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7406595235524690950', 'uniqueId': 'tatiana.r.rocha021328', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65263d812577fe31cc1016cb79e1e113~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=da23f7d9&amp;x-expires=1761483600&amp;x-signature=NCHjaBrWJZnkVY7VCjomXbnVz78%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950541917881104', 'createTime': 1758325535, 'createTimeISO': '2025-09-19T23:45:35.000Z', 'text': 'hola 😘', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5961,18 +5961,18 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pero verídico</t>
+          <t>Lindo</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>45921.13072916667</v>
+        <v>45920.64417824074</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>45921</v>
+        <v>45920</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>03:08:15</t>
+          <t>15:27:37</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552373947406664455', 'createTime': 1758424095, 'createTimeISO': '2025-09-21T03:08:15.000Z', 'text': 'Pero verídico', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6916307664519742470', 'uniqueId': 'daniel_rojas.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/1b1931cd030125ddc18f8e0cba099651~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=abdde3e3&amp;x-expires=1761483600&amp;x-signature=4sU1lm%2FkCMAZsYJr3vtjzloTQko%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552193394950685448', 'createTime': 1758382057, 'createTimeISO': '2025-09-20T15:27:37.000Z', 'text': 'Lindo', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6747056373932590086', 'uniqueId': 'monimarpor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327496776705933318~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2bbedc1a&amp;x-expires=1761570000&amp;x-signature=mhmIGPkItx%2B9SVR8Jd%2Fhol0ntGE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6017,22 +6017,22 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>mi mami trabaja en alpina y me trajo Mochis 🥰</t>
+          <t>Pero verídico</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>45924.08138888889</v>
+        <v>45921.13072916667</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>45924</v>
+        <v>45921</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>01:57:12</t>
+          <t>03:08:15</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553468863707759377', 'createTime': 1758679032, 'createTimeISO': '2025-09-24T01:57:12.000Z', 'text': 'mi mami trabaja en alpina y me trajo Mochis 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6796362843291354118', 'uniqueId': 'sampreds', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6ab46faa73ba2a267e5c627e7857a09a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=195299f8&amp;x-expires=1761483600&amp;x-signature=gBclZZRL2LC0ThCbR5lTyHW71cs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552373947406664455', 'createTime': 1758424095, 'createTimeISO': '2025-09-21T03:08:15.000Z', 'text': 'Pero verídico', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6916307664519742470', 'uniqueId': 'daniel_rojas.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/1b1931cd030125ddc18f8e0cba099651~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=653205f6&amp;x-expires=1761570000&amp;x-signature=pNG6fgE0pL%2FNWwZqCCC%2FcsRA%2FUk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6073,25 +6073,25 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Me encanta!</t>
+          <t>hola</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>45927.95293981482</v>
+        <v>45919.99099537037</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>45927</v>
+        <v>45919</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>22:52:14</t>
+          <t>23:47:02</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554905527273751314', 'createTime': 1759013534, 'createTimeISO': '2025-09-27T22:52:14.000Z', 'text': 'Me encanta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6817121247644124166', 'uniqueId': 'marsd195', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1afb497a92aa0ea23b48a8a687a97094~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9426956a&amp;x-expires=1761483600&amp;x-signature=UF%2FdXJbENVLrFeFyX1B9oa%2Bxk3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950956708922130', 'createTime': 1758325622, 'createTimeISO': '2025-09-19T23:47:02.000Z', 'text': 'hola', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f9e9987c&amp;x-expires=1761570000&amp;x-signature=p%2FE07rUH8alxIxevM29aaBzUoMk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6129,25 +6129,25 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Amooooooooo ✨❤</t>
+          <t>Siiii</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>45920.63488425926</v>
+        <v>45920.26096064815</v>
       </c>
       <c r="H102" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>15:14:14</t>
+          <t>06:15:47</t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552189950164157202', 'createTime': 1758381254, 'createTimeISO': '2025-09-20T15:14:14.000Z', 'text': 'Amooooooooo ✨❤', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=427a4f56&amp;x-expires=1761483600&amp;x-signature=YQx4fM0jcJV9O8C5m1iwl7yHkT8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552051172909024016', 'createTime': 1758348947, 'createTimeISO': '2025-09-20T06:15:47.000Z', 'text': 'Siiii', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781933506022491142', 'uniqueId': 'carovelez_9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9bafd1d600cb2409f94c1df9050c163d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bc132d05&amp;x-expires=1761570000&amp;x-signature=quB1EzmpV5Z59%2Fa5Yo3WQxuM12w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6185,25 +6185,25 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Siiii</t>
+          <t>Amooooooooo ✨❤</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>45920.26096064815</v>
+        <v>45920.63488425926</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>06:15:47</t>
+          <t>15:14:14</t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552051172909024016', 'createTime': 1758348947, 'createTimeISO': '2025-09-20T06:15:47.000Z', 'text': 'Siiii', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781933506022491142', 'uniqueId': 'carovelez_9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9bafd1d600cb2409f94c1df9050c163d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c5a365d&amp;x-expires=1761483600&amp;x-signature=GGWs%2F5mKCy58cBn9s0EaKHXRM9Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552189950164157202', 'createTime': 1758381254, 'createTimeISO': '2025-09-20T15:14:14.000Z', 'text': 'Amooooooooo ✨❤', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a94ad8b3&amp;x-expires=1761570000&amp;x-signature=OpO%2BwRtnjY5miabvZsvSJtDKmxQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6241,22 +6241,22 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tooooooop✨</t>
+          <t>JAJAJAJAJA muuuuu</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>45920.0344675926</v>
+        <v>45920.71737268518</v>
       </c>
       <c r="H104" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>00:49:38</t>
+          <t>17:13:01</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551967111200572161', 'createTime': 1758329378, 'createTimeISO': '2025-09-20T00:49:38.000Z', 'text': 'Tooooooop✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e2ecea28&amp;x-expires=1761483600&amp;x-signature=tArHsKRepHCNYaIrczYaox30Ajo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552220543425413944', 'createTime': 1758388381, 'createTimeISO': '2025-09-20T17:13:01.000Z', 'text': 'JAJAJAJAJA muuuuu', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9318afca&amp;x-expires=1761570000&amp;x-signature=vuOKTe6NBdJzzn2l%2FGqo1IGgWyM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6297,25 +6297,25 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lindo</t>
+          <t>está kiut</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>45920.64417824074</v>
+        <v>45920.7575</v>
       </c>
       <c r="H105" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>15:27:37</t>
+          <t>18:10:48</t>
         </is>
       </c>
       <c r="J105" t="n">
         <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552193394950685448', 'createTime': 1758382057, 'createTimeISO': '2025-09-20T15:27:37.000Z', 'text': 'Lindo', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6747056373932590086', 'uniqueId': 'monimarpor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327496776705933318~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=58843361&amp;x-expires=1761483600&amp;x-signature=b1uGsmDLg3I5WFySIyWwLArmdP4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552235435209802503', 'createTime': 1758391848, 'createTimeISO': '2025-09-20T18:10:48.000Z', 'text': 'está kiut', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7406595235524690950', 'uniqueId': 'tatiana.r.rocha021328', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65263d812577fe31cc1016cb79e1e113~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=62d8526b&amp;x-expires=1761570000&amp;x-signature=l76cozSCbSE4SHR2iEodDZpJH8E%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6353,25 +6353,25 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>hola</t>
+          <t>Me encanta el Muuuuuuu💖</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>45919.99099537037</v>
+        <v>45920.03078703704</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>45919</v>
+        <v>45920</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>23:47:02</t>
+          <t>00:44:20</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950956708922130', 'createTime': 1758325622, 'createTimeISO': '2025-09-19T23:47:02.000Z', 'text': 'hola', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2f29afec&amp;x-expires=1761483600&amp;x-signature=np27DzwhmUWmAlLnUGkaGK1U2uY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551965699524461330', 'createTime': 1758329060, 'createTimeISO': '2025-09-20T00:44:20.000Z', 'text': 'Me encanta el Muuuuuuu💖', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6409,25 +6409,25 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Me encanta</t>
+          <t>amo este muuuuuuundoo😏</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>45925.74446759259</v>
+        <v>45920.07972222222</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>45925</v>
+        <v>45920</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>17:52:02</t>
+          <t>01:54:48</t>
         </is>
       </c>
       <c r="J107" t="n">
         <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554086009761415956', 'createTime': 1758822722, 'createTimeISO': '2025-09-25T17:52:02.000Z', 'text': 'Me encanta', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6824118381916079109', 'uniqueId': 'urg7348', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7333599963433140229~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b4d68333&amp;x-expires=1761483600&amp;x-signature=VSRzi2vkqT0wRjhEcRXiNuVcRwc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983930652689172', 'createTime': 1758333288, 'createTimeISO': '2025-09-20T01:54:48.000Z', 'text': 'amo este muuuuuuundoo😏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6842674101811954693', 'uniqueId': 'lizz_fndz', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f5a7346c0b99528e0b975fc998230121~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=38b806ba&amp;x-expires=1761570000&amp;x-signature=%2BcHQVvaJOdEcFnUx%2BtJiMvhS%2BIg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6465,25 +6465,25 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Me encanta el Muuuuuuu💖</t>
+          <t>mi mami trabaja en alpina y me trajo Mochis 🥰</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>45920.03078703704</v>
+        <v>45924.08138888889</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>45920</v>
+        <v>45924</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>00:44:20</t>
+          <t>01:57:12</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551965699524461330', 'createTime': 1758329060, 'createTimeISO': '2025-09-20T00:44:20.000Z', 'text': 'Me encanta el Muuuuuuu💖', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0efc43a6&amp;x-expires=1761483600&amp;x-signature=%2FlzlYaBNjstaHyyaUdQHSXP8y2U%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553468863707759377', 'createTime': 1758679032, 'createTimeISO': '2025-09-24T01:57:12.000Z', 'text': 'mi mami trabaja en alpina y me trajo Mochis 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6796362843291354118', 'uniqueId': 'sampreds', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6ab46faa73ba2a267e5c627e7857a09a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4008d23a&amp;x-expires=1761570000&amp;x-signature=S%2FBMB9yMn78%2BP%2BorGNNIlzamWIY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6521,22 +6521,22 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>amo este muuuuuuundoo😏</t>
+          <t>ME ENCANTA✨✨</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>45920.07972222222</v>
+        <v>45920.06896990741</v>
       </c>
       <c r="H109" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>01:54:48</t>
+          <t>01:39:19</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
         <v>1</v>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983930652689172', 'createTime': 1758333288, 'createTimeISO': '2025-09-20T01:54:48.000Z', 'text': 'amo este muuuuuuundoo😏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6842674101811954693', 'uniqueId': 'lizz_fndz', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f5a7346c0b99528e0b975fc998230121~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6d9a0706&amp;x-expires=1761483600&amp;x-signature=0aI66ZhGBCJcrtEhRkB4cynIMgU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551979924456211207', 'createTime': 1758332359, 'createTimeISO': '2025-09-20T01:39:19.000Z', 'text': 'ME ENCANTA✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6577,18 +6577,18 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Me gusta MUUUUUcho</t>
+          <t>aprobadooo, amooo</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>45920.63900462963</v>
+        <v>45920.64584490741</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>15:20:10</t>
+          <t>15:30:01</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552191427935208203', 'createTime': 1758381610, 'createTimeISO': '2025-09-20T15:20:10.000Z', 'text': 'Me gusta MUUUUUcho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6786345043017958405', 'uniqueId': 'rafaelladm_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/73cfb3946b471a5575a9bd8db504145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=562031f8&amp;x-expires=1761483600&amp;x-signature=iavh9WlI2nEp%2FXjxL%2BXe37Y1zEI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552194010451477269', 'createTime': 1758382201, 'createTimeISO': '2025-09-20T15:30:01.000Z', 'text': 'aprobadooo, amooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=109ea6b2&amp;x-expires=1761570000&amp;x-signature=rf95%2BkUaV%2Fv4O%2FPzSATd4vhGdvA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6633,25 +6633,25 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ME ENCANTA✨✨</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>45920.06896990741</v>
+        <v>45925.80569444445</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>45920</v>
+        <v>45925</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>01:39:19</t>
+          <t>19:20:12</t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551979924456211207', 'createTime': 1758332359, 'createTimeISO': '2025-09-20T01:39:19.000Z', 'text': 'ME ENCANTA✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4ce9d466&amp;x-expires=1761483600&amp;x-signature=jTsPVOMx3hLRzNrnA0jDXPv%2BHfc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554108742757827346', 'createTime': 1758828012, 'createTimeISO': '2025-09-25T19:20:12.000Z', 'text': 'Si', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7472435716635902996', 'uniqueId': 'saraisabellamolin21', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a143062aac046151f845e8a7d43027c0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=39b83097&amp;x-expires=1761570000&amp;x-signature=L%2BxjMYCn2%2F4pDDLH8XOrdTmGSdA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6689,18 +6689,18 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>aprobadooo, amooo</t>
+          <t>Me gusta MUUUUUcho</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>45920.64584490741</v>
+        <v>45920.63900462963</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>15:30:01</t>
+          <t>15:20:10</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552194010451477269', 'createTime': 1758382201, 'createTimeISO': '2025-09-20T15:30:01.000Z', 'text': 'aprobadooo, amooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3158b83e&amp;x-expires=1761483600&amp;x-signature=b1rjYf14FAtSQp9BfgTNFYSUnAk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552191427935208203', 'createTime': 1758381610, 'createTimeISO': '2025-09-20T15:20:10.000Z', 'text': 'Me gusta MUUUUUcho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6786345043017958405', 'uniqueId': 'rafaelladm_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/73cfb3946b471a5575a9bd8db504145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=da843faf&amp;x-expires=1761570000&amp;x-signature=8igBwrDyEN7%2FUy%2BlGRk%2FQE0ANMw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6745,25 +6745,25 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>Califiquen mi nuevo mochi saurio!!!💗</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>45925.80569444445</v>
+        <v>45922.05614583333</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>45925</v>
+        <v>45922</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>19:20:12</t>
+          <t>01:20:51</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554108742757827346', 'createTime': 1758828012, 'createTimeISO': '2025-09-25T19:20:12.000Z', 'text': 'Si', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7472435716635902996', 'uniqueId': 'saraisabellamolin21', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a143062aac046151f845e8a7d43027c0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=abb09cc9&amp;x-expires=1761483600&amp;x-signature=H%2FkK0rPvpyxpAvAWLgonK0o8md8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552717306100761351', 'createTime': 1758504051, 'createTimeISO': '2025-09-22T01:20:51.000Z', 'text': 'Califiquen mi nuevo mochi saurio!!!💗', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7025228362498999301', 'uniqueId': 'krystelnavarrober', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3da7823061496f0246300c1ee868876f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=55f61d03&amp;x-expires=1761570000&amp;x-signature=lhZ9iWpl%2F4WLBD2yommpMC4NXFk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6801,25 +6801,25 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Califiquen mi nuevo mochi saurio!!!💗</t>
+          <t>✅✅✅</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>45922.05614583333</v>
+        <v>45920.11243055556</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>45922</v>
+        <v>45920</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>01:20:51</t>
+          <t>02:41:54</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552717306100761351', 'createTime': 1758504051, 'createTimeISO': '2025-09-22T01:20:51.000Z', 'text': 'Califiquen mi nuevo mochi saurio!!!💗', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7025228362498999301', 'uniqueId': 'krystelnavarrober', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3da7823061496f0246300c1ee868876f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=60145ae5&amp;x-expires=1761483600&amp;x-signature=NfJ4ilwoe65LWDbP6CgxS1H0FaA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551996069400838930', 'createTime': 1758336114, 'createTimeISO': '2025-09-20T02:41:54.000Z', 'text': '✅✅✅', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775228984448959493', 'uniqueId': 'francescalvarezr_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2e5e4150ee1705a086acc14bc21b08d4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5c2b3c5a&amp;x-expires=1761570000&amp;x-signature=X%2Byd5RdZp8zezdsTCEC0puSFCAc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6857,22 +6857,22 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>✅✅✅</t>
+          <t>🥰</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>45920.11243055556</v>
+        <v>45920.60407407407</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>02:41:54</t>
+          <t>14:29:52</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551996069400838930', 'createTime': 1758336114, 'createTimeISO': '2025-09-20T02:41:54.000Z', 'text': '✅✅✅', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775228984448959493', 'uniqueId': 'francescalvarezr_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2e5e4150ee1705a086acc14bc21b08d4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c4b126d&amp;x-expires=1761483600&amp;x-signature=hGnPQFP7Zs70VMu1VVEe1c3Z95A%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552178343107592961', 'createTime': 1758378592, 'createTimeISO': '2025-09-20T14:29:52.000Z', 'text': '🥰', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806405540710351877', 'uniqueId': 'karenmarcelagarzo', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326838454582460422~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=47ac6a54&amp;x-expires=1761570000&amp;x-signature=HAxM632oE7zW3uTlf%2BkON5VAO9c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6913,18 +6913,18 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>🥰</t>
+          <t>alpina q es esta hermosura</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>45920.60407407407</v>
+        <v>45923.97987268519</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>45920</v>
+        <v>45923</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>14:29:52</t>
+          <t>23:31:01</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552178343107592961', 'createTime': 1758378592, 'createTimeISO': '2025-09-20T14:29:52.000Z', 'text': '🥰', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806405540710351877', 'uniqueId': 'karenmarcelagarzo', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326838454582460422~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=57d10472&amp;x-expires=1761483600&amp;x-signature=j1ZCQ8T0ruObI%2BhjmmNwKDY1Zuk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553431107175662354', 'createTime': 1758670261, 'createTimeISO': '2025-09-23T23:31:01.000Z', 'text': 'alpina q es esta hermosura', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7246183829702034437', 'uniqueId': '2s_sarah', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a9bc5c82ba1c64cdd2810f102faf0c8f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6f305374&amp;x-expires=1761570000&amp;x-signature=tZGnQyH21TPiCLp%2BG4PCbk2bu1M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6969,25 +6969,25 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wow! Que cracks</t>
+          <t>🥰🥰🥰</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>45920.13050925926</v>
+        <v>45919.98965277777</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>45920</v>
+        <v>45919</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>03:07:56</t>
+          <t>23:45:06</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552002771790136071', 'createTime': 1758337676, 'createTimeISO': '2025-09-20T03:07:56.000Z', 'text': 'Wow! Que cracks', 'diggCount': 4, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6761789459468403717', 'uniqueId': 'mariajimenadiaz5', 'avatarThumbnail': 'https://p77-sign-va-lite.tiktokcdn.com/tos-maliva-avt-0068/7334740815043887110~tplv-tiktokx-cropcenter:100:100.jpg?dr=10399&amp;refresh_token=501454e6&amp;x-expires=1761483600&amp;x-signature=QYkZB%2BmQCKSazjUdzXfyQQZYejA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=no1a', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950414629061394', 'createTime': 1758325506, 'createTimeISO': '2025-09-19T23:45:06.000Z', 'text': '🥰🥰🥰', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830514363565278214', 'uniqueId': 'mariafernandasalc02', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/f48ef1c788191659fa2e09d032706b87~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a75aafc6&amp;x-expires=1761570000&amp;x-signature=Y6t23RsXTVBSuvmA8%2FClRygnGHE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7025,25 +7025,25 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Me encantaaaa</t>
+          <t>🥺</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>45920.30841435185</v>
+        <v>45928.61208333333</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>45920</v>
+        <v>45928</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>07:24:07</t>
+          <t>14:41:24</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552068707821749048', 'createTime': 1758353047, 'createTimeISO': '2025-09-20T07:24:07.000Z', 'text': 'Me encantaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6572155711261966341', 'uniqueId': 'renata.garces', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/0e4e281eab3b0fe02f45e37f8562c901~tplv-tiktokx-cropcenter:100:100.jpg?dr=10399&amp;refresh_token=c9c451ae&amp;x-expires=1761483600&amp;x-signature=Stkh2zHYuxfTk8QMuTHlo32vGCg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=no1a', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7555150174504469266', 'createTime': 1759070484, 'createTimeISO': '2025-09-28T14:41:24.000Z', 'text': '🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6891441655778624518', 'uniqueId': 'kris_salazar23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/76c1e9d5f762548bf55f86a2eeb72fa3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=33d0542e&amp;x-expires=1761570000&amp;x-signature=BgFnq8zWBkFQ6iHiC4l9JXd%2FNDg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7085,18 +7085,18 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>45919.98965277777</v>
+        <v>45934.13739583334</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>45919</v>
+        <v>45934</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>23:45:06</t>
+          <t>03:17:51</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950414629061394', 'createTime': 1758325506, 'createTimeISO': '2025-09-19T23:45:06.000Z', 'text': '🥰🥰🥰', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830514363565278214', 'uniqueId': 'mariafernandasalc02', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/f48ef1c788191659fa2e09d032706b87~tplv-tiktokx-cropcenter:100:100.jpg?dr=10399&amp;refresh_token=2ffc3d99&amp;x-expires=1761483600&amp;x-signature=9cB%2BAg8pG7Dfx%2BfjALkKiStE3dg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=no1a', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7557200531950256903', 'createTime': 1759547871, 'createTimeISO': '2025-10-04T03:17:51.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7368157374302946309', 'uniqueId': 'jeronimoo334', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4853e0d53cbeb9e2a1c9346cf5e1b179~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4ad94db8&amp;x-expires=1761570000&amp;x-signature=%2FU3XlyNvrmDtgwMU2C7XdWG43dM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7137,18 +7137,18 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>🥰🥰🥰</t>
+          <t>😅</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>45934.13739583334</v>
+        <v>45937.14810185185</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>45934</v>
+        <v>45937</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>03:17:51</t>
+          <t>03:33:16</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7557200531950256903', 'createTime': 1759547871, 'createTimeISO': '2025-10-04T03:17:51.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7368157374302946309', 'uniqueId': 'jeronimoo334', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4853e0d53cbeb9e2a1c9346cf5e1b179~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=dfae0fda&amp;x-expires=1761483600&amp;x-signature=jIbt%2F9nlWarJSRfk7fJ4qPySqRU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558317759676121874', 'createTime': 1759807996, 'createTimeISO': '2025-10-07T03:33:16.000Z', 'text': '😅', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6842107016141751301', 'uniqueId': 'pandrea9610', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7325541937888952325~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=77b2de12&amp;x-expires=1761570000&amp;x-signature=8fHcH93hZBWvJIgjEaZW8yOExBU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7193,25 +7193,25 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>😅</t>
+          <t>Wow! Que cracks</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>45937.14810185185</v>
+        <v>45920.13050925926</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>45937</v>
+        <v>45920</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>03:33:16</t>
+          <t>03:07:56</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558317759676121874', 'createTime': 1759807996, 'createTimeISO': '2025-10-07T03:33:16.000Z', 'text': '😅', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6842107016141751301', 'uniqueId': 'pandrea9610', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7325541937888952325~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e2e2d571&amp;x-expires=1761483600&amp;x-signature=D9FbQ31zUFYMLVPYPTd17kr66Jc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552002771790136071', 'createTime': 1758337676, 'createTimeISO': '2025-09-20T03:07:56.000Z', 'text': 'Wow! Que cracks', 'diggCount': 4, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6761789459468403717', 'uniqueId': 'mariajimenadiaz5', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/7334740815043887110~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=956df52c&amp;x-expires=1761570000&amp;x-signature=JZqRLRkaLRTPzCKLOdfwf5Vq7LY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7249,25 +7249,25 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨</t>
+          <t>Me encantaaaa</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>45937.91074074074</v>
+        <v>45920.30841435185</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>45937</v>
+        <v>45920</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>21:51:28</t>
+          <t>07:24:07</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558600728525275934', 'createTime': 1759873888, 'createTimeISO': '2025-10-07T21:51:28.000Z', 'text': 'Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '130977736172539904', 'uniqueId': 'giraldotogaby', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-useast5-avt-0068-tx/a2c5a1fbbbc85ff0c2c73bd1842eb1cc~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=738bc3c6&amp;x-expires=1761483600&amp;x-signature=qJojR%2B%2BeBqLlYw2x8lanlAMmMF4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552068707821749048', 'createTime': 1758353047, 'createTimeISO': '2025-09-20T07:24:07.000Z', 'text': 'Me encantaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6572155711261966341', 'uniqueId': 'renata.garces', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/0e4e281eab3b0fe02f45e37f8562c901~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=ef068d0e&amp;x-expires=1761570000&amp;x-signature=5PqrnlmwE1xbzj6ngZ4REEzBDQY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7305,25 +7305,25 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>🥺</t>
+          <t>Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>45928.61208333333</v>
+        <v>45937.91074074074</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>45928</v>
+        <v>45937</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>14:41:24</t>
+          <t>21:51:28</t>
         </is>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7555150174504469266', 'createTime': 1759070484, 'createTimeISO': '2025-09-28T14:41:24.000Z', 'text': '🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6891441655778624518', 'uniqueId': 'kris_salazar23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/76c1e9d5f762548bf55f86a2eeb72fa3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=beca4720&amp;x-expires=1761483600&amp;x-signature=5EjFItU%2FuShSNb9Z1eDpKC8JhGw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558600728525275934', 'createTime': 1759873888, 'createTimeISO': '2025-10-07T21:51:28.000Z', 'text': 'Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '130977736172539904', 'uniqueId': 'giraldotogaby', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/a2c5a1fbbbc85ff0c2c73bd1842eb1cc~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=3363bec1&amp;x-expires=1761570000&amp;x-signature=8lWgdcIhm5lq1URisMtYb3cuWtA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552706319259435783', 'createTime': 1758501808, 'createTimeISO': '2025-09-22T00:43:28.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones acá en el vídeo y me mandasla nueva colección de los mochis dinosaurios (ayuden que lo vean🙊)', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ece1346c&amp;x-expires=1761483600&amp;x-signature=v8gKjwjCClw5%2BsTMyHaBrL4DuF0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552706319259435783', 'createTime': 1758501808, 'createTimeISO': '2025-09-22T00:43:28.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones acá en el vídeo y me mandasla nueva colección de los mochis dinosaurios (ayuden que lo vean🙊)', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=196af7c3&amp;x-expires=1761570000&amp;x-signature=mfmJCzSJseg0BUINUmeciufLGgM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -7417,18 +7417,18 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>También reciben pasantes?</t>
+          <t>Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>45954.7812962963</v>
+        <v>45926.65694444445</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>45954</v>
+        <v>45926</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>18:45:04</t>
+          <t>15:46:00</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7564861171879445256', 'createTime': 1761331504, 'createTimeISO': '2025-10-24T18:45:04.000Z', 'text': 'También reciben pasantes?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '166386831993888768', 'uniqueId': 'aleja040610', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/d38de0738e43e8e0ce00becaad0aca08~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=10790602&amp;x-expires=1761483600&amp;x-signature=MD7GHACf%2BjsFtz4P9AKNe%2BuyJFY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554424648151941905', 'createTime': 1758901560, 'createTimeISO': '2025-09-26T15:46:00.000Z', 'text': 'Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7436539205088396344', 'uniqueId': 'isaac_mora1903', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bd074fbf9f61ee99fcea8ef5f350b2bf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=49e69c97&amp;x-expires=1761570000&amp;x-signature=qlqMqsO1TGLI5UjxJVxDBWpMGj4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7473,25 +7473,25 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mi sueñoooo 😩 ya quiero hacer parte de ustedes</t>
+          <t>nueva presentación 😳!</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>45925.08212962963</v>
+        <v>45925.20309027778</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>01:58:16</t>
+          <t>04:52:27</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553840238716945153', 'createTime': 1758765496, 'createTimeISO': '2025-09-25T01:58:16.000Z', 'text': 'Mi sueñoooo 😩 ya quiero hacer parte de ustedes', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=12eeeed1&amp;x-expires=1761483600&amp;x-signature=%2FQktCU43siBp5Reu%2B5exdZs22Dw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553885128557478672', 'createTime': 1758775947, 'createTimeISO': '2025-09-25T04:52:27.000Z', 'text': 'nueva presentación 😳!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7529,22 +7529,22 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gran historia jajajaja 🥳</t>
+          <t>cuando llegan a Perú los Mochis 😭😭</t>
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>45925.03746527778</v>
+        <v>45927.6415625</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>45925</v>
+        <v>45927</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>00:53:57</t>
+          <t>15:23:51</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553823647435178770', 'createTime': 1758761637, 'createTimeISO': '2025-09-25T00:53:57.000Z', 'text': 'Gran historia jajajaja 🥳', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=dde1ef35&amp;x-expires=1761483600&amp;x-signature=OiEWqH9CLSCXIrUF956O1yzchVc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554790021015946005', 'createTime': 1758986631, 'createTimeISO': '2025-09-27T15:23:51.000Z', 'text': 'cuando llegan a Perú los Mochis 😭😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7093344759511532549', 'uniqueId': 'hanzel3075', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e5fc427c21f18dd65a5d6366a919b2b8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a36ccb6f&amp;x-expires=1761570000&amp;x-signature=qPN%2F2nsESTmE2vKSFc2bn1%2FPU0Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7585,18 +7585,18 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
+          <t>estando en etapa lectiva puedo aplicar gracias</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>45950.08873842593</v>
+        <v>45926.77866898148</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>45950</v>
+        <v>45926</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>02:07:47</t>
+          <t>18:41:17</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7563119838848598792', 'createTime': 1760926067, 'createTimeISO': '2025-10-20T02:07:47.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9ae9c2d0&amp;x-expires=1761483600&amp;x-signature=R%2BFMtXG%2FtHZBMa%2BGf707mjsjDRc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554469785704645384', 'createTime': 1758912077, 'createTimeISO': '2025-09-26T18:41:17.000Z', 'text': 'estando en etapa lectiva puedo aplicar gracias', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=30df542e&amp;x-expires=1761570000&amp;x-signature=ePCGB9BrUbZkPVx3h%2BelHiRBM9o%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7641,25 +7641,25 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>estando en etapa lectiva puedo aplicar gracias</t>
+          <t>Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>45926.77866898148</v>
+        <v>45925.06542824074</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>45926</v>
+        <v>45925</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>18:41:17</t>
+          <t>01:34:13</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554469785704645384', 'createTime': 1758912077, 'createTimeISO': '2025-09-26T18:41:17.000Z', 'text': 'estando en etapa lectiva puedo aplicar gracias', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d24f6cd8&amp;x-expires=1761483600&amp;x-signature=sASoTG8pBaQDFaH%2B6K2yp1PIU2s%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553834039527654152', 'createTime': 1758764053, 'createTimeISO': '2025-09-25T01:34:13.000Z', 'text': 'Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7697,18 +7697,18 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>nueva presentación 😳!</t>
+          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>45925.20309027778</v>
+        <v>45950.08873842593</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>45925</v>
+        <v>45950</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>04:52:27</t>
+          <t>02:07:47</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553885128557478672', 'createTime': 1758775947, 'createTimeISO': '2025-09-25T04:52:27.000Z', 'text': 'nueva presentación 😳!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1520e198&amp;x-expires=1761483600&amp;x-signature=RG02BJPXU1NVHYy8yhGN%2FMY2fJo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7563119838848598792', 'createTime': 1760926067, 'createTimeISO': '2025-10-20T02:07:47.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ef9ccaf3&amp;x-expires=1761570000&amp;x-signature=OsrEaDn9tPollUWncoSd9dptQY0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7753,22 +7753,22 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀</t>
+          <t>Gran historia jajajaja 🥳</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>45926.65694444445</v>
+        <v>45925.03746527778</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>45926</v>
+        <v>45925</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>15:46:00</t>
+          <t>00:53:57</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554424648151941905', 'createTime': 1758901560, 'createTimeISO': '2025-09-26T15:46:00.000Z', 'text': 'Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7436539205088396344', 'uniqueId': 'isaac_mora1903', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bd074fbf9f61ee99fcea8ef5f350b2bf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=98a5820a&amp;x-expires=1761483600&amp;x-signature=nzWMXbJUO3s8%2FPPGB2PTgcvfGCs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553823647435178770', 'createTime': 1758761637, 'createTimeISO': '2025-09-25T00:53:57.000Z', 'text': 'Gran historia jajajaja 🥳', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fca43208&amp;x-expires=1761570000&amp;x-signature=7PCAh1YNOe1EBw2Jm7BcvnE8Ep8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7809,25 +7809,25 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Yo abría amado que mis prácticas hubiesen sido en alpina ☹</t>
+          <t>Es cierto que debajo de la cabaña hay un tunel secreto?👀</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>45925.04715277778</v>
+        <v>45925.02155092593</v>
       </c>
       <c r="H132" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>01:07:54</t>
+          <t>00:31:02</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553827220982170386', 'createTime': 1758762474, 'createTimeISO': '2025-09-25T01:07:54.000Z', 'text': 'Yo abría amado que mis prácticas hubiesen sido en alpina ☹', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6760311129178735621', 'uniqueId': 'dosydosdoss', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4de63d002c8153b317e435b8b677488d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ed15fb36&amp;x-expires=1761483600&amp;x-signature=wmkBEKMbSI23n1o6VwgHW0kxgZg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553817757574349576', 'createTime': 1758760262, 'createTimeISO': '2025-09-25T00:31:02.000Z', 'text': 'Es cierto que debajo de la cabaña hay un tunel secreto?👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd083daf&amp;x-expires=1761570000&amp;x-signature=Mj60V9kePw%2BGmIXKCvNAf2iQtmM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7865,18 +7865,18 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>cuando llegan a Perú los Mochis 😭😭</t>
+          <t>Alpinaa salúdame</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>45927.6415625</v>
+        <v>45932.13111111111</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>45927</v>
+        <v>45932</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>15:23:51</t>
+          <t>03:08:48</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554790021015946005', 'createTime': 1758986631, 'createTimeISO': '2025-09-27T15:23:51.000Z', 'text': 'cuando llegan a Perú los Mochis 😭😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7093344759511532549', 'uniqueId': 'hanzel3075', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e5fc427c21f18dd65a5d6366a919b2b8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d5cada30&amp;x-expires=1761483600&amp;x-signature=8QbBZY91pDeDoR3OlQLOzI%2BejGc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556456003958588178', 'createTime': 1759374528, 'createTimeISO': '2025-10-02T03:08:48.000Z', 'text': 'Alpinaa salúdame', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6783863549585867782', 'uniqueId': 'ciro_492', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a1c71fe90e3afc45b76f3656558f0dae~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b33d7553&amp;x-expires=1761570000&amp;x-signature=T0EUIOuepjnuVcpBiTRnhuwW6H4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7921,25 +7921,25 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰</t>
+          <t>una pregunta las personas del Sena pueden estar en Alpina</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>45931.09893518518</v>
+        <v>45925.33574074074</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>45931</v>
+        <v>45925</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>02:22:28</t>
+          <t>08:03:28</t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556072986438107912', 'createTime': 1759285348, 'createTimeISO': '2025-10-01T02:22:28.000Z', 'text': 'alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7555531729910694930', 'uniqueId': 'danna.isabella.sa2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1352ee914eff9ecaa92c418ab22e747d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fdf7bea5&amp;x-expires=1761483600&amp;x-signature=F4QeCpg4LpoorGfh%2BC6yPogqpfI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553933847436772104', 'createTime': 1758787408, 'createTimeISO': '2025-09-25T08:03:28.000Z', 'text': 'una pregunta las personas del Sena pueden estar en Alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7378542037979644933', 'uniqueId': 'cristian.a_l', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a8d4f24a10c3ff1073ab57bc08de8478~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7159a7de&amp;x-expires=1761570000&amp;x-signature=wqabBR1lISnNHezi1Gig9y7CpVY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7977,18 +7977,18 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alpinaa salúdame</t>
+          <t>Porque es la mejor ❤️❤️✨✨</t>
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>45932.13111111111</v>
+        <v>45925.67758101852</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>03:08:48</t>
+          <t>16:15:43</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556456003958588178', 'createTime': 1759374528, 'createTimeISO': '2025-10-02T03:08:48.000Z', 'text': 'Alpinaa salúdame', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6783863549585867782', 'uniqueId': 'ciro_492', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a1c71fe90e3afc45b76f3656558f0dae~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=dd2df0af&amp;x-expires=1761483600&amp;x-signature=yOEjLyox0JR6j9sFWcNLbdAkdjE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554061217602994962', 'createTime': 1758816943, 'createTimeISO': '2025-09-25T16:15:43.000Z', 'text': 'Porque es la mejor ❤️❤️✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532067139480715266', 'uniqueId': 'irodriguez9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/8934653b245a2db9d7ce7c5499232dd9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1c7908a2&amp;x-expires=1761570000&amp;x-signature=PgtiBbYIA3T8P4D755TXjRkgnEo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8033,25 +8033,25 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>una pregunta las personas del Sena pueden estar en Alpina</t>
+          <t>Mi sueñoooo 😩 ya quiero hacer parte de ustedes</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>45925.33574074074</v>
+        <v>45925.08212962963</v>
       </c>
       <c r="H136" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>08:03:28</t>
+          <t>01:58:16</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553933847436772104', 'createTime': 1758787408, 'createTimeISO': '2025-09-25T08:03:28.000Z', 'text': 'una pregunta las personas del Sena pueden estar en Alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7378542037979644933', 'uniqueId': 'cristian.a_l', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a8d4f24a10c3ff1073ab57bc08de8478~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3b340825&amp;x-expires=1761483600&amp;x-signature=ODdNuZfDNgkKF%2F9LbVFYrH8WV%2F0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553840238716945153', 'createTime': 1758765496, 'createTimeISO': '2025-09-25T01:58:16.000Z', 'text': 'Mi sueñoooo 😩 ya quiero hacer parte de ustedes', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f5aece25&amp;x-expires=1761570000&amp;x-signature=Zl4tz07p0ieZ8Pxe8VY0POWecRU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8089,18 +8089,18 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Porque es la mejor ❤️❤️✨✨</t>
+          <t>alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>45925.67758101852</v>
+        <v>45931.09893518518</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>16:15:43</t>
+          <t>02:22:28</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554061217602994962', 'createTime': 1758816943, 'createTimeISO': '2025-09-25T16:15:43.000Z', 'text': 'Porque es la mejor ❤️❤️✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532067139480715266', 'uniqueId': 'irodriguez9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/8934653b245a2db9d7ce7c5499232dd9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c81620ee&amp;x-expires=1761483600&amp;x-signature=mM2pOjsgcpqnZxGuPFzfDpgQKnI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556072986438107912', 'createTime': 1759285348, 'createTimeISO': '2025-10-01T02:22:28.000Z', 'text': 'alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7555531729910694930', 'uniqueId': 'danna.isabella.sa2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1352ee914eff9ecaa92c418ab22e747d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0c6ced0f&amp;x-expires=1761570000&amp;x-signature=zGMrwfTOMgFXssAuJvBqGWK2QG0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8145,25 +8145,25 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos</t>
+          <t>Yo abría amado que mis prácticas hubiesen sido en alpina ☹</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>45925.06542824074</v>
+        <v>45925.04715277778</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>01:34:13</t>
+          <t>01:07:54</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553834039527654152', 'createTime': 1758764053, 'createTimeISO': '2025-09-25T01:34:13.000Z', 'text': 'Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=15bfe409&amp;x-expires=1761483600&amp;x-signature=tlByJ57%2FCKu5oetmdYI%2BGWFPItA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553827220982170386', 'createTime': 1758762474, 'createTimeISO': '2025-09-25T01:07:54.000Z', 'text': 'Yo abría amado que mis prácticas hubiesen sido en alpina ☹', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6760311129178735621', 'uniqueId': 'dosydosdoss', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4de63d002c8153b317e435b8b677488d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d59a1dfc&amp;x-expires=1761570000&amp;x-signature=q9rWx7axMTIURf0YNqcn166XfVY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8201,25 +8201,25 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Es cierto que debajo de la cabaña hay un tunel secreto?👀</t>
+          <t>Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>45925.02155092593</v>
+        <v>45926.77142361111</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>00:31:02</t>
+          <t>18:30:51</t>
         </is>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553817757574349576', 'createTime': 1758760262, 'createTimeISO': '2025-09-25T00:31:02.000Z', 'text': 'Es cierto que debajo de la cabaña hay un tunel secreto?👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4d60aecf&amp;x-expires=1761483600&amp;x-signature=JlQRda01a1IFfhz6peVy%2BwrkX8M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554467116628640530', 'createTime': 1758911451, 'createTimeISO': '2025-09-26T18:30:51.000Z', 'text': 'Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6865051063218439169', 'uniqueId': 'soy_sebass07', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d3ac239ee21a619bba014942d5f7587e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=320e058d&amp;x-expires=1761570000&amp;x-signature=4r4OJsv3y%2BoRBDGChYJ34QIZ1S8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8257,18 +8257,18 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Y los gatos de alpin?👀</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>45926.9503587963</v>
+        <v>45925.02996527778</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>45926</v>
+        <v>45925</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>22:48:31</t>
+          <t>00:43:09</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554533498993148680', 'createTime': 1758926911, 'createTimeISO': '2025-09-26T22:48:31.000Z', 'text': 'Y los gatos de alpin?👀', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7414647256178230277', 'uniqueId': 'acetaminofenxd', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/94659e73261c442ff86af031e43a41f6~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fef235c8&amp;x-expires=1761483600&amp;x-signature=uhi9LglA79EzCdantGsYTMn8560%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553820808625439495', 'createTime': 1758760989, 'createTimeISO': '2025-09-25T00:43:09.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e0aba58&amp;x-expires=1761570000&amp;x-signature=OWekD83TiJfQ2m%2B3WwuiT6Ts%2BXI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8313,18 +8313,18 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn</t>
+          <t>🥰</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>45926.77142361111</v>
+        <v>45940.88704861111</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>45926</v>
+        <v>45940</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>18:30:51</t>
+          <t>21:17:21</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554467116628640530', 'createTime': 1758911451, 'createTimeISO': '2025-09-26T18:30:51.000Z', 'text': 'Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6865051063218439169', 'uniqueId': 'soy_sebass07', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d3ac239ee21a619bba014942d5f7587e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=200b2147&amp;x-expires=1761483600&amp;x-signature=HAt5BQpzNaCz0kX9mijn3NmMxL0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7559705187091956488', 'createTime': 1760131041, 'createTimeISO': '2025-10-10T21:17:21.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7464357929971483649', 'uniqueId': 'aquiles.indriagol', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/72a6938f97ba8c0e50728d4cd7d182b4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ea36d42d&amp;x-expires=1761570000&amp;x-signature=Ikg3yxNbVWc%2FGZzzE%2B8OF1evxb4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8369,26 +8369,26 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>45925.02996527778</v>
+        <v>45928.8690625</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>45925</v>
+        <v>45928</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>00:43:09</t>
+          <t>20:51:27</t>
         </is>
       </c>
       <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
         <v>1</v>
       </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
       <c r="L142" t="b">
         <v>0</v>
       </c>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553820808625439495', 'createTime': 1758760989, 'createTimeISO': '2025-09-25T00:43:09.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9172a8a8&amp;x-expires=1761483600&amp;x-signature=DEY%2F%2FqVuciP0lvggwKT4xDxwhwE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7555245460417331986', 'createTime': 1759092687, 'createTimeISO': '2025-09-28T20:51:27.000Z', 'text': 'Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7400852594988827654', 'uniqueId': 'whoisandres37', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/317c580e71debf147810b74b93171a6f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=14873671&amp;x-expires=1761570000&amp;x-signature=YsHXSH3NXmW%2BGPL0pdt7k4feCgo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8425,18 +8425,18 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>🥰</t>
+          <t>Hola! Una pregunta ¿es normal qué los minis ilumimochis de conejito verde venga de a 2?</t>
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>45940.88704861111</v>
+        <v>45925.04067129629</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>45940</v>
+        <v>45925</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>21:17:21</t>
+          <t>00:58:34</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7559705187091956488', 'createTime': 1760131041, 'createTimeISO': '2025-10-10T21:17:21.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7464357929971483649', 'uniqueId': 'aquiles.indriagol', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/72a6938f97ba8c0e50728d4cd7d182b4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b0889dd&amp;x-expires=1761483600&amp;x-signature=Ra%2BUKNocHXp50hn63uTGDhvqXdk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553824837010965266', 'createTime': 1758761914, 'createTimeISO': '2025-09-25T00:58:34.000Z', 'text': 'Hola! Una pregunta ¿es normal qué los minis ilumimochis de conejito verde venga de a 2?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7482894692960535570', 'uniqueId': 'eldiploo29', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e71b97d2782d93b9a10a9adec8349876~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2a9b7310&amp;x-expires=1761570000&amp;x-signature=G%2FTR38Knn0ZU6MkRvyF5f9mD8D4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8481,25 +8481,25 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?</t>
+          <t>También reciben pasantes?</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>45928.8690625</v>
+        <v>45954.7812962963</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>45928</v>
+        <v>45954</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>20:51:27</t>
+          <t>18:45:04</t>
         </is>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -8511,13 +8511,13 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7555245460417331986', 'createTime': 1759092687, 'createTimeISO': '2025-09-28T20:51:27.000Z', 'text': 'Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7400852594988827654', 'uniqueId': 'whoisandres37', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/317c580e71debf147810b74b93171a6f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=26608a0c&amp;x-expires=1761483600&amp;x-signature=oxjpWQraFL8yPJfX0o3ZnOgGtc4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7564861171879445256', 'createTime': 1761331504, 'createTimeISO': '2025-10-24T18:45:04.000Z', 'text': 'También reciben pasantes?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '166386831993888768', 'uniqueId': 'aleja040610', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/d38de0738e43e8e0ce00becaad0aca08~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d47e22b8&amp;x-expires=1761570000&amp;x-signature=V1kMHyMoc%2FS71CbJ4A3J%2BK3qhfM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -8531,31 +8531,31 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@alpinacol/video/7553815390661463308?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7530638001644029446</t>
+          <t>https://www.tiktok.com/@alpinacol/video/7554549968778825016?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7530638001644029446</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hola! Una pregunta ¿es normal qué los minis ilumimochis de conejito verde venga de a 2?</t>
+          <t>nuevas familias 😳</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>45925.04067129629</v>
+        <v>45927.005</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>45925</v>
+        <v>45927</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>00:58:34</t>
+          <t>00:07:12</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553824837010965266', 'createTime': 1758761914, 'createTimeISO': '2025-09-25T00:58:34.000Z', 'text': 'Hola! Una pregunta ¿es normal qué los minis ilumimochis de conejito verde venga de a 2?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7482894692960535570', 'uniqueId': 'eldiploo29', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e71b97d2782d93b9a10a9adec8349876~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c8d39b55&amp;x-expires=1761483600&amp;x-signature=YUdNqV6n3ka2q%2BQlJK4qMdOMhuo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554553739177624336', 'createTime': 1758931632, 'createTimeISO': '2025-09-27T00:07:12.000Z', 'text': 'nuevas familias 😳', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8593,22 +8593,22 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]</t>
+          <t>Yo quiero arequipe vegano 🥺</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>45927.49298611111</v>
+        <v>45933.83266203704</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>45927</v>
+        <v>45933</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>11:49:54</t>
+          <t>19:59:02</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554734892081922823', 'createTime': 1758973794, 'createTimeISO': '2025-09-27T11:49:54.000Z', 'text': 'alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f60ce9d4&amp;x-expires=1761483600&amp;x-signature=0JDXyALIaJRHS3r4xtJehL7HhNo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557087381695890193', 'createTime': 1759521542, 'createTimeISO': '2025-10-03T19:59:02.000Z', 'text': 'Yo quiero arequipe vegano 🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6903626505060189189', 'uniqueId': 'mafeocampor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bc55178240ac3f97ce30d333a28a48a5~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d462a6b&amp;x-expires=1761570000&amp;x-signature=Ak5pAkGU0ZjGAHxG96227ZG1gfk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8649,25 +8649,25 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>primerooo alpina me regalas mochisauros porfiss</t>
+          <t>Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>45926.99771990741</v>
+        <v>45927.79994212963</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>23:56:43</t>
+          <t>19:11:55</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554551041196770066', 'createTime': 1758931003, 'createTimeISO': '2025-09-26T23:56:43.000Z', 'text': 'primerooo alpina me regalas mochisauros porfiss', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7547457761526137864', 'uniqueId': 'camisetas.de.futbol1', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c21b0befe49f100b71b7cf8f2e5652~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d8a1371d&amp;x-expires=1761483600&amp;x-signature=V8DCJYKIkbuQRVeMfqV0RqQrNb4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554848766027121426', 'createTime': 1759000315, 'createTimeISO': '2025-09-27T19:11:55.000Z', 'text': 'Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7505793601163674642', 'uniqueId': 'mariangel6169', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/399d2e2b90810396c3ec41de01efcf36~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9e7357b6&amp;x-expires=1761570000&amp;x-signature=UbhgXrLXav1UzsuZGYolGcpnjXk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8705,25 +8705,25 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Yo quiero arequipe vegano 🥺</t>
+          <t>sube otro video de mochiiss</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>45933.83266203704</v>
+        <v>45927.45836805556</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>45933</v>
+        <v>45927</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>19:59:02</t>
+          <t>11:00:03</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557087381695890193', 'createTime': 1759521542, 'createTimeISO': '2025-10-03T19:59:02.000Z', 'text': 'Yo quiero arequipe vegano 🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6903626505060189189', 'uniqueId': 'mafeocampor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bc55178240ac3f97ce30d333a28a48a5~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=08047a0d&amp;x-expires=1761483600&amp;x-signature=CrcvgT7MOa7wti1OHvqPqV9628I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554722020870521616', 'createTime': 1758970803, 'createTimeISO': '2025-09-27T11:00:03.000Z', 'text': 'sube otro video de mochiiss', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7405734042824066054', 'uniqueId': 'emmanuel130816', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a09b533779b756050279fc4f4ba0f5fc~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c913eb86&amp;x-expires=1761570000&amp;x-signature=yA1CMIOzFpoKIegA0bO9srRe1vU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8761,22 +8761,22 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>que paso con los gatos de alpin?</t>
+          <t>¿alpina que paso con los gatos del alpin?</t>
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>45930.19638888889</v>
+        <v>45927.02045138889</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>45930</v>
+        <v>45927</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>04:42:48</t>
+          <t>00:29:27</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555738077466821394', 'createTime': 1759207368, 'createTimeISO': '2025-09-30T04:42:48.000Z', 'text': 'que paso con los gatos de alpin?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6926927885060621317', 'uniqueId': 'josep3473', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7d60822ca9bd29b9cf211e0122ccbfab~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5e602e55&amp;x-expires=1761483600&amp;x-signature=ytI%2F%2BQZaNY27HuwrCJj51rIMpHw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559487220663058', 'createTime': 1758932967, 'createTimeISO': '2025-09-27T00:29:27.000Z', 'text': '¿alpina que paso con los gatos del alpin?', 'diggCount': 9, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7384592401019339781', 'uniqueId': 'el.pepe.joel', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/340ccdf36a548c49ba15c1f1d4f94a5a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f867dfc9&amp;x-expires=1761570000&amp;x-signature=dnRCz5B%2BexCzEGGyn6oxVX7iRb4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8817,25 +8817,25 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>sube otro video de mochiiss</t>
+          <t>Alpinaaaa esos gatos son mi infancia porfavor regresalos</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>45927.45836805556</v>
+        <v>45930.58837962963</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>45927</v>
+        <v>45930</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>11:00:03</t>
+          <t>14:07:16</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554722020870521616', 'createTime': 1758970803, 'createTimeISO': '2025-09-27T11:00:03.000Z', 'text': 'sube otro video de mochiiss', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7405734042824066054', 'uniqueId': 'emmanuel130816', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a09b533779b756050279fc4f4ba0f5fc~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=04512429&amp;x-expires=1761483600&amp;x-signature=pFLVJToOMlNzFZADY4Yo0YJ9SN0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555883548419932948', 'createTime': 1759241236, 'createTimeISO': '2025-09-30T14:07:16.000Z', 'text': 'Alpinaaaa esos gatos son mi infancia porfavor regresalos', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7259921363220792325', 'uniqueId': 'migue_resurgido', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6cea1ed6c965c8a6b67e0007f15f789~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=efd66891&amp;x-expires=1761570000&amp;x-signature=EEH3quWaq%2FyTOTPH9JpiJ9zP3C0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8873,22 +8873,22 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Alpinaaaa esos gatos son mi infancia porfavor regresalos</t>
+          <t>ya se me antojo un yogo yogo mochisaurios</t>
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>45930.58837962963</v>
+        <v>45927.02165509259</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>45930</v>
+        <v>45927</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>14:07:16</t>
+          <t>00:31:11</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555883548419932948', 'createTime': 1759241236, 'createTimeISO': '2025-09-30T14:07:16.000Z', 'text': 'Alpinaaaa esos gatos son mi infancia porfavor regresalos', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7259921363220792325', 'uniqueId': 'migue_resurgido', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6cea1ed6c965c8a6b67e0007f15f789~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cc5498cd&amp;x-expires=1761483600&amp;x-signature=NqwyLIu%2BJJnAmslzaRd0st1qKOg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559943006864136', 'createTime': 1758933071, 'createTimeISO': '2025-09-27T00:31:11.000Z', 'text': 'ya se me antojo un yogo yogo mochisaurios', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=26a7ae26&amp;x-expires=1761570000&amp;x-signature=z4Cc6Vhls%2BKFDO7%2FuIUSOXTFj7k%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8929,22 +8929,22 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>¿alpina que paso con los gatos del alpin?</t>
+          <t>que paso con los gatos de alpin?</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>45927.02045138889</v>
+        <v>45930.19638888889</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>45927</v>
+        <v>45930</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>00:29:27</t>
+          <t>04:42:48</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559487220663058', 'createTime': 1758932967, 'createTimeISO': '2025-09-27T00:29:27.000Z', 'text': '¿alpina que paso con los gatos del alpin?', 'diggCount': 9, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7384592401019339781', 'uniqueId': 'el.pepe.joel', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/340ccdf36a548c49ba15c1f1d4f94a5a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d445cffe&amp;x-expires=1761483600&amp;x-signature=9uLOBfLO668NT%2F%2FjdMAcK6POD%2BQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555738077466821394', 'createTime': 1759207368, 'createTimeISO': '2025-09-30T04:42:48.000Z', 'text': 'que paso con los gatos de alpin?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6926927885060621317', 'uniqueId': 'josep3473', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7d60822ca9bd29b9cf211e0122ccbfab~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=46acee8e&amp;x-expires=1761570000&amp;x-signature=mPAHGmNfNErVq3tok39wkw3iqr0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ya se me antojo un yogo yogo mochisaurios</t>
+          <t>primerooo alpina me regalas mochisauros porfiss</t>
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>45927.02165509259</v>
+        <v>45926.99771990741</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>45927</v>
+        <v>45926</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>00:31:11</t>
+          <t>23:56:43</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559943006864136', 'createTime': 1758933071, 'createTimeISO': '2025-09-27T00:31:11.000Z', 'text': 'ya se me antojo un yogo yogo mochisaurios', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6bfac2db&amp;x-expires=1761483600&amp;x-signature=1X08XRVToySKmYLjFbKGNbE08KI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554551041196770066', 'createTime': 1758931003, 'createTimeISO': '2025-09-26T23:56:43.000Z', 'text': 'primerooo alpina me regalas mochisauros porfiss', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7547457761526137864', 'uniqueId': 'camisetas.de.futbol1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c21b0befe49f100b71b7cf8f2e5652~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2d0ee85e&amp;x-expires=1761570000&amp;x-signature=SUpWNO3D%2BEqKqnlOoZu2JNOzPjQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7556439567764472596', 'createTime': 1759370704, 'createTimeISO': '2025-10-02T02:05:04.000Z', 'text': 'sería super interesante que grabarán un vídeo de cómo alguien se convierte en un maestro quesero (soy fan del queso)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6809345648602350598', 'uniqueId': 'ginapaolae.j', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326882581663334405~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=442a6e1e&amp;x-expires=1761483600&amp;x-signature=BcL6emy0DTeLDuyAoopDtXEPpsw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7556439567764472596', 'createTime': 1759370704, 'createTimeISO': '2025-10-02T02:05:04.000Z', 'text': 'sería super interesante que grabarán un vídeo de cómo alguien se convierte en un maestro quesero (soy fan del queso)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6809345648602350598', 'uniqueId': 'ginapaolae.j', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326882581663334405~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ae038b89&amp;x-expires=1761570000&amp;x-signature=6tJOHSa8hh9zBvuP9WNHGm9ASUQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9097,26 +9097,26 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏</t>
+          <t>Que tarea esa endulzada 😳🥰 la mejor 😇💖</t>
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>45927.79994212963</v>
+        <v>45927.43773148148</v>
       </c>
       <c r="H155" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>19:11:55</t>
+          <t>10:30:20</t>
         </is>
       </c>
       <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
         <v>1</v>
       </c>
-      <c r="K155" t="n">
-        <v>2</v>
-      </c>
       <c r="L155" t="b">
         <v>0</v>
       </c>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554848766027121426', 'createTime': 1759000315, 'createTimeISO': '2025-09-27T19:11:55.000Z', 'text': 'Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7505793601163674642', 'uniqueId': 'mariangel6169', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/399d2e2b90810396c3ec41de01efcf36~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=13393ffc&amp;x-expires=1761483600&amp;x-signature=uDTz%2BZGxslLVfDuOhI2lrzGudKs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554714387131745031', 'createTime': 1758969020, 'createTimeISO': '2025-09-27T10:30:20.000Z', 'text': 'Que tarea esa endulzada 😳🥰 la mejor 😇💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9153,25 +9153,25 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Que tarea esa endulzada 😳🥰 la mejor 😇💖</t>
+          <t>Alpinaaaaa xq quitaste los gatooooooos</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>45927.43773148148</v>
+        <v>45927.06792824074</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>10:30:20</t>
+          <t>01:37:49</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554714387131745031', 'createTime': 1758969020, 'createTimeISO': '2025-09-27T10:30:20.000Z', 'text': 'Que tarea esa endulzada 😳🥰 la mejor 😇💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0efc43a6&amp;x-expires=1761483600&amp;x-signature=%2FlzlYaBNjstaHyyaUdQHSXP8y2U%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554577111799137025', 'createTime': 1758937069, 'createTimeISO': '2025-09-27T01:37:49.000Z', 'text': 'Alpinaaaaa xq quitaste los gatooooooos', 'diggCount': 11, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7414238685522199557', 'uniqueId': 'vxshly_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6f809c16c6632fac081af1ffdcb6d9f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2a61e4f3&amp;x-expires=1761570000&amp;x-signature=pQYt%2F3FRv8TT%2BOeVmegojy%2F4o5I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9209,25 +9209,25 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Alpinaaaaa xq quitaste los gatooooooos</t>
+          <t>alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>45927.06792824074</v>
+        <v>45927.49298611111</v>
       </c>
       <c r="H157" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>01:37:49</t>
+          <t>11:49:54</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554577111799137025', 'createTime': 1758937069, 'createTimeISO': '2025-09-27T01:37:49.000Z', 'text': 'Alpinaaaaa xq quitaste los gatooooooos', 'diggCount': 11, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7414238685522199557', 'uniqueId': 'vxshly_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6f809c16c6632fac081af1ffdcb6d9f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b9fc1b28&amp;x-expires=1761483600&amp;x-signature=VWtHxqAbYuYmWCbJ1SXXpHiRpM4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554734892081922823', 'createTime': 1758973794, 'createTimeISO': '2025-09-27T11:49:54.000Z', 'text': 'alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9265,25 +9265,25 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>nuevas familias 😳</t>
+          <t>😊😊😊</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>45927.005</v>
+        <v>45927.0005787037</v>
       </c>
       <c r="H158" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>00:07:12</t>
+          <t>00:00:50</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554553739177624336', 'createTime': 1758931632, 'createTimeISO': '2025-09-27T00:07:12.000Z', 'text': 'nuevas familias 😳', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1520e198&amp;x-expires=1761483600&amp;x-signature=RG02BJPXU1NVHYy8yhGN%2FMY2fJo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554552119991829255', 'createTime': 1758931250, 'createTimeISO': '2025-09-27T00:00:50.000Z', 'text': '😊😊😊', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7263510507210245125', 'uniqueId': 'anyela1p', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/388bda02c957db9a4a0d8b463d9fb749~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7eb01a6e&amp;x-expires=1761570000&amp;x-signature=x8oLK3IZ5b5tP1OLK3No3feeDw8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9321,18 +9321,18 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>😊😊😊</t>
+          <t>🔝</t>
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>45927.0005787037</v>
+        <v>45927.01375</v>
       </c>
       <c r="H159" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>00:00:50</t>
+          <t>00:19:48</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554552119991829255', 'createTime': 1758931250, 'createTimeISO': '2025-09-27T00:00:50.000Z', 'text': '😊😊😊', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7263510507210245125', 'uniqueId': 'anyela1p', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/388bda02c957db9a4a0d8b463d9fb749~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5fc8be4b&amp;x-expires=1761483600&amp;x-signature=1K8bHx4ZosD%2F6UN5jy4Olx2ySG0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554556989701325580', 'createTime': 1758932388, 'createTimeISO': '2025-09-27T00:19:48.000Z', 'text': '🔝', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9318afca&amp;x-expires=1761570000&amp;x-signature=vuOKTe6NBdJzzn2l%2FGqo1IGgWyM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9377,22 +9377,22 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>🔝</t>
+          <t>❤</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>45927.01375</v>
+        <v>45946.82291666666</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>45927</v>
+        <v>45946</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>00:19:48</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554556989701325580', 'createTime': 1758932388, 'createTimeISO': '2025-09-27T00:19:48.000Z', 'text': '🔝', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f51c2dd0&amp;x-expires=1761483600&amp;x-signature=M4UFlJeqIvSMC8UCj5C0QEpYpgY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907924650574600', 'createTime': 1760643900, 'createTimeISO': '2025-10-16T19:45:00.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9433,18 +9433,18 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>❤</t>
+          <t>♥</t>
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>45946.82291666666</v>
+        <v>45946.82292824074</v>
       </c>
       <c r="H161" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:45:01</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907924650574600', 'createTime': 1760643900, 'createTimeISO': '2025-10-16T19:45:00.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=78b6cd6f&amp;x-expires=1761483600&amp;x-signature=71%2FfCkBhBPw0zmYrFKlCP4BjGFU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907918385365768', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>💚</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907918385365768', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=78b6cd6f&amp;x-expires=1761483600&amp;x-signature=71%2FfCkBhBPw0zmYrFKlCP4BjGFU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907925900821255', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '💚', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9545,18 +9545,18 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>💚</t>
+          <t>♥</t>
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>45946.82292824074</v>
+        <v>45946.82295138889</v>
       </c>
       <c r="H163" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>19:45:01</t>
+          <t>19:45:03</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907925900821255', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '💚', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=78b6cd6f&amp;x-expires=1761483600&amp;x-signature=71%2FfCkBhBPw0zmYrFKlCP4BjGFU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907930460537607', 'createTime': 1760643903, 'createTimeISO': '2025-10-16T19:45:03.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9605,14 +9605,14 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>45946.82295138889</v>
+        <v>45946.82293981482</v>
       </c>
       <c r="H164" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>19:45:03</t>
+          <t>19:45:02</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907930460537607', 'createTime': 1760643903, 'createTimeISO': '2025-10-16T19:45:03.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=78b6cd6f&amp;x-expires=1761483600&amp;x-signature=71%2FfCkBhBPw0zmYrFKlCP4BjGFU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907909032067847', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9657,18 +9657,18 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>@Alpina 🐮 hola necesito un favor suyo 🙏</t>
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>45946.82293981482</v>
+        <v>45930.75880787037</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>45946</v>
+        <v>45930</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>19:45:02</t>
+          <t>18:12:41</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907909032067847', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=78b6cd6f&amp;x-expires=1761483600&amp;x-signature=71%2FfCkBhBPw0zmYrFKlCP4BjGFU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555946787841164050', 'createTime': 1759255961, 'createTimeISO': '2025-09-30T18:12:41.000Z', 'text': '@Alpina 🐮 hola necesito un favor suyo 🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7314724628953121797', 'uniqueId': 'jan.cityzens', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5d6f3dd82f6da2bcac787ef22cb28684~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=47273fa9&amp;x-expires=1761570000&amp;x-signature=I8ubyIepd0u8GeVYs5Iw0rhYNiw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -9713,18 +9713,18 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>@Alpina 🐮 hola necesito un favor suyo 🙏</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>45930.75880787037</v>
+        <v>45951.07341435185</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>45930</v>
+        <v>45951</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>18:12:41</t>
+          <t>01:45:43</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555946787841164050', 'createTime': 1759255961, 'createTimeISO': '2025-09-30T18:12:41.000Z', 'text': '@Alpina 🐮 hola necesito un favor suyo 🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7314724628953121797', 'uniqueId': 'jan.cityzens', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5d6f3dd82f6da2bcac787ef22cb28684~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b7cd0ac6&amp;x-expires=1761483600&amp;x-signature=EHhu201Er8l2FJ455XXIOCWh2RU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7563485230247002888', 'createTime': 1761011143, 'createTimeISO': '2025-10-21T01:45:43.000Z', 'text': '💙💙💙', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6851669436614001669', 'uniqueId': 'villamil2.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/39e44d37d75d07c80dfacb9dc52dc087~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5aab5636&amp;x-expires=1761570000&amp;x-signature=TvjECkAg%2F6m9KcviqnxjNUleMQc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9769,18 +9769,18 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>❤</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>45951.07341435185</v>
+        <v>45946.82293981482</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>45951</v>
+        <v>45946</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>01:45:43</t>
+          <t>19:45:02</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7563485230247002888', 'createTime': 1761011143, 'createTimeISO': '2025-10-21T01:45:43.000Z', 'text': '💙💙💙', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6851669436614001669', 'uniqueId': 'villamil2.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/39e44d37d75d07c80dfacb9dc52dc087~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=24d23e2d&amp;x-expires=1761483600&amp;x-signature=Qy1O0YEsIrJz5aE47juhwlsJK5Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907940182098696', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9825,18 +9825,18 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>❤</t>
+          <t>mochisssssss</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>45946.82293981482</v>
+        <v>45934.81753472222</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>45946</v>
+        <v>45934</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>19:45:02</t>
+          <t>19:37:15</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907940182098696', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=78b6cd6f&amp;x-expires=1761483600&amp;x-signature=71%2FfCkBhBPw0zmYrFKlCP4BjGFU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557452880204202770', 'createTime': 1759606635, 'createTimeISO': '2025-10-04T19:37:15.000Z', 'text': 'mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7329726761418753029', 'uniqueId': 'pipi.potato35', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0d01dfa969f5266b98420f02248fc885~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a266c36d&amp;x-expires=1761570000&amp;x-signature=meB0uyufeqrY%2BBKDTZro%2B4foDps%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9881,18 +9881,18 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>mochisssssss</t>
+          <t>aquí esperando el video donde hablen de los gatos de alpin</t>
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>45934.81753472222</v>
+        <v>45941.26355324074</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>45934</v>
+        <v>45941</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>19:37:15</t>
+          <t>06:19:31</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9911,63 +9911,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557452880204202770', 'createTime': 1759606635, 'createTimeISO': '2025-10-04T19:37:15.000Z', 'text': 'mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7329726761418753029', 'uniqueId': 'pipi.potato35', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0d01dfa969f5266b98420f02248fc885~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2fbb88f2&amp;x-expires=1761483600&amp;x-signature=%2Bnacii%2BB%2B1wUqPSOKFiE8Vc%2BbJU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>8</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>CAMPAÑA_MANUAL_MULTIPLE</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@alpinacol/video/7554549968778825016?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7530638001644029446</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>aquí esperando el video donde hablen de los gatos de alpin</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>45941.26355324074</v>
-      </c>
-      <c r="H170" s="3" t="n">
-        <v>45941</v>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>06:19:31</t>
-        </is>
-      </c>
-      <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" t="b">
-        <v>0</v>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7559844927899992849', 'createTime': 1760163571, 'createTimeISO': '2025-10-11T06:19:31.000Z', 'text': 'aquí esperando el video donde hablen de los gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7001651876342055942', 'uniqueId': 'm1mundo_lu', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/1f167436074f22f5e92f6246fd53543d~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=a5f189f4&amp;x-expires=1761483600&amp;x-signature=ZvtAVRIGTwOMuTt3xAM7ZCSN0Gw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7559844927899992849', 'createTime': 1760163571, 'createTimeISO': '2025-10-11T06:19:31.000Z', 'text': 'aquí esperando el video donde hablen de los gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7001651876342055942', 'uniqueId': 'm1mundo_lu', 'avatarThumbnail': 'https://p77-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/1f167436074f22f5e92f6246fd53543d~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=008e230b&amp;x-expires=1761570000&amp;x-signature=gGq55MztIVwVpN%2F4Mbrpg54qYqc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -10153,10 +10097,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -530,25 +530,26 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaquita Kefir plus😊</t>
+          <t>primero
+ya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45902.03216435185</v>
+        <v>45902.01054398148</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>00:46:19</t>
+          <t>00:15:11</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -560,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545286715469792007', 'createTime': 1756773979, 'createTimeISO': '2025-09-02T00:46:19.000Z', 'text': 'Vaquita Kefir plus😊', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd083daf&amp;x-expires=1761570000&amp;x-signature=Mj60V9kePw%2BGmIXKCvNAf2iQtmM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545278675375244050', 'createTime': 1756772111, 'createTimeISO': '2025-09-02T00:15:11.000Z', 'text': 'primero\nya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 10, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=db5b31d7&amp;x-expires=1761656400&amp;x-signature=UsIyB4FPehHYBAKPFSRsk%2BCQg14%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -616,7 +617,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545316874159293192', 'createTime': 1756780990, 'createTimeISO': '2025-09-02T02:43:10.000Z', 'text': 'Mas videos asiiiii🔥🔥🔥🔥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '178030697805189120', 'uniqueId': 'nico5box', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5a97c5c648a6246f815739afc2a4dd5b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=075190a7&amp;x-expires=1761570000&amp;x-signature=t8%2BcsXWO%2FZ%2F53LxND0s9yn0O%2B%2Bo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545316874159293192', 'createTime': 1756780990, 'createTimeISO': '2025-09-02T02:43:10.000Z', 'text': 'Mas videos asiiiii🔥🔥🔥🔥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '178030697805189120', 'uniqueId': 'nico5box', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5a97c5c648a6246f815739afc2a4dd5b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b0fdd54&amp;x-expires=1761656400&amp;x-signature=bchooBmU9ONiva2ZFXf0efzW%2BRM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -642,27 +643,26 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>primero
-ya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?</t>
+          <t>Vaquita Kefir plus😊</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45902.01054398148</v>
+        <v>45902.03216435185</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>45902</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>00:15:11</t>
+          <t>00:46:19</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
@@ -673,7 +673,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545278675375244050', 'createTime': 1756772111, 'createTimeISO': '2025-09-02T00:15:11.000Z', 'text': 'primero\nya casi es octubre que colección de Mochis van a sacar para halloween ✨✨✨?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 10, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c0ba37db&amp;x-expires=1761570000&amp;x-signature=gnODwCkuU4b3Ipg9bhtCBiAGgQI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7545286715469792007', 'createTime': 1756773979, 'createTimeISO': '2025-09-02T00:46:19.000Z', 'text': 'Vaquita Kefir plus😊', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cc1cfaa6&amp;x-expires=1761656400&amp;x-signature=bDJO1qXde90I1OSGYuWdoSIyPAM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7550080571285816082', 'createTime': 1757890141, 'createTimeISO': '2025-09-14T22:49:01.000Z', 'text': '😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7469966561530430471', 'uniqueId': 'juangmgm84i', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7550080571285816082', 'createTime': 1757890141, 'createTimeISO': '2025-09-14T22:49:01.000Z', 'text': '😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7469966561530430471', 'uniqueId': 'juangmgm84i', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e3f426db&amp;x-expires=1761656400&amp;x-signature=CeasMhebqXOzsPfbnJglDatnVK0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7555339654096388871', 'createTime': 1759114604, 'createTimeISO': '2025-09-29T02:56:44.000Z', 'text': 'YO SOY FAN NUMERO UNO DEL KEFIR PLUS DE ALPINA. REALMENTE ES EFECTIVO Y MUY BUENO PARA EL ORGANISMO. Quería escribirles y decirles que el producto es un Hit absoluto. Yo consumo desde hace dos semanas el kefir, y en mi familia ya quedó instalado también 🥰🥰🥰. Y la versión pequeña personal es una maravilla para consumidoras como yo🥰🥰🥰. Bravooooooooooo ALPINA\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6892758040694359046', 'uniqueId': 'yeriname7', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6c41967350ee22b8d1bcb851e47d28c2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=481614f8&amp;x-expires=1761570000&amp;x-signature=aICpTkyW%2FMbRbysAZwPIWDQf58E%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'input': 'https://www.tiktok.com/@alpinacol/video/7545277103156071736', 'cid': '7555339654096388871', 'createTime': 1759114604, 'createTimeISO': '2025-09-29T02:56:44.000Z', 'text': 'YO SOY FAN NUMERO UNO DEL KEFIR PLUS DE ALPINA. REALMENTE ES EFECTIVO Y MUY BUENO PARA EL ORGANISMO. Quería escribirles y decirles que el producto es un Hit absoluto. Yo consumo desde hace dos semanas el kefir, y en mi familia ya quedó instalado también 🥰🥰🥰. Y la versión pequeña personal es una maravilla para consumidoras como yo🥰🥰🥰. Bravooooooooooo ALPINA\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6892758040694359046', 'uniqueId': 'yeriname7', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6c41967350ee22b8d1bcb851e47d28c2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d0e2fa7&amp;x-expires=1761656400&amp;x-signature=vDHddTYPVKQ7aavSXiX8SkOF5l8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547697455086404360', 'createTime': 1757335263, 'createTimeISO': '2025-09-08T12:41:03.000Z', 'text': 'QUEE?? 😭\nYO YA ESTABA EMOCIONADO SI AVISABAN NUEVOS MOCHIS O SUS VIDEOS QUE ME ENTRETIENEN😭😭😭', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547697455086404360', 'createTime': 1757335263, 'createTimeISO': '2025-09-08T12:41:03.000Z', 'text': 'QUEE?? 😭\nYO YA ESTABA EMOCIONADO SI AVISABAN NUEVOS MOCHIS O SUS VIDEOS QUE ME ENTRETIENEN😭😭😭', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5ea43a58&amp;x-expires=1761656400&amp;x-signature=rPrx6BVgpgyzMper2EVumk952gk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -868,18 +868,18 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NOOO ALPINA XQQQ😭</t>
+          <t>Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>45932.70420138889</v>
+        <v>45920.12734953704</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>45932</v>
+        <v>45920</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16:54:03</t>
+          <t>03:03:23</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7556668683994727189', 'createTime': 1759424043, 'createTimeISO': '2025-10-02T16:54:03.000Z', 'text': 'NOOO ALPINA XQQQ😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183010536447411205', 'uniqueId': 'isa._.325', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0b16bfa6acc7f2d7dbac5f5945453e19~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9d6563d5&amp;x-expires=1761570000&amp;x-signature=WAb%2Fnl0sccJbp2EGcQjBqPapAFI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7552001614913356551', 'createTime': 1758337403, 'createTimeISO': '2025-09-20T03:03:23.000Z', 'text': 'Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=42789dbc&amp;x-expires=1761656400&amp;x-signature=8b8IFFJNw55yLpWQQRoM9V4ow%2FA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -924,18 +924,18 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖</t>
+          <t>NOOO ALPINA XQQQ😭</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>45920.12734953704</v>
+        <v>45932.70420138889</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>45920</v>
+        <v>45932</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>03:03:23</t>
+          <t>16:54:03</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7552001614913356551', 'createTime': 1758337403, 'createTimeISO': '2025-09-20T03:03:23.000Z', 'text': 'Gaby alpinita que sucedio, vuelve vuelveeeeeeew💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7556668683994727189', 'createTime': 1759424043, 'createTimeISO': '2025-10-02T16:54:03.000Z', 'text': 'NOOO ALPINA XQQQ😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183010536447411205', 'uniqueId': 'isa._.325', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0b16bfa6acc7f2d7dbac5f5945453e19~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=34f2a05c&amp;x-expires=1761656400&amp;x-signature=0R3%2BGFw4j3CsYMxf8cG6QOtP0Kw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -980,22 +980,22 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qué? 😭</t>
+          <t>porqueeee??😭😭😭😭</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45905.7774074074</v>
+        <v>45907.57980324074</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>45905</v>
+        <v>45907</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18:39:28</t>
+          <t>13:54:55</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546676538382746376', 'createTime': 1757097568, 'createTimeISO': '2025-09-05T18:39:28.000Z', 'text': 'Qué? 😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=81414567&amp;x-expires=1761570000&amp;x-signature=dyvbRhF3TGiyo9zL0%2Fd3%2FE%2FecEc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547344669736600338', 'createTime': 1757253295, 'createTimeISO': '2025-09-07T13:54:55.000Z', 'text': 'porqueeee??😭😭😭😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=587963e7&amp;x-expires=1761656400&amp;x-signature=dfVwFWWSc0K2jxqu1H3SkZ6cvrs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1036,18 +1036,18 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>por Dios ahora que pasó. y yo etiquetando Alpina 😂</t>
+          <t>Queee ?</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45908.64736111111</v>
+        <v>45905.84496527778</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>45908</v>
+        <v>45905</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15:32:12</t>
+          <t>20:16:45</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547741547535500049', 'createTime': 1757345532, 'createTimeISO': '2025-09-08T15:32:12.000Z', 'text': 'por Dios ahora que pasó. y yo etiquetando Alpina 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830280708298343430', 'uniqueId': 'andreifyt2025_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ca95b033b49845a0bbb72152f6a7fb22~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3fbdc049&amp;x-expires=1761570000&amp;x-signature=IvN6tuqtWk1WXMvFzUg6OrTc1rM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546701614498087688', 'createTime': 1757103405, 'createTimeISO': '2025-09-05T20:16:45.000Z', 'text': 'Queee ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ec054728&amp;x-expires=1761656400&amp;x-signature=ghUxHJlb88FrgUHLoM1M1qcuxnQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1092,22 +1092,22 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queee ?</t>
+          <t>volví, haber cuantos meses me fui, que??!!!, 4 meses 😱</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45905.84496527778</v>
+        <v>45909.19028935185</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20:16:45</t>
+          <t>04:34:01</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546701614498087688', 'createTime': 1757103405, 'createTimeISO': '2025-09-05T20:16:45.000Z', 'text': 'Queee ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d4506b40&amp;x-expires=1761570000&amp;x-signature=uRKVTAtDPvXpUDge3YpkAprFqB8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547942977034617601', 'createTime': 1757392441, 'createTimeISO': '2025-09-09T04:34:01.000Z', 'text': 'volví, haber cuantos meses me fui, que??!!!, 4 meses 😱', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=301f1491&amp;x-expires=1761656400&amp;x-signature=2loFdcup%2BQVzSELx143NGhGRyWg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1148,22 +1148,22 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>porqueeee??😭😭😭😭</t>
+          <t>por Dios ahora que pasó. y yo etiquetando Alpina 😂</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>45907.57980324074</v>
+        <v>45908.64736111111</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13:54:55</t>
+          <t>15:32:12</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547344669736600338', 'createTime': 1757253295, 'createTimeISO': '2025-09-07T13:54:55.000Z', 'text': 'porqueeee??😭😭😭😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd681055&amp;x-expires=1761570000&amp;x-signature=wNrNCutAEF%2FapCKk%2F9SDDIPR9A4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547741547535500049', 'createTime': 1757345532, 'createTimeISO': '2025-09-08T15:32:12.000Z', 'text': 'por Dios ahora que pasó. y yo etiquetando Alpina 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830280708298343430', 'uniqueId': 'andreifyt2025_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ca95b033b49845a0bbb72152f6a7fb22~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7f14e5db&amp;x-expires=1761656400&amp;x-signature=q3ouILkKlGSAip8raCpZEd463JU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1204,22 +1204,22 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>volví, haber cuantos meses me fui, que??!!!, 4 meses 😱</t>
+          <t>Qué? 😭</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>45909.19028935185</v>
+        <v>45905.7774074074</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>45909</v>
+        <v>45905</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>04:34:01</t>
+          <t>18:39:28</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7547942977034617601', 'createTime': 1757392441, 'createTimeISO': '2025-09-09T04:34:01.000Z', 'text': 'volví, haber cuantos meses me fui, que??!!!, 4 meses 😱', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546676538382746376', 'createTime': 1757097568, 'createTimeISO': '2025-09-05T18:39:28.000Z', 'text': 'Qué? 😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8267f2a1&amp;x-expires=1761656400&amp;x-signature=07aHbxuS7oulwFIUpLC%2FO1jNJmw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546705871947072276', 'createTime': 1757104397, 'createTimeISO': '2025-09-05T20:33:17.000Z', 'text': 'Wa hapen', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786334206413177862', 'uniqueId': 'oscardavidaldana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/bc48481fc572183ea9e26aa81964cf2b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1527c2ec&amp;x-expires=1761570000&amp;x-signature=gAvWE%2Fb3xcB9cc4zZNaHfvYme4w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546705871947072276', 'createTime': 1757104397, 'createTimeISO': '2025-09-05T20:33:17.000Z', 'text': 'Wa hapen', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786334206413177862', 'uniqueId': 'oscardavidaldana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/bc48481fc572183ea9e26aa81964cf2b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=86d8618c&amp;x-expires=1761656400&amp;x-signature=Hhp5qihEeClXHmH8LzyQv4kutok%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546693261533659922', 'createTime': 1757101461, 'createTimeISO': '2025-09-05T19:44:21.000Z', 'text': '👀', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9244ecc1&amp;x-expires=1761570000&amp;x-signature=NSDDd81hys0wPh8yt0LKPO%2BRR4M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546693261533659922', 'createTime': 1757101461, 'createTimeISO': '2025-09-05T19:44:21.000Z', 'text': '👀', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=12c2ed25&amp;x-expires=1761656400&amp;x-signature=%2FlKY8ng4%2BWFyH8YnoQjO0p4cG8Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546942799272411922', 'createTime': 1757159557, 'createTimeISO': '2025-09-06T11:52:37.000Z', 'text': '😭😰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b9aca162&amp;x-expires=1761570000&amp;x-signature=BQoWCp7S4NBWqkUmIlQfbTGSjSg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546942799272411922', 'createTime': 1757159557, 'createTimeISO': '2025-09-06T11:52:37.000Z', 'text': '😭😰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9be20add&amp;x-expires=1761656400&amp;x-signature=FGFTxCefax5wPBxc4kYl%2FPy%2ByZk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7549569237565211409', 'createTime': 1757771074, 'createTimeISO': '2025-09-13T13:44:34.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7186369712568189957', 'uniqueId': 'luzadrianacanooro', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ba9035ed44089efdd68ad1a325c0409b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0229817e&amp;x-expires=1761570000&amp;x-signature=MSPftVTnJhYKaKfQpXMW%2FHiaMYI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7549569237565211409', 'createTime': 1757771074, 'createTimeISO': '2025-09-13T13:44:34.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7186369712568189957', 'uniqueId': 'luzadrianacanooro', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ba9035ed44089efdd68ad1a325c0409b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=98fa7be9&amp;x-expires=1761656400&amp;x-signature=azZyX4ClIFN%2Fu6Bxw12KCjxWvM8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7557608767006114567', 'createTime': 1759642921, 'createTimeISO': '2025-10-05T05:42:01.000Z', 'text': 'Por qué están en problemas con el ministerio de trabajo @Ministerio de Trabajo -Bolivia por qué sus distribuidores en el país tienen a sus empleados con explotación laboral sobre carga laboral horarios que exceden las 15 horas y no les pagan extras ni recargos donde un empleado hace lo de 3 empleados', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6954818842602931205', 'uniqueId': 'fabiobedoya1504', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0533c8b2372d1c920dad7ae339c48a3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d0d5f4db&amp;x-expires=1761570000&amp;x-signature=pjSPTHUYXplQ7kWrMUvAgg%2FUpF4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Ministerio de Trabajo -Bolivia'], 'detailedMentions': [{'userId': '6817567040930497541', 'nickName': 'Ministerio de Trabajo -Bolivia', 'profileUrl': 'https://www.tiktok.com/@6817567040930497541', 'secUid': 'MS4wLjABAAAAVga5B9Md-oI5XuH5Ruk5ES1IympOnnPUKuurL6hWMHXQ6hzxZPUYisB2cnA5aPyh'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7557608767006114567', 'createTime': 1759642921, 'createTimeISO': '2025-10-05T05:42:01.000Z', 'text': 'Por qué están en problemas con el ministerio de trabajo @Ministerio de Trabajo -Bolivia por qué sus distribuidores en el país tienen a sus empleados con explotación laboral sobre carga laboral horarios que exceden las 15 horas y no les pagan extras ni recargos donde un empleado hace lo de 3 empleados', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6954818842602931205', 'uniqueId': 'fabiobedoya1504', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0533c8b2372d1c920dad7ae339c48a3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=07f5fe63&amp;x-expires=1761656400&amp;x-signature=0pWrRYjl1qKhftKxupqAFYKF%2BEU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Ministerio de Trabajo -Bolivia'], 'detailedMentions': [{'userId': '6817567040930497541', 'nickName': 'Ministerio de Trabajo -Bolivia', 'profileUrl': 'https://www.tiktok.com/@6817567040930497541', 'secUid': 'MS4wLjABAAAAVga5B9Md-oI5XuH5Ruk5ES1IympOnnPUKuurL6hWMHXQ6hzxZPUYisB2cnA5aPyh'}]}</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546679584475349768', 'createTime': 1757098279, 'createTimeISO': '2025-09-05T18:51:19.000Z', 'text': 'ay y por que alpinita', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7389831937894843398', 'uniqueId': 'un_emo_amigable', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37bc4cd15dd442f352783fdcce05dfb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=55ce5c2e&amp;x-expires=1761570000&amp;x-signature=G1RnXtmDwxKSh3%2BohFQle4lMw28%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'input': 'https://www.tiktok.com/@alpinacol/video/7546652098490797368', 'cid': '7546679584475349768', 'createTime': 1757098279, 'createTimeISO': '2025-09-05T18:51:19.000Z', 'text': 'ay y por que alpinita', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7389831937894843398', 'uniqueId': 'un_emo_amigable', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37bc4cd15dd442f352783fdcce05dfb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=af3f6bf1&amp;x-expires=1761656400&amp;x-signature=qjxEujZ0sabMffscEXUlYnj%2Fqs4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1596,25 +1596,25 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo</t>
+          <t>Ay tan bonitaaaaa mañana nos vemos 🥺</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>45942.55431712963</v>
+        <v>45912.17210648148</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>45942</v>
+        <v>45912</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13:18:13</t>
+          <t>04:07:50</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7560323939830924039', 'createTime': 1760275093, 'createTimeISO': '2025-10-12T13:18:13.000Z', 'text': 'para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7278338689078658054', 'uniqueId': 'chelo_velez', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/66a0861aa54c87fafc40a21878c5a064~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2d079850&amp;x-expires=1761570000&amp;x-signature=TLlfLihhl3A41kC0EzIGD6Z9DTc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549049533700277012', 'createTime': 1757650070, 'createTimeISO': '2025-09-12T04:07:50.000Z', 'text': 'Ay tan bonitaaaaa mañana nos vemos 🥺', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7355258637583844357', 'uniqueId': 'majitouuuuuu0', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/dbc73978fd3f05b374910bef0e207b56~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=d283ead8&amp;x-expires=1761656400&amp;x-signature=EsmYBSk7Ve0hvkJ18cpQrQJTpT8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1652,25 +1652,25 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ay tan bonitaaaaa mañana nos vemos 🥺</t>
+          <t>para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>45912.17210648148</v>
+        <v>45942.55431712963</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>45912</v>
+        <v>45942</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>04:07:50</t>
+          <t>13:18:13</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549049533700277012', 'createTime': 1757650070, 'createTimeISO': '2025-09-12T04:07:50.000Z', 'text': 'Ay tan bonitaaaaa mañana nos vemos 🥺', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7355258637583844357', 'uniqueId': 'majitouuuuuu0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/dbc73978fd3f05b374910bef0e207b56~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d4f4370a&amp;x-expires=1761570000&amp;x-signature=ZFULCeeUtvywpY8p0JXFHKdLZwg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7560323939830924039', 'createTime': 1760275093, 'createTimeISO': '2025-10-12T13:18:13.000Z', 'text': 'para mí alpina no nesecita mucha publicidad,Alpina es un producto que se vende solo....solo con escuchar Alpina en mi mente automáticamente es calidad y muy rico..todo', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7278338689078658054', 'uniqueId': 'chelo_velez', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/66a0861aa54c87fafc40a21878c5a064~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=cf2f6e22&amp;x-expires=1761656400&amp;x-signature=t4qDDBCV6UzYjNGhq35GEAD49%2B4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1708,25 +1708,25 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>jojojo</t>
+          <t>siiii ayudemosle!!!</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>45935.64364583333</v>
+        <v>45912.8164699074</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>45935</v>
+        <v>45912</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15:26:51</t>
+          <t>19:35:43</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557758733863387920', 'createTime': 1759678011, 'createTimeISO': '2025-10-05T15:26:51.000Z', 'text': 'jojojo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554795739316306964', 'uniqueId': 'freydermurcia33', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/699d7f94c2d9a0694952663b219cc25f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=347ebf06&amp;x-expires=1761570000&amp;x-signature=ZWtJaxzCTlQSEHkSHN80aU5lotY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549288639830721301', 'createTime': 1757705743, 'createTimeISO': '2025-09-12T19:35:43.000Z', 'text': 'siiii ayudemosle!!!', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=b8248c9e&amp;x-expires=1761656400&amp;x-signature=lvdBXaNVD7rjORU17O08GG84hMA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549596693055554311', 'createTime': 1757777462, 'createTimeISO': '2025-09-13T15:31:02.000Z', 'text': 'A AYUDAR A ALPINA\U0001fa77\U0001fa77\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549596693055554311', 'createTime': 1757777462, 'createTimeISO': '2025-09-13T15:31:02.000Z', 'text': 'A AYUDAR A ALPINA\U0001fa77\U0001fa77\U0001fa77', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=3cfa67d7&amp;x-expires=1761656400&amp;x-signature=wFsen9%2FyikDVeCZ7bFHp1QjVScE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549217011010044692', 'createTime': 1757689065, 'createTimeISO': '2025-09-12T14:57:45.000Z', 'text': 'Siiiii! Ya quiero ver la nueva practicante🎉🎉🎉', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b3df464&amp;x-expires=1761570000&amp;x-signature=%2B5Kjk%2FNsFieX1m07yrNaeC%2FJ6u8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549217011010044692', 'createTime': 1757689065, 'createTimeISO': '2025-09-12T14:57:45.000Z', 'text': 'Siiiii! Ya quiero ver la nueva practicante🎉🎉🎉', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=f4aa6ddd&amp;x-expires=1761656400&amp;x-signature=sac8%2BDpw4in7VxuHdwxN%2BR3Yb08%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1876,25 +1876,25 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>siiii ayudemosle!!!</t>
+          <t>Quien esssss ? 👀</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>45912.8164699074</v>
+        <v>45912.81784722222</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19:35:43</t>
+          <t>19:37:42</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549288639830721301', 'createTime': 1757705743, 'createTimeISO': '2025-09-12T19:35:43.000Z', 'text': 'siiii ayudemosle!!!', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=109ea6b2&amp;x-expires=1761570000&amp;x-signature=rf95%2BkUaV%2Fv4O%2FPzSATd4vhGdvA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549289149077979912', 'createTime': 1757705862, 'createTimeISO': '2025-09-12T19:37:42.000Z', 'text': 'Quien esssss ? 👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7255348886041691141', 'uniqueId': 'jholainec21', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/205ba05ede21686eb806965cb40fd502~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=fb2dbbc0&amp;x-expires=1761656400&amp;x-signature=%2FlA75ld8nTnY0WpKrBO0JBIXiZA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1932,18 +1932,18 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>holitaaaa</t>
+          <t>jojojo</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>45912.04994212963</v>
+        <v>45935.64364583333</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>45912</v>
+        <v>45935</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>01:11:55</t>
+          <t>15:26:51</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549004192569525000', 'createTime': 1757639515, 'createTimeISO': '2025-09-12T01:11:55.000Z', 'text': 'holitaaaa', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6982722979595863046', 'uniqueId': 'mrbrawl69', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/38c613c8f3cea66a0a3bfeab34f76e58~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1a418b44&amp;x-expires=1761570000&amp;x-signature=WLFo72yWWLoKEetm3mEV7eOGtng%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557758733863387920', 'createTime': 1759678011, 'createTimeISO': '2025-10-05T15:26:51.000Z', 'text': 'jojojo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554795739316306964', 'uniqueId': 'freydermurcia33', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/699d7f94c2d9a0694952663b219cc25f~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=f6484533&amp;x-expires=1761656400&amp;x-signature=22YPnqBmkDtdmwvzJt9g2%2FHLlbU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -1988,18 +1988,18 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Un concurso de cocina ?</t>
+          <t>holitaaaa</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>45912.07991898148</v>
+        <v>45912.04994212963</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>01:55:05</t>
+          <t>01:11:55</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549015309047710471', 'createTime': 1757642105, 'createTimeISO': '2025-09-12T01:55:05.000Z', 'text': 'Un concurso de cocina ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6790480840596358149', 'uniqueId': 'vivianaospina67', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/34082dcda72461c00ba3d59eb0cda82a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=74b57f0b&amp;x-expires=1761570000&amp;x-signature=zcwwCQymWoyS1rBKkE6Q5sGSl3o%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549004192569525000', 'createTime': 1757639515, 'createTimeISO': '2025-09-12T01:11:55.000Z', 'text': 'holitaaaa', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6982722979595863046', 'uniqueId': 'mrbrawl69', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/38c613c8f3cea66a0a3bfeab34f76e58~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=6c8754cf&amp;x-expires=1761656400&amp;x-signature=xFAs8WlicjRNbd126L53cDgkLPw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2044,22 +2044,22 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>Un concurso de cocina ?</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>45912.03950231482</v>
+        <v>45912.07991898148</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>00:56:53</t>
+          <t>01:55:05</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000273060233991', 'createTime': 1757638613, 'createTimeISO': '2025-09-12T00:56:53.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e0aba58&amp;x-expires=1761570000&amp;x-signature=OWekD83TiJfQ2m%2B3WwuiT6Ts%2BXI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549015309047710471', 'createTime': 1757642105, 'createTimeISO': '2025-09-12T01:55:05.000Z', 'text': 'Un concurso de cocina ?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6790480840596358149', 'uniqueId': 'vivianaospina67', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/34082dcda72461c00ba3d59eb0cda82a~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=dda3cffb&amp;x-expires=1761656400&amp;x-signature=Lxtx%2FHToTKRNtkLQ%2B2tDUBCIpFA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2100,22 +2100,22 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>🥰🥰🥰</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>45912.05922453704</v>
+        <v>45912.03950231482</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>01:25:17</t>
+          <t>00:56:53</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549007617818559250', 'createTime': 1757640317, 'createTimeISO': '2025-09-12T01:25:17.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6710319884842337285', 'uniqueId': 'itssantiagocelis', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/c17d4d00500c39eed015d9ab552b352a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5962eec2&amp;x-expires=1761570000&amp;x-signature=7Ju8FYMl8%2Fdw4UxwBQXbQQM2rpU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000273060233991', 'createTime': 1757638613, 'createTimeISO': '2025-09-12T00:56:53.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=764d9094&amp;x-expires=1761656400&amp;x-signature=0xRPdlhG6M23033A%2BnLFLiWE9KU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2156,18 +2156,18 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>😮😮😮</t>
+          <t>🥰😳😁</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>45912.68053240741</v>
+        <v>45912.87542824074</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16:19:58</t>
+          <t>21:00:37</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549238211336487681', 'createTime': 1757693998, 'createTimeISO': '2025-09-12T16:19:58.000Z', 'text': '😮😮😮', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6778152010580509702', 'uniqueId': 'esteban_ocampov', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6a63d386d387123e4d61df4e994bb26d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9aea2ee0&amp;x-expires=1761570000&amp;x-signature=lmAxojUE0vMntGdDG%2F3WvYJar1E%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549310477420708629', 'createTime': 1757710837, 'createTimeISO': '2025-09-12T21:00:37.000Z', 'text': '🥰😳😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7509769410816705544', 'uniqueId': 'user749076194246', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=029fb7c2&amp;x-expires=1761656400&amp;x-signature=QuFjNuIATuzch0RIfRZ5ZEnVh6I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2212,18 +2212,18 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>🥰😳😁</t>
+          <t>😮😮😮</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>45912.87542824074</v>
+        <v>45912.68053240741</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21:00:37</t>
+          <t>16:19:58</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549310477420708629', 'createTime': 1757710837, 'createTimeISO': '2025-09-12T21:00:37.000Z', 'text': '🥰😳😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7509769410816705544', 'uniqueId': 'user749076194246', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549238211336487681', 'createTime': 1757693998, 'createTimeISO': '2025-09-12T16:19:58.000Z', 'text': '😮😮😮', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6778152010580509702', 'uniqueId': 'esteban_ocampov', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/6a63d386d387123e4d61df4e994bb26d~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=e6566f28&amp;x-expires=1761656400&amp;x-signature=02FRNBQ0mY%2BN%2BR5jG2w96jvk%2Bsg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2268,18 +2268,18 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>🗿🗿🗿</t>
+          <t>🥰🥰🥰</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>45912.03923611111</v>
+        <v>45912.05922453704</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>45912</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>00:56:30</t>
+          <t>01:25:17</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000221259399954', 'createTime': 1757638590, 'createTimeISO': '2025-09-12T00:56:30.000Z', 'text': '🗿🗿🗿', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319745287890387973', 'uniqueId': 'matias_8595', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/37f085e6cd1478b738e427953d05ecb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b1455c2b&amp;x-expires=1761570000&amp;x-signature=0QmrdHIjL0AlbTctpekJS6qwrmY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549007617818559250', 'createTime': 1757640317, 'createTimeISO': '2025-09-12T01:25:17.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6710319884842337285', 'uniqueId': 'itssantiagocelis', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/c17d4d00500c39eed015d9ab552b352a~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=ec898d63&amp;x-expires=1761656400&amp;x-signature=7zc9Mp7AS5napQpphCNKvbIpyWA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2324,18 +2324,18 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>rgcuhif</t>
+          <t>🗿🗿🗿</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>45936.01050925926</v>
+        <v>45912.03923611111</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>45936</v>
+        <v>45912</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>00:15:08</t>
+          <t>00:56:30</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557895538470322945', 'createTime': 1759709708, 'createTimeISO': '2025-10-06T00:15:08.000Z', 'text': 'rgcuhif', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6975369451886593029', 'uniqueId': 'noraortegom', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549000221259399954', 'createTime': 1757638590, 'createTimeISO': '2025-09-12T00:56:30.000Z', 'text': '🗿🗿🗿', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319745287890387973', 'uniqueId': 'matias_8595', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/37f085e6cd1478b738e427953d05ecb8~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=cc406af2&amp;x-expires=1761656400&amp;x-signature=P1%2FxtK7BFlKBjAfYjqZXfHXenUo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>que vuelvan los gatos porfiiii</t>
+          <t>rgcuhif</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>45940.73591435186</v>
+        <v>45936.01050925926</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>45940</v>
+        <v>45936</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17:39:43</t>
+          <t>00:15:08</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7559649133477823253', 'createTime': 1760117983, 'createTimeISO': '2025-10-10T17:39:43.000Z', 'text': 'que vuelvan los gatos porfiiii', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7541238264298357778', 'uniqueId': 'invencible799', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/41228f33689b86eba8bd2b23e2173644~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a725470&amp;x-expires=1761570000&amp;x-signature=TmzbHPjb70icT0jmSa2RBd0EwUY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7557895538470322945', 'createTime': 1759709708, 'createTimeISO': '2025-10-06T00:15:08.000Z', 'text': 'rgcuhif', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6975369451886593029', 'uniqueId': 'noraortegom', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=029fb7c2&amp;x-expires=1761656400&amp;x-signature=QuFjNuIATuzch0RIfRZ5ZEnVh6I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549191179351474951', 'createTime': 1757683161, 'createTimeISO': '2025-09-12T13:19:21.000Z', 'text': 'alpina yo quiero saber si¿la nueva colección de yogo premio se llama mochi saurios????@Alpina 🐮', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5e566503&amp;x-expires=1761570000&amp;x-signature=crBApd%2Fd%2FyYfuKhDihwij3EbqYg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549191179351474951', 'createTime': 1757683161, 'createTimeISO': '2025-09-12T13:19:21.000Z', 'text': 'alpina yo quiero saber si¿la nueva colección de yogo premio se llama mochi saurios????@Alpina 🐮', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=72702226&amp;x-expires=1761656400&amp;x-signature=Z%2BstzNwJORu4g%2FObAk22uj9pNG8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -2492,22 +2492,22 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quien esssss ? 👀</t>
+          <t>que vuelvan los gatos porfiiii</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>45912.81784722222</v>
+        <v>45940.73591435186</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>45912</v>
+        <v>45940</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19:37:42</t>
+          <t>17:39:43</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7549289149077979912', 'createTime': 1757705862, 'createTimeISO': '2025-09-12T19:37:42.000Z', 'text': 'Quien esssss ? 👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7255348886041691141', 'uniqueId': 'jholainec21', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/205ba05ede21686eb806965cb40fd502~tplv-tiktokx-cropcenter:100:100.jpg?dr=10399&amp;refresh_token=e9b6b21a&amp;x-expires=1761570000&amp;x-signature=OCr5DmD5DyvV91bBM8%2BPVIhcTq4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=no1a', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'input': 'https://www.tiktok.com/@alpinacol/video/7548999291960823096', 'cid': '7559649133477823253', 'createTime': 1760117983, 'createTimeISO': '2025-10-10T17:39:43.000Z', 'text': 'que vuelvan los gatos porfiiii', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7541238264298357778', 'uniqueId': 'invencible799', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/41228f33689b86eba8bd2b23e2173644~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=7b15c385&amp;x-expires=1761656400&amp;x-signature=82915O9Qa2KJvfDZwHDnu14bouU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2548,22 +2548,22 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Te amo me encanta Alpina 🥰</t>
+          <t>QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>45917.01868055556</v>
+        <v>45917.02540509259</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>00:26:54</t>
+          <t>00:36:35</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550847978996859666', 'createTime': 1758068814, 'createTimeISO': '2025-09-17T00:26:54.000Z', 'text': 'Te amo me encanta Alpina 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6aa5f872&amp;x-expires=1761570000&amp;x-signature=ll%2FiiMVSWZhZEwWV%2BWhvVB5FP18%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550850431720325905', 'createTime': 1758069395, 'createTimeISO': '2025-09-17T00:36:35.000Z', 'text': 'QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '282408726983028736', 'uniqueId': 'wanna_juana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/17e1ad71c0265acba1716a4696601785~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bd4dc1eb&amp;x-expires=1761660000&amp;x-signature=6Kzo5ZDnjsCu5GdCCHwkA2fJGYM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2604,25 +2604,25 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)</t>
+          <t>no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>45922.03340277778</v>
+        <v>45916.99344907407</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>45922</v>
+        <v>45916</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>00:48:06</t>
+          <t>23:50:34</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552707780533863189', 'createTime': 1758502086, 'createTimeISO': '2025-09-22T00:48:06.000Z', 'text': 'cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=196af7c3&amp;x-expires=1761570000&amp;x-signature=mfmJCzSJseg0BUINUmeciufLGgM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550838637400179464', 'createTime': 1758066634, 'createTimeISO': '2025-09-16T23:50:34.000Z', 'text': 'no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6952624737991443462', 'uniqueId': 'valeria_noo2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1a1431eb5fd2ec2b3db383b2b0e26ac9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ca1abcde&amp;x-expires=1761660000&amp;x-signature=HAEMdAWHP5XS%2FdZwHsRfhRqhsrg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2660,25 +2660,25 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭</t>
+          <t>Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>45916.99344907407</v>
+        <v>45936.70731481481</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>45916</v>
+        <v>45936</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>23:50:34</t>
+          <t>16:58:32</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550838637400179464', 'createTime': 1758066634, 'createTimeISO': '2025-09-16T23:50:34.000Z', 'text': 'no soy practicante Pero quiero trabajar con ustedes 😭 soy admin, que puedo hacer? 😭', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6952624737991443462', 'uniqueId': 'valeria_noo2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1a1431eb5fd2ec2b3db383b2b0e26ac9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ab113881&amp;x-expires=1761570000&amp;x-signature=xPForBLlds5o5g4%2Fd9Kh74LuwIM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558154185101247240', 'createTime': 1759769912, 'createTimeISO': '2025-10-06T16:58:32.000Z', 'text': 'Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7005260384655574022', 'uniqueId': 'diegoalejandropat3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327286844337127429~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=608b2e70&amp;x-expires=1761660000&amp;x-signature=Sc3VjlJDeoR3dqpizDmZVE5BzcA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2716,22 +2716,22 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗</t>
+          <t>Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>45917.02540509259</v>
+        <v>45917.05436342592</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>00:36:35</t>
+          <t>01:18:17</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550850431720325905', 'createTime': 1758069395, 'createTimeISO': '2025-09-17T00:36:35.000Z', 'text': 'QUIERO MI MOCHISAURIOOOOO 😭🦕😩💗', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '282408726983028736', 'uniqueId': 'wanna_juana', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/17e1ad71c0265acba1716a4696601785~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=88c097fc&amp;x-expires=1761570000&amp;x-signature=MIQ7FC6pR3S7mhDreHpWpiFoOU8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550861226680648468', 'createTime': 1758071897, 'createTimeISO': '2025-09-17T01:18:17.000Z', 'text': 'Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c794ea9c&amp;x-expires=1761660000&amp;x-signature=sB2GhCshW5CvGVZX0LaXIDSL9hI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2772,22 +2772,22 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩</t>
+          <t>AMAMOSSSS el contenido de Gabi</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>45917.05436342592</v>
+        <v>45917.09577546296</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>01:18:17</t>
+          <t>02:17:55</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550861226680648468', 'createTime': 1758071897, 'createTimeISO': '2025-09-17T01:18:17.000Z', 'text': 'Lo emocionada que estoy por hacer parte del equipo no tiene nombre 😩', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f5aece25&amp;x-expires=1761570000&amp;x-signature=Zl4tz07p0ieZ8Pxe8VY0POWecRU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550876642629944071', 'createTime': 1758075475, 'createTimeISO': '2025-09-17T02:17:55.000Z', 'text': 'AMAMOSSSS el contenido de Gabi', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b40e946a&amp;x-expires=1761660000&amp;x-signature=pxwrH0IJ9gHlVSshUpkXx3grUWo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2828,18 +2828,18 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amò este Alpina</t>
+          <t>Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>45919.13483796296</v>
+        <v>45917.58866898148</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>45919</v>
+        <v>45917</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>03:14:10</t>
+          <t>14:07:41</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551633311488082696', 'createTime': 1758251650, 'createTimeISO': '2025-09-19T03:14:10.000Z', 'text': 'Amò este Alpina', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6955254769972806662', 'uniqueId': 'santiwhosthat', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9848dac63ccb5eeefc999aaeb526145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=38287148&amp;x-expires=1761570000&amp;x-signature=T36cejv0HS%2FeTrSmbE%2FE6%2FZQyu4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551059537588929298', 'createTime': 1758118061, 'createTimeISO': '2025-09-17T14:07:41.000Z', 'text': 'Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=23b8df77&amp;x-expires=1761660000&amp;x-signature=AC5tEYMZp41mwv3OsAL3CrhWkZQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550836019215958805', 'createTime': 1758066041, 'createTimeISO': '2025-09-16T23:40:41.000Z', 'text': '1ro\nalpina te amo!!', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452218782174446597', 'uniqueId': 'shidouxsae0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2865ac893335cccef6405d3bf354fedb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ac44156&amp;x-expires=1761570000&amp;x-signature=leR4FwW%2FIBrxMInIYQmj77K6py8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550836019215958805', 'createTime': 1758066041, 'createTimeISO': '2025-09-16T23:40:41.000Z', 'text': '1ro\nalpina te amo!!', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452218782174446597', 'uniqueId': 'shidouxsae0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2865ac893335cccef6405d3bf354fedb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=97768ae7&amp;x-expires=1761660000&amp;x-signature=vXiYFFZX0%2FMgrXD14CWU4PdxKP0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2941,26 +2941,26 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis</t>
+          <t>Yo quierooooo✨</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>45917.87722222223</v>
+        <v>45917.00403935185</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21:03:12</t>
+          <t>00:05:49</t>
         </is>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551166524197077767', 'createTime': 1758142992, 'createTimeISO': '2025-09-17T21:03:12.000Z', 'text': 'pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=26a7ae26&amp;x-expires=1761570000&amp;x-signature=z4Cc6Vhls%2BKFDO7%2FuIUSOXTFj7k%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550842534529860370', 'createTime': 1758067549, 'createTimeISO': '2025-09-17T00:05:49.000Z', 'text': 'Yo quierooooo✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781227104677250053', 'uniqueId': 'lauraleguizamou', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0ac3e8266fc87e3612cd93ce4262beda~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7fe7685f&amp;x-expires=1761660000&amp;x-signature=uVwQE9woqnC8BsijOBswoorEkEw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -2997,25 +2997,25 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭</t>
+          <t>¿Qué tipo de contrato tienen?</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>45919.69366898148</v>
+        <v>45920.96097222222</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>45919</v>
+        <v>45920</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16:38:53</t>
+          <t>23:03:48</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551840682764829458', 'createTime': 1758299933, 'createTimeISO': '2025-09-19T16:38:53.000Z', 'text': 'si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6885505605576377345', 'uniqueId': 'spaaaak_4.m', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7324800281223364610~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=828a8d27&amp;x-expires=1761570000&amp;x-signature=TXWPVFYwrWbDwSfgjGSmjwn3CVY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552310929883448084', 'createTime': 1758409428, 'createTimeISO': '2025-09-20T23:03:48.000Z', 'text': '¿Qué tipo de contrato tienen?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856891169080443909', 'uniqueId': 'lourdesbarragan_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e377e28c29d509541307260e66fb275d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3294501e&amp;x-expires=1761660000&amp;x-signature=BUv3vdB45slbrDRcmT5ScVEgErI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3053,25 +3053,25 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!</t>
+          <t>Me salió tarde el vídeo 😟 yo quiero 🥹🙏🏻</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>45917.58866898148</v>
+        <v>45941.61577546296</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>45917</v>
+        <v>45941</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14:07:41</t>
+          <t>14:46:43</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551059537588929298', 'createTime': 1758118061, 'createTimeISO': '2025-09-17T14:07:41.000Z', 'text': 'Gaby! Quiero ver cómo hacen el arequipe! Deberías hacer un tour por la planta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6823366905291965446', 'uniqueId': 'jfelipegomez1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7329628384854736902~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=81414567&amp;x-expires=1761570000&amp;x-signature=dyvbRhF3TGiyo9zL0%2Fd3%2FE%2FecEc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7559975652176577288', 'createTime': 1760194003, 'createTimeISO': '2025-10-11T14:46:43.000Z', 'text': 'Me salió tarde el vídeo 😟 yo quiero \U0001f979🙏🏻', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6670638394765033478', 'uniqueId': 'lindanarino', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/873e52b20a774b09b73f0f0d565e6959~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f8dfbf41&amp;x-expires=1761660000&amp;x-signature=eBt6wPvfgDQZOH8k27cnLmF6s00%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3109,25 +3109,25 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AMAMOSSSS el contenido de Gabi</t>
+          <t>Buenisimo!!!!!</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>45917.09577546296</v>
+        <v>45919.87149305556</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>02:17:55</t>
+          <t>20:54:57</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550876642629944071', 'createTime': 1758075475, 'createTimeISO': '2025-09-17T02:17:55.000Z', 'text': 'AMAMOSSSS el contenido de Gabi', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bb35b1b1&amp;x-expires=1761570000&amp;x-signature=QjOPv77uCLlckf8dBxpc%2BZwaAdA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551906649611830023', 'createTime': 1758315297, 'createTimeISO': '2025-09-19T20:54:57.000Z', 'text': 'Buenisimo!!!!!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7068293195050877957', 'uniqueId': 'mfzamarriego', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5891c8d97d65891a135a4f898bbe9dc6~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8abedc86&amp;x-expires=1761660000&amp;x-signature=%2FziP6EnZTEpipNMGE1nqiCt%2Fjek%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3165,18 +3165,18 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yo quierooooo✨</t>
+          <t>Mi sueño haciéndose realidad 🥰🥺</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>45917.00403935185</v>
+        <v>45918.62016203703</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>00:05:49</t>
+          <t>14:53:02</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550842534529860370', 'createTime': 1758067549, 'createTimeISO': '2025-09-17T00:05:49.000Z', 'text': 'Yo quierooooo✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781227104677250053', 'uniqueId': 'lauraleguizamou', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0ac3e8266fc87e3612cd93ce4262beda~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1b54d5d9&amp;x-expires=1761570000&amp;x-signature=ohoskb0UmDbnF6LY7dnFTgKr09c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551442303657116436', 'createTime': 1758207182, 'createTimeISO': '2025-09-18T14:53:02.000Z', 'text': 'Mi sueño haciéndose realidad 🥰🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6788284872554497030', 'uniqueId': 'anirivera_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c6e77f0d746b65b48a78e1205c8c82~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e4d57b5&amp;x-expires=1761660000&amp;x-signature=piVE8vHfZGLRLkCFVW1POF8UfJY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3221,25 +3221,25 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? 🥹</t>
+          <t>cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>45918.74025462963</v>
+        <v>45922.03340277778</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>17:45:58</t>
+          <t>00:48:06</t>
         </is>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551486875396948744', 'createTime': 1758217558, 'createTimeISO': '2025-09-18T17:45:58.000Z', 'text': 'Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? \U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6817806087653164037', 'uniqueId': 'brandontarcila_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6b11bf080b10cd0207666b99c05d31b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b39b37b8&amp;x-expires=1761570000&amp;x-signature=aOEiDV7M7bxRKaoH8RSp%2FyuCpMc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552707780533863189', 'createTime': 1758502086, 'createTimeISO': '2025-09-22T00:48:06.000Z', 'text': 'cuantos comentarios y reacciones para ganarme la nueva colección de Mochis de dinosaurios 🥺 (no me ignoren, ayuden personas a que lo vean🙏🏻)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d7d3025f&amp;x-expires=1761660000&amp;x-signature=tA0h7xmzMJont6v3WzoDB1g1%2BWI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3277,18 +3277,18 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Buenisimo!!!!!</t>
+          <t>como se puede conseguir el álbum de mochis</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>45919.87149305556</v>
+        <v>45928.17954861111</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>45919</v>
+        <v>45928</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20:54:57</t>
+          <t>04:18:33</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551906649611830023', 'createTime': 1758315297, 'createTimeISO': '2025-09-19T20:54:57.000Z', 'text': 'Buenisimo!!!!!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7068293195050877957', 'uniqueId': 'mfzamarriego', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5891c8d97d65891a135a4f898bbe9dc6~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b20f8bd2&amp;x-expires=1761570000&amp;x-signature=jT2u9ag7o%2B34ROZjlxknjf6FFHE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554989643563205384', 'createTime': 1759033113, 'createTimeISO': '2025-09-28T04:18:33.000Z', 'text': 'como se puede conseguir el álbum de mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7340762611166299142', 'uniqueId': 'wilson.piraquive5', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/376f70562283aeaeeb98265a1fe54ae8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f7ee3da7&amp;x-expires=1761660000&amp;x-signature=mGj0h7mrZbPSrjKyC%2F%2BTtksjfR8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3333,18 +3333,18 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Buen día, aceptan pasantes en área administrativa?😳</t>
+          <t>estando en etapa lectiva puedo aplicar</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>45924.54788194445</v>
+        <v>45926.77971064814</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13:08:57</t>
+          <t>18:42:47</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553641991944602386', 'createTime': 1758719337, 'createTimeISO': '2025-09-24T13:08:57.000Z', 'text': 'Buen día, aceptan pasantes en área administrativa?😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819016661686453254', 'uniqueId': 'scatalina15', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65616505ecd12a1b5dd469d79ec8a719~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=33c13ddb&amp;x-expires=1761570000&amp;x-signature=6n8L8yA8cdrzFEwJqaLjmdUPxNg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554470184620000018', 'createTime': 1758912167, 'createTimeISO': '2025-09-26T18:42:47.000Z', 'text': 'estando en etapa lectiva puedo aplicar', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1e1dd5ba&amp;x-expires=1761660000&amp;x-signature=cYY2Tzh0w40BVDhBcI9Co%2F7twXA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3389,25 +3389,25 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>me enteré que ya subieron nuevo video 😍</t>
+          <t>pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>45917.08885416666</v>
+        <v>45917.87722222223</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>02:07:57</t>
+          <t>21:03:12</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550874055755203345', 'createTime': 1758074877, 'createTimeISO': '2025-09-17T02:07:57.000Z', 'text': 'me enteré que ya subieron nuevo video 😍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551166524197077767', 'createTime': 1758142992, 'createTimeISO': '2025-09-17T21:03:12.000Z', 'text': 'pueden sacar en yogoyogolab lods puntos autorizados de oxxo para reclamar los mochisaurios plis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f214d020&amp;x-expires=1761660000&amp;x-signature=X3Y%2F2%2BR1BUGxsQI0icleF%2FwLtYM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3445,18 +3445,18 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cuando comienzan a dar respuesta si ya apliqué?🥹</t>
+          <t>Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? 🥹</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>45916.99778935185</v>
+        <v>45918.74025462963</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23:56:49</t>
+          <t>17:45:58</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550840242002150162', 'createTime': 1758067009, 'createTimeISO': '2025-09-16T23:56:49.000Z', 'text': 'Cuando comienzan a dar respuesta si ya apliqué?\U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b5403971a2c0063750a9b7140d15458b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7548553e&amp;x-expires=1761570000&amp;x-signature=BlfR6%2B%2FfkD%2BokVL0Mtp6MdOTDUU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551486875396948744', 'createTime': 1758217558, 'createTimeISO': '2025-09-18T17:45:58.000Z', 'text': 'Estoy por graduarme de ingeniería industrial. Me encantaría hacer mis prácticas o trabajar en un futuro con ustedes. Me encanta la familia Alpina, creen que pueda hacer parte algún día? \U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6817806087653164037', 'uniqueId': 'brandontarcila_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6b11bf080b10cd0207666b99c05d31b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=efac991d&amp;x-expires=1761660000&amp;x-signature=6LwHPlHil%2FYe1aXinxriDFrwnj0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3501,25 +3501,25 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>estando en etapa lectiva puedo aplicar</t>
+          <t>si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>45926.77971064814</v>
+        <v>45919.69366898148</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>45926</v>
+        <v>45919</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>18:42:47</t>
+          <t>16:38:53</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554470184620000018', 'createTime': 1758912167, 'createTimeISO': '2025-09-26T18:42:47.000Z', 'text': 'estando en etapa lectiva puedo aplicar', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=30df542e&amp;x-expires=1761570000&amp;x-signature=ePCGB9BrUbZkPVx3h%2BelHiRBM9o%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551840682764829458', 'createTime': 1758299933, 'createTimeISO': '2025-09-19T16:38:53.000Z', 'text': 'si estudio narrativas en medios digitales y audiovisuales puedo aplicar? 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6885505605576377345', 'uniqueId': 'spaaaak_4.m', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7324800281223364610~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cac88c26&amp;x-expires=1761660000&amp;x-signature=IR5dLiMQyKHL%2FcgZq%2FARhYnaZp0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3557,18 +3557,18 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>como se puede conseguir el álbum de mochis</t>
+          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>45928.17954861111</v>
+        <v>45950.08646990741</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>45928</v>
+        <v>45950</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>04:18:33</t>
+          <t>02:04:31</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7554989643563205384', 'createTime': 1759033113, 'createTimeISO': '2025-09-28T04:18:33.000Z', 'text': 'como se puede conseguir el álbum de mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7340762611166299142', 'uniqueId': 'wilson.piraquive5', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/376f70562283aeaeeb98265a1fe54ae8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67c5fa42&amp;x-expires=1761570000&amp;x-signature=LwD24MhO3mWnwQhXBJ7z%2FRd%2Biy4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7563119000310334226', 'createTime': 1760925871, 'createTimeISO': '2025-10-20T02:04:31.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2ca9f7dc&amp;x-expires=1761660000&amp;x-signature=unZQm11UctBVLTK%2BcAJEK89ByYE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3613,25 +3613,25 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema</t>
+          <t>Cuando comienzan a dar respuesta si ya apliqué?🥹</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>45936.70731481481</v>
+        <v>45916.99778935185</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>45936</v>
+        <v>45916</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>16:58:32</t>
+          <t>23:56:49</t>
         </is>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558154185101247240', 'createTime': 1759769912, 'createTimeISO': '2025-10-06T16:58:32.000Z', 'text': 'Hola alpina cambien el vasito de yogo yogo mochisaurio por qué es muy duro y me corte cambienlo por el de premio yogo yogo que se quita fácil se que no es del tema', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7005260384655574022', 'uniqueId': 'diegoalejandropat3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327286844337127429~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4238950b&amp;x-expires=1761570000&amp;x-signature=o7S3AxC9lgK8KpakZhr%2B5YG%2F8vg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550840242002150162', 'createTime': 1758067009, 'createTimeISO': '2025-09-16T23:56:49.000Z', 'text': 'Cuando comienzan a dar respuesta si ya apliqué?\U0001f979', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b5403971a2c0063750a9b7140d15458b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=42b8f626&amp;x-expires=1761660000&amp;x-signature=acnEnY3yvru%2BwtJnMS89lX3Ol78%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3669,25 +3669,25 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
+          <t>Amò este Alpina</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>45950.08646990741</v>
+        <v>45919.13483796296</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>45950</v>
+        <v>45919</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>02:04:31</t>
+          <t>03:14:10</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7563119000310334226', 'createTime': 1760925871, 'createTimeISO': '2025-10-20T02:04:31.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ef9ccaf3&amp;x-expires=1761570000&amp;x-signature=OsrEaDn9tPollUWncoSd9dptQY0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551633311488082696', 'createTime': 1758251650, 'createTimeISO': '2025-09-19T03:14:10.000Z', 'text': 'Amò este Alpina', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6955254769972806662', 'uniqueId': 'santiwhosthat', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9848dac63ccb5eeefc999aaeb526145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=74e4fdf6&amp;x-expires=1761660000&amp;x-signature=UZKVMpCFrx%2FMVsLRjmF1XRLlx9w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3725,25 +3725,25 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mi sueño haciéndose realidad 🥰🥺</t>
+          <t>hola alpina esta es mi colección de Mochis no es mucha molestia si me envías una caja de Mochisaurios gracias 😃😉</t>
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>45918.62016203703</v>
+        <v>45931.97782407407</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>45918</v>
+        <v>45931</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>14:53:02</t>
+          <t>23:28:04</t>
         </is>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551442303657116436', 'createTime': 1758207182, 'createTimeISO': '2025-09-18T14:53:02.000Z', 'text': 'Mi sueño haciéndose realidad 🥰🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6788284872554497030', 'uniqueId': 'anirivera_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c6e77f0d746b65b48a78e1205c8c82~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=18149634&amp;x-expires=1761570000&amp;x-signature=BoQKp1u0h9cWHHJc2i3Pc6d%2BVB4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556399100905341703', 'createTime': 1759361284, 'createTimeISO': '2025-10-01T23:28:04.000Z', 'text': 'hola alpina esta es mi colección de Mochis no es mucha molestia si me envías una caja de Mochisaurios gracias 😃😉', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531368579791438866', 'uniqueId': 'damian.smith.mora', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3106fbebef557d53c4193c9474d4163c~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=96ca8914&amp;x-expires=1761660000&amp;x-signature=HH35fizfItYkfhwBnLwUZwOZxr8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3781,18 +3781,18 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Me salió tarde el vídeo 😟 yo quiero 🥹🙏🏻</t>
+          <t>@Chantal Thorin 😂</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>45941.61577546296</v>
+        <v>45917.01428240741</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>45941</v>
+        <v>45917</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14:46:43</t>
+          <t>00:20:34</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7559975652176577288', 'createTime': 1760194003, 'createTimeISO': '2025-10-11T14:46:43.000Z', 'text': 'Me salió tarde el vídeo 😟 yo quiero \U0001f979🙏🏻', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6670638394765033478', 'uniqueId': 'lindanarino', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/873e52b20a774b09b73f0f0d565e6959~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=66d1f629&amp;x-expires=1761570000&amp;x-signature=1LsnCvnrmE4%2Ff1aH6soMndEHhAo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550846347324130055', 'createTime': 1758068434, 'createTimeISO': '2025-09-17T00:20:34.000Z', 'text': '@Chantal Thorin 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6788904373575074822', 'uniqueId': 'juanolmos023', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/715053c66c983c3c1c50e1eb7df0c471~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=09cab8c4&amp;x-expires=1761660000&amp;x-signature=0%2Fm2zOfAXwK2O99GF64oBw264I4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Chantal Thorin'], 'detailedMentions': [{'userId': '7323823789984531462', 'nickName': 'Chantal Thorin', 'profileUrl': 'https://www.tiktok.com/@7323823789984531462', 'secUid': 'MS4wLjABAAAAeVzy1YXMwyrURUZkWFufcDOQpRrR-rZvvbSNYGZdeSPQL7wiKvQELMaPx312In6i'}]}</t>
         </is>
       </c>
     </row>
@@ -3837,25 +3837,25 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Me encantaaaa✨</t>
+          <t>😳</t>
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>45917.15711805555</v>
+        <v>45928.70622685185</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>45917</v>
+        <v>45928</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>03:46:15</t>
+          <t>16:56:58</t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550899370625254165', 'createTime': 1758080775, 'createTimeISO': '2025-09-17T03:46:15.000Z', 'text': 'Me encantaaaa✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67e127c0&amp;x-expires=1761570000&amp;x-signature=vPwM08FcKecDUNpRacSTSqBH8lw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7555185101043680018', 'createTime': 1759078618, 'createTimeISO': '2025-09-28T16:56:58.000Z', 'text': '😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7475879249447666705', 'uniqueId': 'al454329', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/00eba74212b2c117219704065444145b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e1fc79be&amp;x-expires=1761660000&amp;x-signature=XUQfpCGaCkE0rgvcw%2FegOWuaysc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3893,18 +3893,18 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>¿Qué tipo de contrato tienen?</t>
+          <t>🫡🫡🫡</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>45920.96097222222</v>
+        <v>45917.00991898148</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>45920</v>
+        <v>45917</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>23:03:48</t>
+          <t>00:14:17</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552310929883448084', 'createTime': 1758409428, 'createTimeISO': '2025-09-20T23:03:48.000Z', 'text': '¿Qué tipo de contrato tienen?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856891169080443909', 'uniqueId': 'lourdesbarragan_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e377e28c29d509541307260e66fb275d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=439eae03&amp;x-expires=1761570000&amp;x-signature=6eqgGgzpXhGjZA1Amfyx%2FCvDlW8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550844710467732242', 'createTime': 1758068057, 'createTimeISO': '2025-09-17T00:14:17.000Z', 'text': '\U0001fae1\U0001fae1\U0001fae1', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b40e946a&amp;x-expires=1761660000&amp;x-signature=pxwrH0IJ9gHlVSshUpkXx3grUWo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -3949,18 +3949,18 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>hola alpina esta es mi colección de Mochis no es mucha molestia si me envías una caja de Mochisaurios gracias 😃😉</t>
+          <t>😁</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>45931.97782407407</v>
+        <v>45932.00375</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>23:28:04</t>
+          <t>00:05:24</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556399100905341703', 'createTime': 1759361284, 'createTimeISO': '2025-10-01T23:28:04.000Z', 'text': 'hola alpina esta es mi colección de Mochis no es mucha molestia si me envías una caja de Mochisaurios gracias 😃😉', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531368579791438866', 'uniqueId': 'damian.smith.mora', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3106fbebef557d53c4193c9474d4163c~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bcfbc599&amp;x-expires=1761570000&amp;x-signature=%2BA7cmk5tD0HFBmhoeEkKuxY8WKQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556408658076435218', 'createTime': 1759363524, 'createTimeISO': '2025-10-02T00:05:24.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7280259132014806022', 'uniqueId': 'matilde.guerrero3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7280259483488665606~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e864b0c&amp;x-expires=1761660000&amp;x-signature=hNp3pS2i1ZeKwT5b%2Fh6MgO%2FVw2M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4005,25 +4005,25 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Me encantaaaa✨</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>45936.8365625</v>
+        <v>45917.15711805555</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>45936</v>
+        <v>45917</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20:04:39</t>
+          <t>03:46:15</t>
         </is>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558202100607091476', 'createTime': 1759781079, 'createTimeISO': '2025-10-06T20:04:39.000Z', 'text': '👍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452056190890116114', 'uniqueId': 'sabeldani10', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4b19cfb39961d6a4eec67ddf6a71ac66~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c6915cd5&amp;x-expires=1761570000&amp;x-signature=fmI7OQhmhKMMJ75bRwg80ZZxTrY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550899370625254165', 'createTime': 1758080775, 'createTimeISO': '2025-09-17T03:46:15.000Z', 'text': 'Me encantaaaa✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=b92107e5&amp;x-expires=1761660000&amp;x-signature=Oe1mm5Acdm52m8XgJgFmtuAW7GE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4061,25 +4061,25 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>🫡🫡🫡</t>
+          <t>me enteré que ya subieron nuevo video 😍</t>
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>45917.00991898148</v>
+        <v>45917.08885416666</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>45917</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>00:14:17</t>
+          <t>02:07:57</t>
         </is>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550844710467732242', 'createTime': 1758068057, 'createTimeISO': '2025-09-17T00:14:17.000Z', 'text': '\U0001fae1\U0001fae1\U0001fae1', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7323823789984531462', 'uniqueId': 'chantal.thorin', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/5be5fbd7e28fb667d0d61e8de45fc752~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=02da4822&amp;x-expires=1761570000&amp;x-signature=Tabf9cJDwWwdyVqfNIByzzQf6Ks%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550874055755203345', 'createTime': 1758074877, 'createTimeISO': '2025-09-17T02:07:57.000Z', 'text': 'me enteré que ya subieron nuevo video 😍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=f2cbb402&amp;x-expires=1761660000&amp;x-signature=tMkie7O0lsfK%2FxixvxLcmzODH%2BY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4117,25 +4117,25 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>😂</t>
+          <t>Te amo me encanta Alpina 🥰</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>45933.28815972222</v>
+        <v>45917.01868055556</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>45933</v>
+        <v>45917</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>06:54:57</t>
+          <t>00:26:54</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556885364948173586', 'createTime': 1759474497, 'createTimeISO': '2025-10-03T06:54:57.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7444383176737113144', 'uniqueId': 'lirasa91', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550847978996859666', 'createTime': 1758068814, 'createTimeISO': '2025-09-17T00:26:54.000Z', 'text': 'Te amo me encanta Alpina 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=07ff8e94&amp;x-expires=1761660000&amp;x-signature=wMrzn9FJX6CGHMPVjcn00bC8W1I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4173,18 +4173,18 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina</t>
+          <t>Buen día, aceptan pasantes en área administrativa?😳</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>45920.12986111111</v>
+        <v>45924.54788194445</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>45920</v>
+        <v>45924</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>03:07:00</t>
+          <t>13:08:57</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552002528465699592', 'createTime': 1758337620, 'createTimeISO': '2025-09-20T03:07:00.000Z', 'text': '@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7382728939964548101', 'uniqueId': 'eve_watajai', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/c9212056428da8609f48a989cd6e9170~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c231ba0c&amp;x-expires=1761570000&amp;x-signature=dXbhER9DncJr0DPG2E7QuRDpet8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@mochis_yogoyogo💗'], 'detailedMentions': [{'userId': '7469144855873651730', 'nickName': 'mochis_yogoyogo💗', 'profileUrl': 'https://www.tiktok.com/@7469144855873651730', 'secUid': 'MS4wLjABAAAAfnDzVmGgNedG0asJ6YoXVgPkaL-69fpJq_hPO_uLHcj8SYDqMhAidX6vu-pf-BmB'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553641991944602386', 'createTime': 1758719337, 'createTimeISO': '2025-09-24T13:08:57.000Z', 'text': 'Buen día, aceptan pasantes en área administrativa?😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6819016661686453254', 'uniqueId': 'scatalina15', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/65616505ecd12a1b5dd469d79ec8a719~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=38efe9b3&amp;x-expires=1761660000&amp;x-signature=C5BTxW5H0MGZT9OzRkzBB8YQemw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4229,18 +4229,18 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>😳</t>
+          <t>👍</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>45928.70622685185</v>
+        <v>45936.8365625</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>45928</v>
+        <v>45936</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>16:56:58</t>
+          <t>20:04:39</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7555185101043680018', 'createTime': 1759078618, 'createTimeISO': '2025-09-28T16:56:58.000Z', 'text': '😳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7475879249447666705', 'uniqueId': 'al454329', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/00eba74212b2c117219704065444145b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d093ad88&amp;x-expires=1761570000&amp;x-signature=AKN8KM2vmiV1sO3onQaKKA%2FEYug%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7558202100607091476', 'createTime': 1759781079, 'createTimeISO': '2025-10-06T20:04:39.000Z', 'text': '👍', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452056190890116114', 'uniqueId': 'sabeldani10', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/4b19cfb39961d6a4eec67ddf6a71ac66~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=eb30db8c&amp;x-expires=1761660000&amp;x-signature=QWUR8r9eMImR3YniGfLFy69hs00%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4285,18 +4285,18 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>@Chantal Thorin 😂</t>
+          <t>@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina</t>
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>45917.01428240741</v>
+        <v>45920.12986111111</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>45917</v>
+        <v>45920</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>00:20:34</t>
+          <t>03:07:00</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7550846347324130055', 'createTime': 1758068434, 'createTimeISO': '2025-09-17T00:20:34.000Z', 'text': '@Chantal Thorin 😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6788904373575074822', 'uniqueId': 'juanolmos023', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/715053c66c983c3c1c50e1eb7df0c471~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cdb6ae97&amp;x-expires=1761570000&amp;x-signature=za8CGAxYdpoFKFN4CSh6gvoIbb0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Chantal Thorin'], 'detailedMentions': [{'userId': '7323823789984531462', 'nickName': 'Chantal Thorin', 'profileUrl': 'https://www.tiktok.com/@7323823789984531462', 'secUid': 'MS4wLjABAAAAeVzy1YXMwyrURUZkWFufcDOQpRrR-rZvvbSNYGZdeSPQL7wiKvQELMaPx312In6i'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7552002528465699592', 'createTime': 1758337620, 'createTimeISO': '2025-09-20T03:07:00.000Z', 'text': '@mochis_yogoyogo💗 ya quiero mochisss aaaa está es mi cuenta donde haré unboxings de los dinomochis y más cosas de alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7382728939964548101', 'uniqueId': 'eve_watajai', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/c9212056428da8609f48a989cd6e9170~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=10bdbda9&amp;x-expires=1761660000&amp;x-signature=p%2FRwKj%2Bq3tQm1QKPfSAwzc4lYAc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@mochis_yogoyogo💗'], 'detailedMentions': [{'userId': '7469144855873651730', 'nickName': 'mochis_yogoyogo💗', 'profileUrl': 'https://www.tiktok.com/@7469144855873651730', 'secUid': 'MS4wLjABAAAAfnDzVmGgNedG0asJ6YoXVgPkaL-69fpJq_hPO_uLHcj8SYDqMhAidX6vu-pf-BmB'}]}</t>
         </is>
       </c>
     </row>
@@ -4341,18 +4341,18 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>😁</t>
+          <t>QUE VUELVA ALPILITRO 🙌🙏</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>45932.00375</v>
+        <v>45923.78733796296</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>45932</v>
+        <v>45923</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>00:05:24</t>
+          <t>18:53:46</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556408658076435218', 'createTime': 1759363524, 'createTimeISO': '2025-10-02T00:05:24.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7280259132014806022', 'uniqueId': 'matilde.guerrero3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7280259483488665606~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c7cb0cc3&amp;x-expires=1761570000&amp;x-signature=1fAymO1dwOzmYkcL%2BhDpL2ruHEo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553359733933458194', 'createTime': 1758653626, 'createTimeISO': '2025-09-23T18:53:46.000Z', 'text': 'QUE VUELVA ALPILITRO 🙌🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=dc039374&amp;x-expires=1761660000&amp;x-signature=bG%2BECD71jf298byDd09qy%2FV%2BIbM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4397,18 +4397,18 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>vuelvan a poner a la banda de gatos de alpin</t>
+          <t>Amooooo los mochisssssss</t>
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>45932.98778935185</v>
+        <v>45919.10697916667</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>45932</v>
+        <v>45919</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>23:42:25</t>
+          <t>02:34:03</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556773829139677960', 'createTime': 1759448545, 'createTimeISO': '2025-10-02T23:42:25.000Z', 'text': 'vuelvan a poner a la banda de gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7338967674703905797', 'uniqueId': 'xa.m25', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f18aaf30609d233d93d48aaec98bdc23~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a0a80b73&amp;x-expires=1761570000&amp;x-signature=H4P5friRQF2vXLO%2Bs332x7GT7nE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551622936564073224', 'createTime': 1758249243, 'createTimeISO': '2025-09-19T02:34:03.000Z', 'text': 'Amooooo los mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f6605c92&amp;x-expires=1761660000&amp;x-signature=qdjs%2Fm2rO9t8shvLDOPSLOHgPIo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4453,18 +4453,18 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amooooo los mochisssssss</t>
+          <t>vuelvan a poner a la banda de gatos de alpin</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>45919.10697916667</v>
+        <v>45932.98778935185</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>45919</v>
+        <v>45932</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>02:34:03</t>
+          <t>23:42:25</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7551622936564073224', 'createTime': 1758249243, 'createTimeISO': '2025-09-19T02:34:03.000Z', 'text': 'Amooooo los mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7c1e60b0&amp;x-expires=1761570000&amp;x-signature=Egj07X6mFOQf%2F9xF%2B3GghWInpO4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556773829139677960', 'createTime': 1759448545, 'createTimeISO': '2025-10-02T23:42:25.000Z', 'text': 'vuelvan a poner a la banda de gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7338967674703905797', 'uniqueId': 'xa.m25', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f18aaf30609d233d93d48aaec98bdc23~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=61796a96&amp;x-expires=1761660000&amp;x-signature=YL2btSVn%2BwSB7usnMaYLvWn2OCk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4509,18 +4509,18 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>QUE VUELVA ALPILITRO 🙌🙏</t>
+          <t>😂</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>45923.78733796296</v>
+        <v>45933.28815972222</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>18:53:46</t>
+          <t>06:54:57</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7553359733933458194', 'createTime': 1758653626, 'createTimeISO': '2025-09-23T18:53:46.000Z', 'text': 'QUE VUELVA ALPILITRO 🙌🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=895ae214&amp;x-expires=1761570000&amp;x-signature=sklHDUPVpgD%2BtJ6ZL2LNVhS9ie0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'input': 'https://www.tiktok.com/@alpinacol/video/7550835075697462533', 'cid': '7556885364948173586', 'createTime': 1759474497, 'createTimeISO': '2025-10-03T06:54:57.000Z', 'text': '😂', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7444383176737113144', 'uniqueId': 'lirasa91', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=10399&amp;refresh_token=82dffdec&amp;x-expires=1761660000&amp;x-signature=pKVLonko9X5R4FAwtxRHb49ulNI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=no1a', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229830001885973', 'createTime': 1758157724, 'createTimeISO': '2025-09-18T01:08:44.000Z', 'text': 'Hmmm avena saladaaa gabsss?', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b3df464&amp;x-expires=1761570000&amp;x-signature=%2B5Kjk%2FNsFieX1m07yrNaeC%2FJ6u8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229830001885973', 'createTime': 1758157724, 'createTimeISO': '2025-09-18T01:08:44.000Z', 'text': 'Hmmm avena saladaaa gabsss?', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=408babe6&amp;x-expires=1761660000&amp;x-signature=Gb4ogNJxteo2A5Xaae7UwLa3mds%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220050720670471', 'createTime': 1758155608, 'createTimeISO': '2025-09-18T00:33:28.000Z', 'text': 'quiero parte 2💙💙💙', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd681055&amp;x-expires=1761570000&amp;x-signature=wNrNCutAEF%2FapCKk%2F9SDDIPR9A4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220050720670471', 'createTime': 1758155608, 'createTimeISO': '2025-09-18T00:33:28.000Z', 'text': 'quiero parte 2💙💙💙', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7467024639018468360', 'uniqueId': 'leidy_y22', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/170467e038e889966ba7de820632ba9a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9e9bb356&amp;x-expires=1761660000&amp;x-signature=sWcd3vzm2m4SiN7xYACKsHvNdHY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551496749665649415', 'createTime': 1758219864, 'createTimeISO': '2025-09-18T18:24:24.000Z', 'text': 'jajajajajajajjajajajajajajaja eara miy bueno', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7337124256608732166', 'uniqueId': 'nathalye.cruz', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7337124473063407621~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0945d70a&amp;x-expires=1761570000&amp;x-signature=ziCcwA%2BJ6D8TfTk9hFfAz9Bxu%2BY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551496749665649415', 'createTime': 1758219864, 'createTimeISO': '2025-09-18T18:24:24.000Z', 'text': 'jajajajajajajjajajajajajajaja eara miy bueno', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7337124256608732166', 'uniqueId': 'nathalye.cruz', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7337124473063407621~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e403fcfd&amp;x-expires=1761660000&amp;x-signature=lUvk%2B5KV8XJmrif72B3GibTRPdc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4733,25 +4733,25 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>chevre el juego</t>
+          <t>Viene en varios sabores?</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>45919.12591435185</v>
+        <v>45918.12743055556</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>45919</v>
+        <v>45918</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>03:01:19</t>
+          <t>03:03:30</t>
         </is>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551629960492106503', 'createTime': 1758250879, 'createTimeISO': '2025-09-19T03:01:19.000Z', 'text': 'chevre el juego', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7428447431131857925', 'uniqueId': 'dario.bermudez.me', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e3f68c187a5bb898072670c79697373f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=33a6fd4e&amp;x-expires=1761570000&amp;x-signature=9ACe7jD8i4iGnkxDLxSpKNVVSm4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551259447134585631', 'createTime': 1758164610, 'createTimeISO': '2025-09-18T03:03:30.000Z', 'text': 'Viene en varios sabores?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '125087857735528448', 'uniqueId': 'camilocc3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-useast8-avt-0068-tx2/24fcb4fdd0b5e8275182d605c3f58355~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2689d7a7&amp;x-expires=1761660000&amp;x-signature=jFBFEA7UENbj3HGbKU6Zd69PqlQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4789,25 +4789,25 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Viene en varios sabores?</t>
+          <t>Jajajjaajajajjaa buenísimo</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>45918.12743055556</v>
+        <v>45918.04732638889</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>45918</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>03:03:30</t>
+          <t>01:08:09</t>
         </is>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551259447134585631', 'createTime': 1758164610, 'createTimeISO': '2025-09-18T03:03:30.000Z', 'text': 'Viene en varios sabores?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '125087857735528448', 'uniqueId': 'camilocc3', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-useast8-avt-0068-tx2/24fcb4fdd0b5e8275182d605c3f58355~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f29c1a0f&amp;x-expires=1761570000&amp;x-signature=fMsjDJWGCDRvYUJ%2BAUJicCk9Vw4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229700225778453', 'createTime': 1758157689, 'createTimeISO': '2025-09-18T01:08:09.000Z', 'text': 'Jajajjaajajajjaa buenísimo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=408babe6&amp;x-expires=1761660000&amp;x-signature=Gb4ogNJxteo2A5Xaae7UwLa3mds%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4845,18 +4845,18 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jajajjaajajajjaa buenísimo</t>
+          <t>chevre el juego</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>45918.04732638889</v>
+        <v>45919.12591435185</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>01:08:09</t>
+          <t>03:01:19</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551229700225778453', 'createTime': 1758157689, 'createTimeISO': '2025-09-18T01:08:09.000Z', 'text': 'Jajajjaajajajjaa buenísimo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6819089554679940101', 'uniqueId': 'julianavivasr03', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f3051c41eba0cedcc184a155cdd5fe57~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0b3df464&amp;x-expires=1761570000&amp;x-signature=%2B5Kjk%2FNsFieX1m07yrNaeC%2FJ6u8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551629960492106503', 'createTime': 1758250879, 'createTimeISO': '2025-09-19T03:01:19.000Z', 'text': 'chevre el juego', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7428447431131857925', 'uniqueId': 'dario.bermudez.me', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e3f68c187a5bb898072670c79697373f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9cd54706&amp;x-expires=1761660000&amp;x-signature=%2FWAW2WFZo%2F%2FkevtWz4QIJ4QsYps%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551227674766607120', 'createTime': 1758157221, 'createTimeISO': '2025-09-18T01:00:21.000Z', 'text': '', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551227674766607120', 'createTime': 1758157221, 'createTimeISO': '2025-09-18T01:00:21.000Z', 'text': '', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d5b80d7&amp;x-expires=1761660000&amp;x-signature=Sd%2B5H5xHBcGJo50KbRbUW9h393c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551217905787978504', 'createTime': 1758155356, 'createTimeISO': '2025-09-18T00:29:16.000Z', 'text': '✨✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6933232569349653510', 'uniqueId': 'mariangel_alzate01', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6bab063f1c64d97abedc28d75951cd7~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7b547b2b&amp;x-expires=1761570000&amp;x-signature=Ufb6Vi0Zx4XLdTa9jzAUWN3Jbf0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551217905787978504', 'createTime': 1758155356, 'createTimeISO': '2025-09-18T00:29:16.000Z', 'text': '✨✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6933232569349653510', 'uniqueId': 'mariangel_alzate01', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6bab063f1c64d97abedc28d75951cd7~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d8b7e7a0&amp;x-expires=1761660000&amp;x-signature=ReC%2Bv6p2zsJw6T65St0eBj7jzT8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220042781573895', 'createTime': 1758155443, 'createTimeISO': '2025-09-18T00:30:43.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7503357568275285010', 'uniqueId': 'mara.alejandra.va13', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b0e9c531aa12326c2c39b489de39faaf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bbadeedd&amp;x-expires=1761570000&amp;x-signature=Ki0ovR4frSdtDWWmp5phxRthSG4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7551220042781573895', 'createTime': 1758155443, 'createTimeISO': '2025-09-18T00:30:43.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7503357568275285010', 'uniqueId': 'mara.alejandra.va13', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b0e9c531aa12326c2c39b489de39faaf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67c8d103&amp;x-expires=1761660000&amp;x-signature=6M8vO%2FP%2BdN%2BFunKRpEvWbWo23KQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5065,18 +5065,18 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>💗</t>
+          <t>😁</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>45928.03357638889</v>
+        <v>45933.99601851852</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>45928</v>
+        <v>45933</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>00:48:21</t>
+          <t>23:54:16</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7554935448256398088', 'createTime': 1759020501, 'createTimeISO': '2025-09-28T00:48:21.000Z', 'text': '💗', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452411908450108422', 'uniqueId': 'unatalgaby_17', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d31bb8b63795296e53c4901e56663b5d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8c9a8b03&amp;x-expires=1761570000&amp;x-signature=2vWbQGkyK9l26qpZ1OSUmcF60As%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557148031993807634', 'createTime': 1759535656, 'createTimeISO': '2025-10-03T23:54:16.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6927611184364356614', 'uniqueId': 'user0hhptpeva0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=86a16cb0&amp;x-expires=1761660000&amp;x-signature=2atCMukO7iwSqb7Vs0UJWDz25BE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7553402143257854727', 'createTime': 1758663504, 'createTimeISO': '2025-09-23T21:38:24.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6979791991334077446', 'uniqueId': 'lala_garzon0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/54f52760d8466c8575be7ac4ca3c5627~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=490cd65f&amp;x-expires=1761570000&amp;x-signature=xW14ZuCk6hK5%2FKR4OCZ%2BZ3bl2tw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7553402143257854727', 'createTime': 1758663504, 'createTimeISO': '2025-09-23T21:38:24.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6979791991334077446', 'uniqueId': 'lala_garzon0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/54f52760d8466c8575be7ac4ca3c5627~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0a3268ad&amp;x-expires=1761660000&amp;x-signature=wxGeZrLB%2FdNOkQeNw2vaU1%2BKFCk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557009575929938696', 'createTime': 1759503408, 'createTimeISO': '2025-10-03T14:56:48.000Z', 'text': '☺️☺️☺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9244ecc1&amp;x-expires=1761570000&amp;x-signature=NSDDd81hys0wPh8yt0LKPO%2BRR4M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557009575929938696', 'createTime': 1759503408, 'createTimeISO': '2025-10-03T14:56:48.000Z', 'text': '☺️☺️☺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808331911279903750', 'uniqueId': 'aleja.cardenas', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/ae26428fddeb4cb0c608c71af324941d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=177e07bc&amp;x-expires=1761660000&amp;x-signature=eNm3zt%2FX9MVM19isVvOraoBRoD4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5233,18 +5233,18 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>😁</t>
+          <t>💗</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>45933.99601851852</v>
+        <v>45928.03357638889</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>45933</v>
+        <v>45928</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>23:54:16</t>
+          <t>00:48:21</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7557148031993807634', 'createTime': 1759535656, 'createTimeISO': '2025-10-03T23:54:16.000Z', 'text': '😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6927611184364356614', 'uniqueId': 'user0hhptpeva0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/musically-maliva-obj/1594805258216454~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9150469a&amp;x-expires=1761570000&amp;x-signature=I7QHoT6ObfIaTjscYm99LxXk8Js%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7554935448256398088', 'createTime': 1759020501, 'createTimeISO': '2025-09-28T00:48:21.000Z', 'text': '💗', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452411908450108422', 'uniqueId': 'unatalgaby_17', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d31bb8b63795296e53c4901e56663b5d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d14fabbe&amp;x-expires=1761660000&amp;x-signature=yjG5UGtQ9WkVyN6%2Bw7syXLrqeoI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7552707432578876180', 'createTime': 1758502001, 'createTimeISO': '2025-09-22T00:46:41.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones y me ayudan a completar la colección de Mochis e ilumimochis (ayuden gente a que lo vean🥺)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=196af7c3&amp;x-expires=1761570000&amp;x-signature=mfmJCzSJseg0BUINUmeciufLGgM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'input': 'https://www.tiktok.com/@alpinacol/video/7551218859919822086', 'cid': '7552707432578876180', 'createTime': 1758502001, 'createTimeISO': '2025-09-22T00:46:41.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones y me ayudan a completar la colección de Mochis e ilumimochis (ayuden gente a que lo vean🥺)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d7d3025f&amp;x-expires=1761660000&amp;x-signature=tA0h7xmzMJont6v3WzoDB1g1%2BWI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -5345,22 +5345,22 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tooooooop✨</t>
+          <t>Súper aprobado jajajaja</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>45920.0344675926</v>
+        <v>45920.00429398148</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>00:49:38</t>
+          <t>00:06:11</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551967111200572161', 'createTime': 1758329378, 'createTimeISO': '2025-09-20T00:49:38.000Z', 'text': 'Tooooooop✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=67e127c0&amp;x-expires=1761570000&amp;x-signature=vPwM08FcKecDUNpRacSTSqBH8lw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551955913683682055', 'createTime': 1758326771, 'createTimeISO': '2025-09-20T00:06:11.000Z', 'text': 'Súper aprobado jajajaja', 'diggCount': 32, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b5403971a2c0063750a9b7140d15458b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=42b8f626&amp;x-expires=1761660000&amp;x-signature=acnEnY3yvru%2BwtJnMS89lX3Ol78%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5401,22 +5401,22 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Súper aprobado jajajaja</t>
+          <t>está kiut</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>45920.00429398148</v>
+        <v>45920.7575</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>00:06:11</t>
+          <t>18:10:48</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551955913683682055', 'createTime': 1758326771, 'createTimeISO': '2025-09-20T00:06:11.000Z', 'text': 'Súper aprobado jajajaja', 'diggCount': 32, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6774446029552354309', 'uniqueId': 'its.bri_ugc', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b5403971a2c0063750a9b7140d15458b~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3c8e7250&amp;x-expires=1761570000&amp;x-signature=UQMzZnJ%2FrlFhXJhZnlKl2gUk%2F7c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552235435209802503', 'createTime': 1758391848, 'createTimeISO': '2025-09-20T18:10:48.000Z', 'text': 'está kiut', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7406595235524690950', 'uniqueId': 'tatiana.r.rocha021328', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65263d812577fe31cc1016cb79e1e113~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4b4dc311&amp;x-expires=1761660000&amp;x-signature=TQzmUH6U%2BellMAbYLdm0iUqI6Mg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5457,22 +5457,22 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Me encantaaa!!!!! Aprobadooo</t>
+          <t>Apoyo muuuuuuuucho jajaja</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>45919.99805555555</v>
+        <v>45920.07915509259</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>45919</v>
+        <v>45920</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>23:57:12</t>
+          <t>01:53:59</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K90" t="n">
         <v>1</v>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551953579881202440', 'createTime': 1758326232, 'createTimeISO': '2025-09-19T23:57:12.000Z', 'text': 'Me encantaaa!!!!! Aprobadooo', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6806474480425796614', 'uniqueId': 'lrendon11', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65f278fccdfba09731ee15dda4e3cb13~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=55881956&amp;x-expires=1761570000&amp;x-signature=xm2LUG6oG5vbXC10gDn0cOb2CW4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983682992784136', 'createTime': 1758333239, 'createTimeISO': '2025-09-20T01:53:59.000Z', 'text': 'Apoyo muuuuuuuucho jajaja', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6577436033524727814', 'uniqueId': 'mafelovera', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7dea885196e9f4c245ffd2cb465a4c8a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=e2928c7c&amp;x-expires=1761660000&amp;x-signature=rIU3rSMu7pWcXF%2Fgo571QZVZkD0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5513,22 +5513,22 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mi primer mandato! Ajajjaa toda dictadora 😂😂</t>
+          <t>JAJAJAJAJA muuuuu</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>45921.60706018518</v>
+        <v>45920.71737268518</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>45921</v>
+        <v>45920</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14:34:10</t>
+          <t>17:13:01</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
         <v>1</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552550716473639700', 'createTime': 1758465250, 'createTimeISO': '2025-09-21T14:34:10.000Z', 'text': 'Mi primer mandato! Ajajjaa toda dictadora 😂😂', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7127494140724216838', 'uniqueId': 'marlinq23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7127494903172923398~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=da07acf4&amp;x-expires=1761570000&amp;x-signature=fRiF7O3JjhNtAgVd5%2FD2F4JDnE4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552220543425413944', 'createTime': 1758388381, 'createTimeISO': '2025-09-20T17:13:01.000Z', 'text': 'JAJAJAJAJA muuuuu', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bfade73a&amp;x-expires=1761660000&amp;x-signature=Owi5SAKC6UWu%2BV%2BwdCORYwA0t68%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5569,25 +5569,25 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏</t>
+          <t>Me encantaaa!!!!! Aprobadooo</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>45923.78701388889</v>
+        <v>45919.99805555555</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>45923</v>
+        <v>45919</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>18:53:18</t>
+          <t>23:57:12</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553359647815484167', 'createTime': 1758653598, 'createTimeISO': '2025-09-23T18:53:18.000Z', 'text': 'QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=895ae214&amp;x-expires=1761570000&amp;x-signature=sklHDUPVpgD%2BtJ6ZL2LNVhS9ie0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551953579881202440', 'createTime': 1758326232, 'createTimeISO': '2025-09-19T23:57:12.000Z', 'text': 'Me encantaaa!!!!! Aprobadooo', 'diggCount': 12, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6806474480425796614', 'uniqueId': 'lrendon11', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65f278fccdfba09731ee15dda4e3cb13~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5ad9467d&amp;x-expires=1761660000&amp;x-signature=G9AcW0H0cX3cIIx%2FdA9B%2ByCX0GA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5625,22 +5625,22 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Me encanta</t>
+          <t>QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>45925.74446759259</v>
+        <v>45923.78701388889</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>45925</v>
+        <v>45923</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>17:52:02</t>
+          <t>18:53:18</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554086009761415956', 'createTime': 1758822722, 'createTimeISO': '2025-09-25T17:52:02.000Z', 'text': 'Me encanta', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6824118381916079109', 'uniqueId': 'urg7348', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7333599963433140229~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4f912f19&amp;x-expires=1761570000&amp;x-signature=mmKTApPjoPQDzn8bbD9QJ7Ft%2Fss%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553359647815484167', 'createTime': 1758653598, 'createTimeISO': '2025-09-23T18:53:18.000Z', 'text': 'QUE VUELVA EL ALPILITRO 😭😭🙌🙌🙌🙏🙏', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7493133555746489351', 'uniqueId': 'andreykdy3', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ffdb73d8f0b1bc3e2a3bf54e4492d457~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=dc039374&amp;x-expires=1761660000&amp;x-signature=bG%2BECD71jf298byDd09qy%2FV%2BIbM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5681,26 +5681,26 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Increíbleeee</t>
+          <t>Mi primer mandato! Ajajjaa toda dictadora 😂😂</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>45922.29777777778</v>
+        <v>45921.60706018518</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>45922</v>
+        <v>45921</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>07:08:48</t>
+          <t>14:34:10</t>
         </is>
       </c>
       <c r="J94" t="n">
+        <v>6</v>
+      </c>
+      <c r="K94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
       <c r="L94" t="b">
         <v>0</v>
       </c>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552806947365241622', 'createTime': 1758524928, 'createTimeISO': '2025-09-22T07:08:48.000Z', 'text': 'Increíbleeee', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7251571663123465243', 'uniqueId': 'barbaramayan', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/58ed5201d3060082de17047de0ec72f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0d29e792&amp;x-expires=1761570000&amp;x-signature=4TP5c00vLmAa4zIE8PpmDHXegts%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552550716473639700', 'createTime': 1758465250, 'createTimeISO': '2025-09-21T14:34:10.000Z', 'text': 'Mi primer mandato! Ajajjaa toda dictadora 😂😂', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7127494140724216838', 'uniqueId': 'marlinq23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7127494903172923398~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=286bf325&amp;x-expires=1761660000&amp;x-signature=2fkGqh9iv20JZrSgwtmhcoDI4H8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5737,26 +5737,26 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Me encanta!</t>
+          <t>hola 😘</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>45927.95293981482</v>
+        <v>45919.98998842593</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>45927</v>
+        <v>45919</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>22:52:14</t>
+          <t>23:45:35</t>
         </is>
       </c>
       <c r="J95" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
       <c r="L95" t="b">
         <v>0</v>
       </c>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554905527273751314', 'createTime': 1759013534, 'createTimeISO': '2025-09-27T22:52:14.000Z', 'text': 'Me encanta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6817121247644124166', 'uniqueId': 'marsd195', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1afb497a92aa0ea23b48a8a687a97094~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=adfdb620&amp;x-expires=1761570000&amp;x-signature=IzG9TEtEJ9qHUW6c%2BoUAK7lRjVQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950541917881104', 'createTime': 1758325535, 'createTimeISO': '2025-09-19T23:45:35.000Z', 'text': 'hola 😘', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d5b80d7&amp;x-expires=1761660000&amp;x-signature=Sd%2B5H5xHBcGJo50KbRbUW9h393c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553033945219810055', 'createTime': 1758577775, 'createTimeISO': '2025-09-22T21:49:35.000Z', 'text': 'Empezó mi novela favorita😭😍', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd083daf&amp;x-expires=1761570000&amp;x-signature=Mj60V9kePw%2BGmIXKCvNAf2iQtmM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553033945219810055', 'createTime': 1758577775, 'createTimeISO': '2025-09-22T21:49:35.000Z', 'text': 'Empezó mi novela favorita😭😍', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=62c80d82&amp;x-expires=1761660000&amp;x-signature=gBB%2B%2FcC0j9jvb7UGIQeCpCEyzdY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5849,25 +5849,25 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Apoyo muuuuuuuucho jajaja</t>
+          <t>Pero verídico</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>45920.07915509259</v>
+        <v>45921.13072916667</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>45920</v>
+        <v>45921</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>01:53:59</t>
+          <t>03:08:15</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983682992784136', 'createTime': 1758333239, 'createTimeISO': '2025-09-20T01:53:59.000Z', 'text': 'Apoyo muuuuuuuucho jajaja', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6577436033524727814', 'uniqueId': 'mafelovera', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7dea885196e9f4c245ffd2cb465a4c8a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ef91bd35&amp;x-expires=1761570000&amp;x-signature=Ur9NQy0qbxMscSdL1dM6GgykKX4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552373947406664455', 'createTime': 1758424095, 'createTimeISO': '2025-09-21T03:08:15.000Z', 'text': 'Pero verídico', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6916307664519742470', 'uniqueId': 'daniel_rojas.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/1b1931cd030125ddc18f8e0cba099651~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e1e6d26&amp;x-expires=1761660000&amp;x-signature=fQVAp39ozySVwzdXFpiFHCKMeiE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5905,25 +5905,25 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>hola 😘</t>
+          <t>Increíbleeee</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>45919.98998842593</v>
+        <v>45922.29777777778</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>23:45:35</t>
+          <t>07:08:48</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950541917881104', 'createTime': 1758325535, 'createTimeISO': '2025-09-19T23:45:35.000Z', 'text': 'hola 😘', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552806947365241622', 'createTime': 1758524928, 'createTimeISO': '2025-09-22T07:08:48.000Z', 'text': 'Increíbleeee', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7251571663123465243', 'uniqueId': 'barbaramayan', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/58ed5201d3060082de17047de0ec72f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b8368900&amp;x-expires=1761660000&amp;x-signature=ykzya%2B5F9E9ZG4%2FYIf1ZwBREmWI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -5961,22 +5961,22 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lindo</t>
+          <t>mi mami trabaja en alpina y me trajo Mochis 🥰</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>45920.64417824074</v>
+        <v>45924.08138888889</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>45920</v>
+        <v>45924</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>15:27:37</t>
+          <t>01:57:12</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552193394950685448', 'createTime': 1758382057, 'createTimeISO': '2025-09-20T15:27:37.000Z', 'text': 'Lindo', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6747056373932590086', 'uniqueId': 'monimarpor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327496776705933318~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2bbedc1a&amp;x-expires=1761570000&amp;x-signature=mhmIGPkItx%2B9SVR8Jd%2Fhol0ntGE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553468863707759377', 'createTime': 1758679032, 'createTimeISO': '2025-09-24T01:57:12.000Z', 'text': 'mi mami trabaja en alpina y me trajo Mochis 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6796362843291354118', 'uniqueId': 'sampreds', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6ab46faa73ba2a267e5c627e7857a09a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ca5bf405&amp;x-expires=1761660000&amp;x-signature=AqU9%2FMJQOHyQXUErvhpb7gDQ8NE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6017,18 +6017,18 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pero verídico</t>
+          <t>Me encanta!</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>45921.13072916667</v>
+        <v>45927.95293981482</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>45921</v>
+        <v>45927</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>03:08:15</t>
+          <t>22:52:14</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552373947406664455', 'createTime': 1758424095, 'createTimeISO': '2025-09-21T03:08:15.000Z', 'text': 'Pero verídico', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6916307664519742470', 'uniqueId': 'daniel_rojas.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/1b1931cd030125ddc18f8e0cba099651~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=653205f6&amp;x-expires=1761570000&amp;x-signature=pNG6fgE0pL%2FNWwZqCCC%2FcsRA%2FUk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554905527273751314', 'createTime': 1759013534, 'createTimeISO': '2025-09-27T22:52:14.000Z', 'text': 'Me encanta!', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6817121247644124166', 'uniqueId': 'marsd195', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1afb497a92aa0ea23b48a8a687a97094~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=456e568a&amp;x-expires=1761660000&amp;x-signature=BfTCO8NCs9Vh%2FqFqknMSR3Fed1Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6073,25 +6073,25 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>hola</t>
+          <t>alpina q es esta hermosura</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>45919.99099537037</v>
+        <v>45923.97987268519</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>23:47:02</t>
+          <t>23:31:01</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950956708922130', 'createTime': 1758325622, 'createTimeISO': '2025-09-19T23:47:02.000Z', 'text': 'hola', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f9e9987c&amp;x-expires=1761570000&amp;x-signature=p%2FE07rUH8alxIxevM29aaBzUoMk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553431107175662354', 'createTime': 1758670261, 'createTimeISO': '2025-09-23T23:31:01.000Z', 'text': 'alpina q es esta hermosura', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7246183829702034437', 'uniqueId': '2s_sarah', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a9bc5c82ba1c64cdd2810f102faf0c8f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f50d5d4e&amp;x-expires=1761660000&amp;x-signature=RqFDyjb%2BC8Q4dppP2rrv6mAPZsY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6129,25 +6129,25 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Siiii</t>
+          <t>Amooooooooo ✨❤</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>45920.26096064815</v>
+        <v>45920.63488425926</v>
       </c>
       <c r="H102" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>06:15:47</t>
+          <t>15:14:14</t>
         </is>
       </c>
       <c r="J102" t="n">
         <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552051172909024016', 'createTime': 1758348947, 'createTimeISO': '2025-09-20T06:15:47.000Z', 'text': 'Siiii', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781933506022491142', 'uniqueId': 'carovelez_9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9bafd1d600cb2409f94c1df9050c163d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bc132d05&amp;x-expires=1761570000&amp;x-signature=quB1EzmpV5Z59%2Fa5Yo3WQxuM12w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552189950164157202', 'createTime': 1758381254, 'createTimeISO': '2025-09-20T15:14:14.000Z', 'text': 'Amooooooooo ✨❤', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f6605c92&amp;x-expires=1761660000&amp;x-signature=qdjs%2Fm2rO9t8shvLDOPSLOHgPIo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6185,25 +6185,25 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Amooooooooo ✨❤</t>
+          <t>Siiii</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>45920.63488425926</v>
+        <v>45920.26096064815</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>15:14:14</t>
+          <t>06:15:47</t>
         </is>
       </c>
       <c r="J103" t="n">
         <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552189950164157202', 'createTime': 1758381254, 'createTimeISO': '2025-09-20T15:14:14.000Z', 'text': 'Amooooooooo ✨❤', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6775204820329579525', 'uniqueId': 'danivalenciaa', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/16f06ae19c05a3c06f041a0a4078e97e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a94ad8b3&amp;x-expires=1761570000&amp;x-signature=OpO%2BwRtnjY5miabvZsvSJtDKmxQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552051172909024016', 'createTime': 1758348947, 'createTimeISO': '2025-09-20T06:15:47.000Z', 'text': 'Siiii', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781933506022491142', 'uniqueId': 'carovelez_9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9bafd1d600cb2409f94c1df9050c163d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b52ccaf5&amp;x-expires=1761660000&amp;x-signature=jJ%2B1Zl518tTlCGm8MPwwkoCmhas%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6241,22 +6241,22 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>JAJAJAJAJA muuuuu</t>
+          <t>Tooooooop✨</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>45920.71737268518</v>
+        <v>45920.0344675926</v>
       </c>
       <c r="H104" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>17:13:01</t>
+          <t>00:49:38</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552220543425413944', 'createTime': 1758388381, 'createTimeISO': '2025-09-20T17:13:01.000Z', 'text': 'JAJAJAJAJA muuuuu', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9318afca&amp;x-expires=1761570000&amp;x-signature=vuOKTe6NBdJzzn2l%2FGqo1IGgWyM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551967111200572161', 'createTime': 1758329378, 'createTimeISO': '2025-09-20T00:49:38.000Z', 'text': 'Tooooooop✨', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6636032545857355782', 'uniqueId': 'amygonzal_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bcf09f13282d39a21e796330dfd9b28d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3f2d084a&amp;x-expires=1761660000&amp;x-signature=yH%2Buv%2BRYFJlZOh1fqCRT4wpGJAI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6297,25 +6297,25 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>está kiut</t>
+          <t>hola</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>45920.7575</v>
+        <v>45919.99099537037</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>45920</v>
+        <v>45919</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>18:10:48</t>
+          <t>23:47:02</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552235435209802503', 'createTime': 1758391848, 'createTimeISO': '2025-09-20T18:10:48.000Z', 'text': 'está kiut', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7406595235524690950', 'uniqueId': 'tatiana.r.rocha021328', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/65263d812577fe31cc1016cb79e1e113~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=62d8526b&amp;x-expires=1761570000&amp;x-signature=l76cozSCbSE4SHR2iEodDZpJH8E%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950956708922130', 'createTime': 1758325622, 'createTimeISO': '2025-09-19T23:47:02.000Z', 'text': 'hola', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7416452271041987590', 'uniqueId': 'saragutierrez9607', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2d50ff98a95e65e1155080427e14139e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b7afaa35&amp;x-expires=1761660000&amp;x-signature=wMf02rb7Z8Czo1Gt9sqbouR0Cnk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6353,25 +6353,25 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Me encanta el Muuuuuuu💖</t>
+          <t>Lindo</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>45920.03078703704</v>
+        <v>45920.64417824074</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>00:44:20</t>
+          <t>15:27:37</t>
         </is>
       </c>
       <c r="J106" t="n">
         <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551965699524461330', 'createTime': 1758329060, 'createTimeISO': '2025-09-20T00:44:20.000Z', 'text': 'Me encanta el Muuuuuuu💖', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552193394950685448', 'createTime': 1758382057, 'createTimeISO': '2025-09-20T15:27:37.000Z', 'text': 'Lindo', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6747056373932590086', 'uniqueId': 'monimarpor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7327496776705933318~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=160b74a0&amp;x-expires=1761660000&amp;x-signature=vtGBl9MMKc9BxgunSjGYKwLbVPw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6409,25 +6409,25 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>amo este muuuuuuundoo😏</t>
+          <t>Me encanta</t>
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>45920.07972222222</v>
+        <v>45925.74446759259</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>45920</v>
+        <v>45925</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>01:54:48</t>
+          <t>17:52:02</t>
         </is>
       </c>
       <c r="J107" t="n">
         <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983930652689172', 'createTime': 1758333288, 'createTimeISO': '2025-09-20T01:54:48.000Z', 'text': 'amo este muuuuuuundoo😏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6842674101811954693', 'uniqueId': 'lizz_fndz', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f5a7346c0b99528e0b975fc998230121~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=38b806ba&amp;x-expires=1761570000&amp;x-signature=%2BcHQVvaJOdEcFnUx%2BtJiMvhS%2BIg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554086009761415956', 'createTime': 1758822722, 'createTimeISO': '2025-09-25T17:52:02.000Z', 'text': 'Me encanta', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6824118381916079109', 'uniqueId': 'urg7348', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7333599963433140229~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=478a9a04&amp;x-expires=1761660000&amp;x-signature=auTtZap5ZPTS%2Bybay8lxRsQrPCc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6465,25 +6465,25 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>mi mami trabaja en alpina y me trajo Mochis 🥰</t>
+          <t>Me encanta el Muuuuuuu💖</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>45924.08138888889</v>
+        <v>45920.03078703704</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>45924</v>
+        <v>45920</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>01:57:12</t>
+          <t>00:44:20</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553468863707759377', 'createTime': 1758679032, 'createTimeISO': '2025-09-24T01:57:12.000Z', 'text': 'mi mami trabaja en alpina y me trajo Mochis 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6796362843291354118', 'uniqueId': 'sampreds', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6ab46faa73ba2a267e5c627e7857a09a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4008d23a&amp;x-expires=1761570000&amp;x-signature=S%2FBMB9yMn78%2BP%2BorGNNIlzamWIY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551965699524461330', 'createTime': 1758329060, 'createTimeISO': '2025-09-20T00:44:20.000Z', 'text': 'Me encanta el Muuuuuuu💖', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2bac3cd2&amp;x-expires=1761660000&amp;x-signature=WEArl9n59Fp%2BiSxBaRnvAI77Xfs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6521,22 +6521,22 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ME ENCANTA✨✨</t>
+          <t>amo este muuuuuuundoo😏</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>45920.06896990741</v>
+        <v>45920.07972222222</v>
       </c>
       <c r="H109" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>01:39:19</t>
+          <t>01:54:48</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" t="n">
         <v>1</v>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551979924456211207', 'createTime': 1758332359, 'createTimeISO': '2025-09-20T01:39:19.000Z', 'text': 'ME ENCANTA✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551983930652689172', 'createTime': 1758333288, 'createTimeISO': '2025-09-20T01:54:48.000Z', 'text': 'amo este muuuuuuundoo😏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6842674101811954693', 'uniqueId': 'lizz_fndz', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/f5a7346c0b99528e0b975fc998230121~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b5d757b2&amp;x-expires=1761660000&amp;x-signature=ePh36s8%2FiPlDmLmFvxJgMybrzrY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6577,18 +6577,18 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>aprobadooo, amooo</t>
+          <t>Me gusta MUUUUUcho</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>45920.64584490741</v>
+        <v>45920.63900462963</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>15:30:01</t>
+          <t>15:20:10</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552194010451477269', 'createTime': 1758382201, 'createTimeISO': '2025-09-20T15:30:01.000Z', 'text': 'aprobadooo, amooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=109ea6b2&amp;x-expires=1761570000&amp;x-signature=rf95%2BkUaV%2Fv4O%2FPzSATd4vhGdvA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552191427935208203', 'createTime': 1758381610, 'createTimeISO': '2025-09-20T15:20:10.000Z', 'text': 'Me gusta MUUUUUcho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6786345043017958405', 'uniqueId': 'rafaelladm_', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/73cfb3946b471a5575a9bd8db504145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a5a48b4b&amp;x-expires=1761660000&amp;x-signature=JxOyDFV3iDGZ02NJ4IpYHYz%2FLJg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6633,25 +6633,25 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>ME ENCANTA✨✨</t>
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>45925.80569444445</v>
+        <v>45920.06896990741</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>45925</v>
+        <v>45920</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>19:20:12</t>
+          <t>01:39:19</t>
         </is>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554108742757827346', 'createTime': 1758828012, 'createTimeISO': '2025-09-25T19:20:12.000Z', 'text': 'Si', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7472435716635902996', 'uniqueId': 'saraisabellamolin21', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a143062aac046151f845e8a7d43027c0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=39b83097&amp;x-expires=1761570000&amp;x-signature=L%2BxjMYCn2%2F4pDDLH8XOrdTmGSdA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551979924456211207', 'createTime': 1758332359, 'createTimeISO': '2025-09-20T01:39:19.000Z', 'text': 'ME ENCANTA✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=638b7f00&amp;x-expires=1761660000&amp;x-signature=FU7F41cZGJuNGgPqq9ZMLtFsmTE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6689,18 +6689,18 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Me gusta MUUUUUcho</t>
+          <t>aprobadooo, amooo</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>45920.63900462963</v>
+        <v>45920.64584490741</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>15:20:10</t>
+          <t>15:30:01</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552191427935208203', 'createTime': 1758381610, 'createTimeISO': '2025-09-20T15:20:10.000Z', 'text': 'Me gusta MUUUUUcho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6786345043017958405', 'uniqueId': 'rafaelladm_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/73cfb3946b471a5575a9bd8db504145d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=da843faf&amp;x-expires=1761570000&amp;x-signature=8igBwrDyEN7%2FUy%2BlGRk%2FQE0ANMw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552194010451477269', 'createTime': 1758382201, 'createTimeISO': '2025-09-20T15:30:01.000Z', 'text': 'aprobadooo, amooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6770401168398386182', 'uniqueId': 'gabrielaguerrero70', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a36d643d0a9ecc0cdaafc93b6200aa8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b91862a7&amp;x-expires=1761660000&amp;x-signature=VKLkGZ3SJ4c6cyYpq22yKwTHDho%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6745,25 +6745,25 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Califiquen mi nuevo mochi saurio!!!💗</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>45922.05614583333</v>
+        <v>45925.80569444445</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>01:20:51</t>
+          <t>19:20:12</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552717306100761351', 'createTime': 1758504051, 'createTimeISO': '2025-09-22T01:20:51.000Z', 'text': 'Califiquen mi nuevo mochi saurio!!!💗', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7025228362498999301', 'uniqueId': 'krystelnavarrober', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3da7823061496f0246300c1ee868876f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=55f61d03&amp;x-expires=1761570000&amp;x-signature=lhZ9iWpl%2F4WLBD2yommpMC4NXFk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7554108742757827346', 'createTime': 1758828012, 'createTimeISO': '2025-09-25T19:20:12.000Z', 'text': 'Si', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7472435716635902996', 'uniqueId': 'saraisabellamolin21', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a143062aac046151f845e8a7d43027c0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f8633a33&amp;x-expires=1761660000&amp;x-signature=OR%2Fg5er%2B6fWqxjFIEWU67p3v10Q%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6801,25 +6801,25 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>✅✅✅</t>
+          <t>Califiquen mi nuevo mochi saurio!!!💗</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>45920.11243055556</v>
+        <v>45922.05614583333</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>45920</v>
+        <v>45922</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>02:41:54</t>
+          <t>01:20:51</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551996069400838930', 'createTime': 1758336114, 'createTimeISO': '2025-09-20T02:41:54.000Z', 'text': '✅✅✅', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775228984448959493', 'uniqueId': 'francescalvarezr_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2e5e4150ee1705a086acc14bc21b08d4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5c2b3c5a&amp;x-expires=1761570000&amp;x-signature=X%2Byd5RdZp8zezdsTCEC0puSFCAc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552717306100761351', 'createTime': 1758504051, 'createTimeISO': '2025-09-22T01:20:51.000Z', 'text': 'Califiquen mi nuevo mochi saurio!!!💗', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7025228362498999301', 'uniqueId': 'krystelnavarrober', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3da7823061496f0246300c1ee868876f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1148e248&amp;x-expires=1761660000&amp;x-signature=4HKt6rnDRRbUOyIVyKLwY2%2FqPt4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6857,22 +6857,22 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>🥰</t>
+          <t>✅✅✅</t>
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>45920.60407407407</v>
+        <v>45920.11243055556</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>14:29:52</t>
+          <t>02:41:54</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552178343107592961', 'createTime': 1758378592, 'createTimeISO': '2025-09-20T14:29:52.000Z', 'text': '🥰', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806405540710351877', 'uniqueId': 'karenmarcelagarzo', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326838454582460422~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=47ac6a54&amp;x-expires=1761570000&amp;x-signature=HAxM632oE7zW3uTlf%2BkON5VAO9c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551996069400838930', 'createTime': 1758336114, 'createTimeISO': '2025-09-20T02:41:54.000Z', 'text': '✅✅✅', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6775228984448959493', 'uniqueId': 'francescalvarezr_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2e5e4150ee1705a086acc14bc21b08d4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fe08a662&amp;x-expires=1761660000&amp;x-signature=LgdWMpFtXagzYvEZ100%2FScecaXQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6913,18 +6913,18 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>alpina q es esta hermosura</t>
+          <t>🥰</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>45923.97987268519</v>
+        <v>45920.60407407407</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>45923</v>
+        <v>45920</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>23:31:01</t>
+          <t>14:29:52</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7553431107175662354', 'createTime': 1758670261, 'createTimeISO': '2025-09-23T23:31:01.000Z', 'text': 'alpina q es esta hermosura', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7246183829702034437', 'uniqueId': '2s_sarah', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a9bc5c82ba1c64cdd2810f102faf0c8f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=6f305374&amp;x-expires=1761570000&amp;x-signature=tZGnQyH21TPiCLp%2BG4PCbk2bu1M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552178343107592961', 'createTime': 1758378592, 'createTimeISO': '2025-09-20T14:29:52.000Z', 'text': '🥰', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806405540710351877', 'uniqueId': 'karenmarcelagarzo', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326838454582460422~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=162265d6&amp;x-expires=1761660000&amp;x-signature=4%2BT4JmeC4JyE7lu8jbjjVM1iTiA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -6969,25 +6969,25 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>🥰🥰🥰</t>
+          <t>Wow! Que cracks</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>45919.98965277777</v>
+        <v>45920.13050925926</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>45919</v>
+        <v>45920</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>23:45:06</t>
+          <t>03:07:56</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950414629061394', 'createTime': 1758325506, 'createTimeISO': '2025-09-19T23:45:06.000Z', 'text': '🥰🥰🥰', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830514363565278214', 'uniqueId': 'mariafernandasalc02', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/f48ef1c788191659fa2e09d032706b87~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a75aafc6&amp;x-expires=1761570000&amp;x-signature=Y6t23RsXTVBSuvmA8%2FClRygnGHE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552002771790136071', 'createTime': 1758337676, 'createTimeISO': '2025-09-20T03:07:56.000Z', 'text': 'Wow! Que cracks', 'diggCount': 4, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6761789459468403717', 'uniqueId': 'mariajimenadiaz5', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/7334740815043887110~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=995dda9d&amp;x-expires=1761660000&amp;x-signature=r86YkR0z%2BbBnVtZxVXtbODpK7iE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7025,25 +7025,25 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>🥺</t>
+          <t>Me encantaaaa</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>45928.61208333333</v>
+        <v>45920.30841435185</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>45928</v>
+        <v>45920</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>14:41:24</t>
+          <t>07:24:07</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7555150174504469266', 'createTime': 1759070484, 'createTimeISO': '2025-09-28T14:41:24.000Z', 'text': '🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6891441655778624518', 'uniqueId': 'kris_salazar23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/76c1e9d5f762548bf55f86a2eeb72fa3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=33d0542e&amp;x-expires=1761570000&amp;x-signature=BgFnq8zWBkFQ6iHiC4l9JXd%2FNDg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552068707821749048', 'createTime': 1758353047, 'createTimeISO': '2025-09-20T07:24:07.000Z', 'text': 'Me encantaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6572155711261966341', 'uniqueId': 'renata.garces', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/0e4e281eab3b0fe02f45e37f8562c901~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=d498c3f3&amp;x-expires=1761660000&amp;x-signature=eN%2B%2B4DMMSXQYaxma7F2I7Y%2BENdg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7085,18 +7085,18 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>45934.13739583334</v>
+        <v>45919.98965277777</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>45934</v>
+        <v>45919</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>03:17:51</t>
+          <t>23:45:06</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7557200531950256903', 'createTime': 1759547871, 'createTimeISO': '2025-10-04T03:17:51.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7368157374302946309', 'uniqueId': 'jeronimoo334', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4853e0d53cbeb9e2a1c9346cf5e1b179~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4ad94db8&amp;x-expires=1761570000&amp;x-signature=%2FU3XlyNvrmDtgwMU2C7XdWG43dM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7551950414629061394', 'createTime': 1758325506, 'createTimeISO': '2025-09-19T23:45:06.000Z', 'text': '🥰🥰🥰', 'diggCount': 2, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6830514363565278214', 'uniqueId': 'mariafernandasalc02', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/f48ef1c788191659fa2e09d032706b87~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=903c4f13&amp;x-expires=1761660000&amp;x-signature=fricjFb%2FzDIsQLehj4WMDFzFEis%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7137,18 +7137,18 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>😅</t>
+          <t>🥰🥰🥰</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>45937.14810185185</v>
+        <v>45934.13739583334</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>45937</v>
+        <v>45934</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>03:33:16</t>
+          <t>03:17:51</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558317759676121874', 'createTime': 1759807996, 'createTimeISO': '2025-10-07T03:33:16.000Z', 'text': '😅', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6842107016141751301', 'uniqueId': 'pandrea9610', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7325541937888952325~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=77b2de12&amp;x-expires=1761570000&amp;x-signature=8fHcH93hZBWvJIgjEaZW8yOExBU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7557200531950256903', 'createTime': 1759547871, 'createTimeISO': '2025-10-04T03:17:51.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7368157374302946309', 'uniqueId': 'jeronimoo334', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4853e0d53cbeb9e2a1c9346cf5e1b179~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2799c662&amp;x-expires=1761660000&amp;x-signature=92AHHwS4dpYsOE4xtYviC8K7KJM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7193,25 +7193,25 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wow! Que cracks</t>
+          <t>😅</t>
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>45920.13050925926</v>
+        <v>45937.14810185185</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>45920</v>
+        <v>45937</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>03:07:56</t>
+          <t>03:33:16</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552002771790136071', 'createTime': 1758337676, 'createTimeISO': '2025-09-20T03:07:56.000Z', 'text': 'Wow! Que cracks', 'diggCount': 4, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6761789459468403717', 'uniqueId': 'mariajimenadiaz5', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/7334740815043887110~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=956df52c&amp;x-expires=1761570000&amp;x-signature=JZqRLRkaLRTPzCKLOdfwf5Vq7LY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558317759676121874', 'createTime': 1759807996, 'createTimeISO': '2025-10-07T03:33:16.000Z', 'text': '😅', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6842107016141751301', 'uniqueId': 'pandrea9610', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7325541937888952325~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=504c14e6&amp;x-expires=1761660000&amp;x-signature=CjSoI9rEmBz%2FtSrJbuZUK601Yzw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7249,25 +7249,25 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Me encantaaaa</t>
+          <t>Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>45920.30841435185</v>
+        <v>45937.91074074074</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>45920</v>
+        <v>45937</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>07:24:07</t>
+          <t>21:51:28</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552068707821749048', 'createTime': 1758353047, 'createTimeISO': '2025-09-20T07:24:07.000Z', 'text': 'Me encantaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6572155711261966341', 'uniqueId': 'renata.garces', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/0e4e281eab3b0fe02f45e37f8562c901~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=ef068d0e&amp;x-expires=1761570000&amp;x-signature=5PqrnlmwE1xbzj6ngZ4REEzBDQY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558600728525275934', 'createTime': 1759873888, 'createTimeISO': '2025-10-07T21:51:28.000Z', 'text': 'Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '130977736172539904', 'uniqueId': 'giraldotogaby', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-useast5-avt-0068-tx/a2c5a1fbbbc85ff0c2c73bd1842eb1cc~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2ee3688d&amp;x-expires=1761660000&amp;x-signature=Gy9pz%2Fa3gtriPE6zpDtrw73ANNA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -7305,25 +7305,25 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨</t>
+          <t>🥺</t>
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>45937.91074074074</v>
+        <v>45928.61208333333</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>45937</v>
+        <v>45928</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>21:51:28</t>
+          <t>14:41:24</t>
         </is>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7558600728525275934', 'createTime': 1759873888, 'createTimeISO': '2025-10-07T21:51:28.000Z', 'text': 'Holaaa!! ¿Cuánto tiempo tarda en finalizar los filtros de la convocatoria? @Alpina 🐮 ✨✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '130977736172539904', 'uniqueId': 'giraldotogaby', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/a2c5a1fbbbc85ff0c2c73bd1842eb1cc~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=3363bec1&amp;x-expires=1761570000&amp;x-signature=8lWgdcIhm5lq1URisMtYb3cuWtA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7555150174504469266', 'createTime': 1759070484, 'createTimeISO': '2025-09-28T14:41:24.000Z', 'text': '🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6891441655778624518', 'uniqueId': 'kris_salazar23', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/76c1e9d5f762548bf55f86a2eeb72fa3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=66237f50&amp;x-expires=1761660000&amp;x-signature=eDpzOGQWzMlR1Qxw4IjMTU%2BM0no%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552706319259435783', 'createTime': 1758501808, 'createTimeISO': '2025-09-22T00:43:28.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones acá en el vídeo y me mandasla nueva colección de los mochis dinosaurios (ayuden que lo vean🙊)', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=196af7c3&amp;x-expires=1761570000&amp;x-signature=mfmJCzSJseg0BUINUmeciufLGgM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'input': 'https://www.tiktok.com/@alpinacol/video/7551949227333635339', 'cid': '7552706319259435783', 'createTime': 1758501808, 'createTimeISO': '2025-09-22T00:43:28.000Z', 'text': '@Alpina 🐮 cuantos comentarios y reacciones acá en el vídeo y me mandasla nueva colección de los mochis dinosaurios (ayuden que lo vean🙊)', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6915493889098187782', 'uniqueId': 'angel18mendoza', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/68f808039457cd87fd4d7b94e867d357~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d7d3025f&amp;x-expires=1761660000&amp;x-signature=tA0h7xmzMJont6v3WzoDB1g1%2BWI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -7417,25 +7417,25 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀</t>
+          <t>Mi sueñoooo 😩 ya quiero hacer parte de ustedes</t>
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>45926.65694444445</v>
+        <v>45925.08212962963</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>45926</v>
+        <v>45925</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>15:46:00</t>
+          <t>01:58:16</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554424648151941905', 'createTime': 1758901560, 'createTimeISO': '2025-09-26T15:46:00.000Z', 'text': 'Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7436539205088396344', 'uniqueId': 'isaac_mora1903', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bd074fbf9f61ee99fcea8ef5f350b2bf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=49e69c97&amp;x-expires=1761570000&amp;x-signature=qlqMqsO1TGLI5UjxJVxDBWpMGj4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553840238716945153', 'createTime': 1758765496, 'createTimeISO': '2025-09-25T01:58:16.000Z', 'text': 'Mi sueñoooo 😩 ya quiero hacer parte de ustedes', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c794ea9c&amp;x-expires=1761660000&amp;x-signature=sB2GhCshW5CvGVZX0LaXIDSL9hI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7473,18 +7473,18 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>nueva presentación 😳!</t>
+          <t>Alpinaa salúdame</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>45925.20309027778</v>
+        <v>45932.13111111111</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>45925</v>
+        <v>45932</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>04:52:27</t>
+          <t>03:08:48</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553885128557478672', 'createTime': 1758775947, 'createTimeISO': '2025-09-25T04:52:27.000Z', 'text': 'nueva presentación 😳!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556456003958588178', 'createTime': 1759374528, 'createTimeISO': '2025-10-02T03:08:48.000Z', 'text': 'Alpinaa salúdame', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6783863549585867782', 'uniqueId': 'ciro_492', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a1c71fe90e3afc45b76f3656558f0dae~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=cbb0a6b9&amp;x-expires=1761660000&amp;x-signature=G%2B2c34zdgNZoV%2BIwQKTDZ%2FJmGYY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7529,22 +7529,22 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>cuando llegan a Perú los Mochis 😭😭</t>
+          <t>Gran historia jajajaja 🥳</t>
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>45927.6415625</v>
+        <v>45925.03746527778</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>45927</v>
+        <v>45925</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>15:23:51</t>
+          <t>00:53:57</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554790021015946005', 'createTime': 1758986631, 'createTimeISO': '2025-09-27T15:23:51.000Z', 'text': 'cuando llegan a Perú los Mochis 😭😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7093344759511532549', 'uniqueId': 'hanzel3075', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e5fc427c21f18dd65a5d6366a919b2b8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a36ccb6f&amp;x-expires=1761570000&amp;x-signature=qPN%2F2nsESTmE2vKSFc2bn1%2FPU0Y%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553823647435178770', 'createTime': 1758761637, 'createTimeISO': '2025-09-25T00:53:57.000Z', 'text': 'Gran historia jajajaja 🥳', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=acff92c2&amp;x-expires=1761660000&amp;x-signature=OdurVojxAvIT21gS4zM1aVWf13I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7585,18 +7585,18 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>estando en etapa lectiva puedo aplicar gracias</t>
+          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>45926.77866898148</v>
+        <v>45950.08873842593</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>45926</v>
+        <v>45950</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>18:41:17</t>
+          <t>02:07:47</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554469785704645384', 'createTime': 1758912077, 'createTimeISO': '2025-09-26T18:41:17.000Z', 'text': 'estando en etapa lectiva puedo aplicar gracias', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=30df542e&amp;x-expires=1761570000&amp;x-signature=ePCGB9BrUbZkPVx3h%2BelHiRBM9o%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7563119838848598792', 'createTime': 1760926067, 'createTimeISO': '2025-10-20T02:07:47.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2ca9f7dc&amp;x-expires=1761660000&amp;x-signature=unZQm11UctBVLTK%2BcAJEK89ByYE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7641,25 +7641,25 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos</t>
+          <t>nueva presentación 😳!</t>
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>45925.06542824074</v>
+        <v>45925.20309027778</v>
       </c>
       <c r="H129" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>01:34:13</t>
+          <t>04:52:27</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553834039527654152', 'createTime': 1758764053, 'createTimeISO': '2025-09-25T01:34:13.000Z', 'text': 'Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553885128557478672', 'createTime': 1758775947, 'createTimeISO': '2025-09-25T04:52:27.000Z', 'text': 'nueva presentación 😳!', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d5b80d7&amp;x-expires=1761660000&amp;x-signature=Sd%2B5H5xHBcGJo50KbRbUW9h393c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7697,25 +7697,25 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año</t>
+          <t>Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>45950.08873842593</v>
+        <v>45925.06542824074</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>45950</v>
+        <v>45925</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>02:07:47</t>
+          <t>01:34:13</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7563119838848598792', 'createTime': 1760926067, 'createTimeISO': '2025-10-20T02:07:47.000Z', 'text': 'Hola, debo estar en la universidad para entrar? Quisiera entrar el próximo año pero me graduó este año', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532073308303660032', 'uniqueId': 'marimar1707_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/ecab724fac1b9a8b98bef5bad85fbad2~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ef9ccaf3&amp;x-expires=1761570000&amp;x-signature=OsrEaDn9tPollUWncoSd9dptQY0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553834039527654152', 'createTime': 1758764053, 'createTimeISO': '2025-09-25T01:34:13.000Z', 'text': 'Pregunta cuantos minimochis tienes 💖 quiero tenerlos todos', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bf2b7644&amp;x-expires=1761660000&amp;x-signature=yZD%2FMO4CbddWm9rSlQrPE7xbfC4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7753,22 +7753,22 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gran historia jajajaja 🥳</t>
+          <t>También reciben pasantes?</t>
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>45925.03746527778</v>
+        <v>45954.7812962963</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>45925</v>
+        <v>45954</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>00:53:57</t>
+          <t>18:45:04</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553823647435178770', 'createTime': 1758761637, 'createTimeISO': '2025-09-25T00:53:57.000Z', 'text': 'Gran historia jajajaja 🥳', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6781206829306807302', 'uniqueId': 'gaaaabs6', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2a7fc8c65b0dd0d7a44653d5b817e337~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fca43208&amp;x-expires=1761570000&amp;x-signature=7PCAh1YNOe1EBw2Jm7BcvnE8Ep8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7564861171879445256', 'createTime': 1761331504, 'createTimeISO': '2025-10-24T18:45:04.000Z', 'text': 'También reciben pasantes?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '166386831993888768', 'uniqueId': 'aleja040610', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/d38de0738e43e8e0ce00becaad0aca08~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=aa5f9c7b&amp;x-expires=1761660000&amp;x-signature=0i%2FVUNB5FeTS1Pu4cl5%2BjY71aXw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7809,25 +7809,25 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Es cierto que debajo de la cabaña hay un tunel secreto?👀</t>
+          <t>una pregunta las personas del Sena pueden estar en Alpina</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>45925.02155092593</v>
+        <v>45925.33574074074</v>
       </c>
       <c r="H132" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>00:31:02</t>
+          <t>08:03:28</t>
         </is>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553817757574349576', 'createTime': 1758760262, 'createTimeISO': '2025-09-25T00:31:02.000Z', 'text': 'Es cierto que debajo de la cabaña hay un tunel secreto?👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=fd083daf&amp;x-expires=1761570000&amp;x-signature=Mj60V9kePw%2BGmIXKCvNAf2iQtmM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553933847436772104', 'createTime': 1758787408, 'createTimeISO': '2025-09-25T08:03:28.000Z', 'text': 'una pregunta las personas del Sena pueden estar en Alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7378542037979644933', 'uniqueId': 'cristian.a_l', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a8d4f24a10c3ff1073ab57bc08de8478~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3bff719e&amp;x-expires=1761660000&amp;x-signature=KME4bwf8Cy%2Bxn%2BYUxdo1yIxFdjg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7865,18 +7865,18 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Alpinaa salúdame</t>
+          <t>Porque es la mejor ❤️❤️✨✨</t>
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>45932.13111111111</v>
+        <v>45925.67758101852</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>45932</v>
+        <v>45925</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>03:08:48</t>
+          <t>16:15:43</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556456003958588178', 'createTime': 1759374528, 'createTimeISO': '2025-10-02T03:08:48.000Z', 'text': 'Alpinaa salúdame', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6783863549585867782', 'uniqueId': 'ciro_492', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a1c71fe90e3afc45b76f3656558f0dae~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=b33d7553&amp;x-expires=1761570000&amp;x-signature=T0EUIOuepjnuVcpBiTRnhuwW6H4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554061217602994962', 'createTime': 1758816943, 'createTimeISO': '2025-09-25T16:15:43.000Z', 'text': 'Porque es la mejor ❤️❤️✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532067139480715266', 'uniqueId': 'irodriguez9', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/8934653b245a2db9d7ce7c5499232dd9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8564f584&amp;x-expires=1761660000&amp;x-signature=yzy7cqxj8kNMP6S31lI00xXKFHo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7921,25 +7921,25 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>una pregunta las personas del Sena pueden estar en Alpina</t>
+          <t>Es cierto que debajo de la cabaña hay un tunel secreto?👀</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>45925.33574074074</v>
+        <v>45925.02155092593</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>45925</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>08:03:28</t>
+          <t>00:31:02</t>
         </is>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553933847436772104', 'createTime': 1758787408, 'createTimeISO': '2025-09-25T08:03:28.000Z', 'text': 'una pregunta las personas del Sena pueden estar en Alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7378542037979644933', 'uniqueId': 'cristian.a_l', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a8d4f24a10c3ff1073ab57bc08de8478~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7159a7de&amp;x-expires=1761570000&amp;x-signature=wqabBR1lISnNHezi1Gig9y7CpVY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553817757574349576', 'createTime': 1758760262, 'createTimeISO': '2025-09-25T00:31:02.000Z', 'text': 'Es cierto que debajo de la cabaña hay un tunel secreto?👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '6686398605715244037', 'uniqueId': 'carolina_serrano', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/79be4af25ec17f747428b28ea34a0231~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=62c80d82&amp;x-expires=1761660000&amp;x-signature=gBB%2B%2FcC0j9jvb7UGIQeCpCEyzdY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -7977,18 +7977,18 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Porque es la mejor ❤️❤️✨✨</t>
+          <t>Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀</t>
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>45925.67758101852</v>
+        <v>45926.65694444445</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>16:15:43</t>
+          <t>15:46:00</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554061217602994962', 'createTime': 1758816943, 'createTimeISO': '2025-09-25T16:15:43.000Z', 'text': 'Porque es la mejor ❤️❤️✨✨', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6532067139480715266', 'uniqueId': 'irodriguez9', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/8934653b245a2db9d7ce7c5499232dd9~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1c7908a2&amp;x-expires=1761570000&amp;x-signature=PgtiBbYIA3T8P4D755TXjRkgnEo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554424648151941905', 'createTime': 1758901560, 'createTimeISO': '2025-09-26T15:46:00.000Z', 'text': 'Alpina que paso con los gatos de la leche alpina?, si me contestas me voy a la cabaña alpina👀', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7436539205088396344', 'uniqueId': 'isaac_mora1903', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bd074fbf9f61ee99fcea8ef5f350b2bf~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5013252e&amp;x-expires=1761660000&amp;x-signature=GD6Em4a93esyhF%2BW9srKSaYxbMI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8033,25 +8033,25 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mi sueñoooo 😩 ya quiero hacer parte de ustedes</t>
+          <t>alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>45925.08212962963</v>
+        <v>45931.09893518518</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>01:58:16</t>
+          <t>02:22:28</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553840238716945153', 'createTime': 1758765496, 'createTimeISO': '2025-09-25T01:58:16.000Z', 'text': 'Mi sueñoooo 😩 ya quiero hacer parte de ustedes', 'diggCount': 7, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '6561143503132540934', 'uniqueId': 'maaaarirg', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7324826520122785798~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f5aece25&amp;x-expires=1761570000&amp;x-signature=Zl4tz07p0ieZ8Pxe8VY0POWecRU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556072986438107912', 'createTime': 1759285348, 'createTimeISO': '2025-10-01T02:22:28.000Z', 'text': 'alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7555531729910694930', 'uniqueId': 'danna.isabella.sa2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1352ee914eff9ecaa92c418ab22e747d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d248ff81&amp;x-expires=1761660000&amp;x-signature=MwKAgx0KsqEpWWDoenuHHqK5zvk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8089,18 +8089,18 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰</t>
+          <t>estando en etapa lectiva puedo aplicar gracias</t>
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>45931.09893518518</v>
+        <v>45926.77866898148</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>45931</v>
+        <v>45926</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>02:22:28</t>
+          <t>18:41:17</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7556072986438107912', 'createTime': 1759285348, 'createTimeISO': '2025-10-01T02:22:28.000Z', 'text': 'alpina por favor me puedes mandar la lavadora de mochis pls🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7555531729910694930', 'uniqueId': 'danna.isabella.sa2', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/1352ee914eff9ecaa92c418ab22e747d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0c6ced0f&amp;x-expires=1761570000&amp;x-signature=zGMrwfTOMgFXssAuJvBqGWK2QG0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554469785704645384', 'createTime': 1758912077, 'createTimeISO': '2025-09-26T18:41:17.000Z', 'text': 'estando en etapa lectiva puedo aplicar gracias', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964937358190445574', 'uniqueId': 'daneicy8', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/a6e6af884aceb8af9c72174f73167f68~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1e1dd5ba&amp;x-expires=1761660000&amp;x-signature=cYY2Tzh0w40BVDhBcI9Co%2F7twXA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553827220982170386', 'createTime': 1758762474, 'createTimeISO': '2025-09-25T01:07:54.000Z', 'text': 'Yo abría amado que mis prácticas hubiesen sido en alpina ☹', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6760311129178735621', 'uniqueId': 'dosydosdoss', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4de63d002c8153b317e435b8b677488d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d59a1dfc&amp;x-expires=1761570000&amp;x-signature=q9rWx7axMTIURf0YNqcn166XfVY%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553827220982170386', 'createTime': 1758762474, 'createTimeISO': '2025-09-25T01:07:54.000Z', 'text': 'Yo abría amado que mis prácticas hubiesen sido en alpina ☹', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6760311129178735621', 'uniqueId': 'dosydosdoss', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/4de63d002c8153b317e435b8b677488d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=de07a01c&amp;x-expires=1761660000&amp;x-signature=93QFTTwAV83rbTx8DukoFRghSYA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8201,18 +8201,18 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn</t>
+          <t>cuando llegan a Perú los Mochis 😭😭</t>
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>45926.77142361111</v>
+        <v>45927.6415625</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>18:30:51</t>
+          <t>15:23:51</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554467116628640530', 'createTime': 1758911451, 'createTimeISO': '2025-09-26T18:30:51.000Z', 'text': 'Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6865051063218439169', 'uniqueId': 'soy_sebass07', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d3ac239ee21a619bba014942d5f7587e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=320e058d&amp;x-expires=1761570000&amp;x-signature=4r4OJsv3y%2BoRBDGChYJ34QIZ1S8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554790021015946005', 'createTime': 1758986631, 'createTimeISO': '2025-09-27T15:23:51.000Z', 'text': 'cuando llegan a Perú los Mochis 😭😭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7093344759511532549', 'uniqueId': 'hanzel3075', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/e5fc427c21f18dd65a5d6366a919b2b8~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8d25540f&amp;x-expires=1761660000&amp;x-signature=iaLMfTO2rTyEH859r7tbAFK30Yc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8257,22 +8257,22 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>45925.02996527778</v>
+        <v>45926.77142361111</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>00:43:09</t>
+          <t>18:30:51</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553820808625439495', 'createTime': 1758760989, 'createTimeISO': '2025-09-25T00:43:09.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3e0aba58&amp;x-expires=1761570000&amp;x-signature=OWekD83TiJfQ2m%2B3WwuiT6Ts%2BXI%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7554467116628640530', 'createTime': 1758911451, 'createTimeISO': '2025-09-26T18:30:51.000Z', 'text': 'Alpina que pasó con los gatos de la leche alpina queremos que vuelvaaannnnnn', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6865051063218439169', 'uniqueId': 'soy_sebass07', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d3ac239ee21a619bba014942d5f7587e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7f7a7fba&amp;x-expires=1761660000&amp;x-signature=n3D%2FKrHhHdoAcCJNIzN%2FWIDC8Do%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8313,22 +8313,22 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>🥰</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>45940.88704861111</v>
+        <v>45925.02996527778</v>
       </c>
       <c r="H141" s="3" t="n">
-        <v>45940</v>
+        <v>45925</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>21:17:21</t>
+          <t>00:43:09</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7559705187091956488', 'createTime': 1760131041, 'createTimeISO': '2025-10-10T21:17:21.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7464357929971483649', 'uniqueId': 'aquiles.indriagol', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/72a6938f97ba8c0e50728d4cd7d182b4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ea36d42d&amp;x-expires=1761570000&amp;x-signature=Ikg3yxNbVWc%2FGZzzE%2B8OF1evxb4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553820808625439495', 'createTime': 1758760989, 'createTimeISO': '2025-09-25T00:43:09.000Z', 'text': '💙💙💙', 'diggCount': 1, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7046148050101109766', 'uniqueId': 'juanp846', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/cdf703b505ceb5a3cf5f7b216c352922~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f726b676&amp;x-expires=1761660000&amp;x-signature=ep%2BDjeINLXqQLnpazMzaBgidHaU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8369,25 +8369,25 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?</t>
+          <t>🥰</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>45928.8690625</v>
+        <v>45940.88704861111</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>45928</v>
+        <v>45940</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>20:51:27</t>
+          <t>21:17:21</t>
         </is>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7555245460417331986', 'createTime': 1759092687, 'createTimeISO': '2025-09-28T20:51:27.000Z', 'text': 'Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7400852594988827654', 'uniqueId': 'whoisandres37', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/317c580e71debf147810b74b93171a6f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=14873671&amp;x-expires=1761570000&amp;x-signature=YsHXSH3NXmW%2BGPL0pdt7k4feCgo%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7559705187091956488', 'createTime': 1760131041, 'createTimeISO': '2025-10-10T21:17:21.000Z', 'text': '🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7464357929971483649', 'uniqueId': 'aquiles.indriagol', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/72a6938f97ba8c0e50728d4cd7d182b4~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5903cb68&amp;x-expires=1761660000&amp;x-signature=nqZJxIsmjpoSdEcIeK0ZJwvjeMc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553824837010965266', 'createTime': 1758761914, 'createTimeISO': '2025-09-25T00:58:34.000Z', 'text': 'Hola! Una pregunta ¿es normal qué los minis ilumimochis de conejito verde venga de a 2?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7482894692960535570', 'uniqueId': 'eldiploo29', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e71b97d2782d93b9a10a9adec8349876~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2a9b7310&amp;x-expires=1761570000&amp;x-signature=G%2FTR38Knn0ZU6MkRvyF5f9mD8D4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7553824837010965266', 'createTime': 1758761914, 'createTimeISO': '2025-09-25T00:58:34.000Z', 'text': 'Hola! Una pregunta ¿es normal qué los minis ilumimochis de conejito verde venga de a 2?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7482894692960535570', 'uniqueId': 'eldiploo29', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e71b97d2782d93b9a10a9adec8349876~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9843abbb&amp;x-expires=1761660000&amp;x-signature=oRRziBk1t48RUC%2FvQxXbmMNg1iU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8481,25 +8481,25 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>También reciben pasantes?</t>
+          <t>Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>45954.7812962963</v>
+        <v>45928.8690625</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>45954</v>
+        <v>45928</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>18:45:04</t>
+          <t>20:51:27</t>
         </is>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7564861171879445256', 'createTime': 1761331504, 'createTimeISO': '2025-10-24T18:45:04.000Z', 'text': 'También reciben pasantes?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '166386831993888768', 'uniqueId': 'aleja040610', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/d38de0738e43e8e0ce00becaad0aca08~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d47e22b8&amp;x-expires=1761570000&amp;x-signature=V1kMHyMoc%2FS71CbJ4A3J%2BK3qhfM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'input': 'https://www.tiktok.com/@alpinacol/video/7553815390661463308', 'cid': '7555245460417331986', 'createTime': 1759092687, 'createTimeISO': '2025-09-28T20:51:27.000Z', 'text': 'Me encuentro en el departamento del Meta puedo hacer mis Pasantías del Sena Con Alpina?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7400852594988827654', 'uniqueId': 'whoisandres37', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/317c580e71debf147810b74b93171a6f~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c49ee845&amp;x-expires=1761660000&amp;x-signature=4BAt8T1SbF711gbcCp5n7jyNLYs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8537,25 +8537,25 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>nuevas familias 😳</t>
+          <t>alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]</t>
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>45927.005</v>
+        <v>45927.49298611111</v>
       </c>
       <c r="H145" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>00:07:12</t>
+          <t>11:49:54</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554553739177624336', 'createTime': 1758931632, 'createTimeISO': '2025-09-27T00:07:12.000Z', 'text': 'nuevas familias 😳', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9a1fe501&amp;x-expires=1761570000&amp;x-signature=szv47idYNVI%2BI%2FtRkYc5Iummabs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554734892081922823', 'createTime': 1758973794, 'createTimeISO': '2025-09-27T11:49:54.000Z', 'text': 'alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=638b7f00&amp;x-expires=1761660000&amp;x-signature=FU7F41cZGJuNGgPqq9ZMLtFsmTE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8593,25 +8593,25 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Yo quiero arequipe vegano 🥺</t>
+          <t>Alpinaaaaa xq quitaste los gatooooooos</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>45933.83266203704</v>
+        <v>45927.06792824074</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>45933</v>
+        <v>45927</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>19:59:02</t>
+          <t>01:37:49</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557087381695890193', 'createTime': 1759521542, 'createTimeISO': '2025-10-03T19:59:02.000Z', 'text': 'Yo quiero arequipe vegano 🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6903626505060189189', 'uniqueId': 'mafeocampor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bc55178240ac3f97ce30d333a28a48a5~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d462a6b&amp;x-expires=1761570000&amp;x-signature=Ak5pAkGU0ZjGAHxG96227ZG1gfk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554577111799137025', 'createTime': 1758937069, 'createTimeISO': '2025-09-27T01:37:49.000Z', 'text': 'Alpinaaaaa xq quitaste los gatooooooos', 'diggCount': 11, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7414238685522199557', 'uniqueId': 'vxshly_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6f809c16c6632fac081af1ffdcb6d9f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7d5f1796&amp;x-expires=1761660000&amp;x-signature=6NwpW7Kq3tGjArviKJGn54R5gPA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8649,25 +8649,25 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏</t>
+          <t>Yo quiero arequipe vegano 🥺</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>45927.79994212963</v>
+        <v>45933.83266203704</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>45927</v>
+        <v>45933</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>19:11:55</t>
+          <t>19:59:02</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554848766027121426', 'createTime': 1759000315, 'createTimeISO': '2025-09-27T19:11:55.000Z', 'text': 'Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7505793601163674642', 'uniqueId': 'mariangel6169', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/399d2e2b90810396c3ec41de01efcf36~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9e7357b6&amp;x-expires=1761570000&amp;x-signature=UbhgXrLXav1UzsuZGYolGcpnjXk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557087381695890193', 'createTime': 1759521542, 'createTimeISO': '2025-10-03T19:59:02.000Z', 'text': 'Yo quiero arequipe vegano 🥺', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6903626505060189189', 'uniqueId': 'mafeocampor', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bc55178240ac3f97ce30d333a28a48a5~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c7bc7f97&amp;x-expires=1761660000&amp;x-signature=11xeC8WLAynBvrs3SAOIYgJXF%2B8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554722020870521616', 'createTime': 1758970803, 'createTimeISO': '2025-09-27T11:00:03.000Z', 'text': 'sube otro video de mochiiss', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7405734042824066054', 'uniqueId': 'emmanuel130816', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a09b533779b756050279fc4f4ba0f5fc~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=c913eb86&amp;x-expires=1761570000&amp;x-signature=yA1CMIOzFpoKIegA0bO9srRe1vU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554722020870521616', 'createTime': 1758970803, 'createTimeISO': '2025-09-27T11:00:03.000Z', 'text': 'sube otro video de mochiiss', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7405734042824066054', 'uniqueId': 'emmanuel130816', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a09b533779b756050279fc4f4ba0f5fc~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=19b5d0d9&amp;x-expires=1761660000&amp;x-signature=lp5cf5TL1lwqEAxXLHaJGIBU9hs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8761,22 +8761,22 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>¿alpina que paso con los gatos del alpin?</t>
+          <t>sería super interesante que grabarán un vídeo de cómo alguien se convierte en un maestro quesero (soy fan del queso)</t>
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>45927.02045138889</v>
+        <v>45932.08685185185</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>45927</v>
+        <v>45932</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>00:29:27</t>
+          <t>02:05:04</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559487220663058', 'createTime': 1758932967, 'createTimeISO': '2025-09-27T00:29:27.000Z', 'text': '¿alpina que paso con los gatos del alpin?', 'diggCount': 9, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7384592401019339781', 'uniqueId': 'el.pepe.joel', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/340ccdf36a548c49ba15c1f1d4f94a5a~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=f867dfc9&amp;x-expires=1761570000&amp;x-signature=dnRCz5B%2BexCzEGGyn6oxVX7iRb4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7556439567764472596', 'createTime': 1759370704, 'createTimeISO': '2025-10-02T02:05:04.000Z', 'text': 'sería super interesante que grabarán un vídeo de cómo alguien se convierte en un maestro quesero (soy fan del queso)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6809345648602350598', 'uniqueId': 'ginapaolae.j', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326882581663334405~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=d84a06cf&amp;x-expires=1761660000&amp;x-signature=XBnVK8gR22zSpRg6oMK6m1GtStc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555883548419932948', 'createTime': 1759241236, 'createTimeISO': '2025-09-30T14:07:16.000Z', 'text': 'Alpinaaaa esos gatos son mi infancia porfavor regresalos', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7259921363220792325', 'uniqueId': 'migue_resurgido', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6cea1ed6c965c8a6b67e0007f15f789~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=efd66891&amp;x-expires=1761570000&amp;x-signature=EEH3quWaq%2FyTOTPH9JpiJ9zP3C0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555883548419932948', 'createTime': 1759241236, 'createTimeISO': '2025-09-30T14:07:16.000Z', 'text': 'Alpinaaaa esos gatos son mi infancia porfavor regresalos', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7259921363220792325', 'uniqueId': 'migue_resurgido', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e6cea1ed6c965c8a6b67e0007f15f789~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2aa8d7f1&amp;x-expires=1761660000&amp;x-signature=2PfN2Y7xMsKcKSfrYeGGiKgHAkU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559943006864136', 'createTime': 1758933071, 'createTimeISO': '2025-09-27T00:31:11.000Z', 'text': 'ya se me antojo un yogo yogo mochisaurios', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=26a7ae26&amp;x-expires=1761570000&amp;x-signature=z4Cc6Vhls%2BKFDO7%2FuIUSOXTFj7k%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559943006864136', 'createTime': 1758933071, 'createTimeISO': '2025-09-27T00:31:11.000Z', 'text': 'ya se me antojo un yogo yogo mochisaurios', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7283326063072642053', 'uniqueId': 'socorrito.lopez0', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/9007660a09caa09f7a749fc3a9a23c0e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bf750db5&amp;x-expires=1761660000&amp;x-signature=UA6Af5qE4%2F%2FgQ9GOol2PliFMTow%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8929,25 +8929,25 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>que paso con los gatos de alpin?</t>
+          <t>Que tarea esa endulzada 😳🥰 la mejor 😇💖</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>45930.19638888889</v>
+        <v>45927.43773148148</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>45930</v>
+        <v>45927</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>04:42:48</t>
+          <t>10:30:20</t>
         </is>
       </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555738077466821394', 'createTime': 1759207368, 'createTimeISO': '2025-09-30T04:42:48.000Z', 'text': 'que paso con los gatos de alpin?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6926927885060621317', 'uniqueId': 'josep3473', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/7d60822ca9bd29b9cf211e0122ccbfab~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=46acee8e&amp;x-expires=1761570000&amp;x-signature=mPAHGmNfNErVq3tok39wkw3iqr0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554714387131745031', 'createTime': 1758969020, 'createTimeISO': '2025-09-27T10:30:20.000Z', 'text': 'Que tarea esa endulzada 😳🥰 la mejor 😇💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p19-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2bac3cd2&amp;x-expires=1761660000&amp;x-signature=WEArl9n59Fp%2BiSxBaRnvAI77Xfs%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -8985,25 +8985,25 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>primerooo alpina me regalas mochisauros porfiss</t>
+          <t>nuevas familias 😳</t>
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>45926.99771990741</v>
+        <v>45927.005</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>23:56:43</t>
+          <t>00:07:12</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554551041196770066', 'createTime': 1758931003, 'createTimeISO': '2025-09-26T23:56:43.000Z', 'text': 'primerooo alpina me regalas mochisauros porfiss', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7547457761526137864', 'uniqueId': 'camisetas.de.futbol1', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/a6c21b0befe49f100b71b7cf8f2e5652~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2d0ee85e&amp;x-expires=1761570000&amp;x-signature=SUpWNO3D%2BEqKqnlOoZu2JNOzPjQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554553739177624336', 'createTime': 1758931632, 'createTimeISO': '2025-09-27T00:07:12.000Z', 'text': 'nuevas familias 😳', 'diggCount': 5, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7155964557461144581', 'uniqueId': 'marilincastillo46', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/e0ba4723b994319985b1ee959919edbb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=1d5b80d7&amp;x-expires=1761660000&amp;x-signature=Sd%2B5H5xHBcGJo50KbRbUW9h393c%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9041,22 +9041,22 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>sería super interesante que grabarán un vídeo de cómo alguien se convierte en un maestro quesero (soy fan del queso)</t>
+          <t>🔝</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>45932.08685185185</v>
+        <v>45927.01375</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>45932</v>
+        <v>45927</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>02:05:04</t>
+          <t>00:19:48</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7556439567764472596', 'createTime': 1759370704, 'createTimeISO': '2025-10-02T02:05:04.000Z', 'text': 'sería super interesante que grabarán un vídeo de cómo alguien se convierte en un maestro quesero (soy fan del queso)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6809345648602350598', 'uniqueId': 'ginapaolae.j', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7326882581663334405~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ae038b89&amp;x-expires=1761570000&amp;x-signature=6tJOHSa8hh9zBvuP9WNHGm9ASUQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554556989701325580', 'createTime': 1758932388, 'createTimeISO': '2025-09-27T00:19:48.000Z', 'text': '🔝', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=bfade73a&amp;x-expires=1761660000&amp;x-signature=Owi5SAKC6UWu%2BV%2BwdCORYwA0t68%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9097,25 +9097,25 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Que tarea esa endulzada 😳🥰 la mejor 😇💖</t>
+          <t>😊😊😊</t>
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>45927.43773148148</v>
+        <v>45927.0005787037</v>
       </c>
       <c r="H155" s="3" t="n">
         <v>45927</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>10:30:20</t>
+          <t>00:00:50</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554714387131745031', 'createTime': 1758969020, 'createTimeISO': '2025-09-27T10:30:20.000Z', 'text': 'Que tarea esa endulzada 😳🥰 la mejor 😇💖', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6781208974266188805', 'uniqueId': 'andregg077', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/0c493aa7c5dae089ff639650c6b17a8e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=601101e6&amp;x-expires=1761570000&amp;x-signature=JILH8DcPWnOgie%2Bn%2B8v2TGE2X7I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554552119991829255', 'createTime': 1758931250, 'createTimeISO': '2025-09-27T00:00:50.000Z', 'text': '😊😊😊', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7263510507210245125', 'uniqueId': 'anyela1p', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/388bda02c957db9a4a0d8b463d9fb749~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=4b095d8e&amp;x-expires=1761660000&amp;x-signature=OLYSpEDY2pPynqtKygVKG8rzOqA%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9153,25 +9153,25 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Alpinaaaaa xq quitaste los gatooooooos</t>
+          <t>💙💙💙</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>45927.06792824074</v>
+        <v>45951.07341435185</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>45927</v>
+        <v>45951</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>01:37:49</t>
+          <t>01:45:43</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554577111799137025', 'createTime': 1758937069, 'createTimeISO': '2025-09-27T01:37:49.000Z', 'text': 'Alpinaaaaa xq quitaste los gatooooooos', 'diggCount': 11, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 3, 'uid': '7414238685522199557', 'uniqueId': 'vxshly_', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/6f809c16c6632fac081af1ffdcb6d9f0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=2a61e4f3&amp;x-expires=1761570000&amp;x-signature=pQYt%2F3FRv8TT%2BOeVmegojy%2F4o5I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7563485230247002888', 'createTime': 1761011143, 'createTimeISO': '2025-10-21T01:45:43.000Z', 'text': '💙💙💙', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6851669436614001669', 'uniqueId': 'villamil2.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/39e44d37d75d07c80dfacb9dc52dc087~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8033c4a4&amp;x-expires=1761660000&amp;x-signature=jDsNkZSllh9sQNpG3fgOtw7l1Sk%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9209,22 +9209,22 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]</t>
+          <t>💚</t>
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>45927.49298611111</v>
+        <v>45946.82292824074</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>45927</v>
+        <v>45946</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>11:49:54</t>
+          <t>19:45:01</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554734892081922823', 'createTime': 1758973794, 'createTimeISO': '2025-09-27T11:49:54.000Z', 'text': 'alpina cuando vas a mostras las familias ya tenemos Los nombres solo faltan las familias[happy][yummy]', 'diggCount': 3, 'likedByAuthor': True, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7477553551649506320', 'uniqueId': 'tailsmilespower44', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b54ac1faf1f39b6779eb0b9a7ceab5df~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0ef532ce&amp;x-expires=1761570000&amp;x-signature=RKt5tPaOrcsntRN4pE8cOzaUhh0%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907925900821255', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '💚', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=72ea30a5&amp;x-expires=1761660000&amp;x-signature=AJDdBo2z0ciCHfgXsGoRmILk2cQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9265,22 +9265,22 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>😊😊😊</t>
+          <t>@Alpina 🐮 hola necesito un favor suyo 🙏</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>45927.0005787037</v>
+        <v>45930.75880787037</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>45927</v>
+        <v>45930</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>00:00:50</t>
+          <t>18:12:41</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554552119991829255', 'createTime': 1758931250, 'createTimeISO': '2025-09-27T00:00:50.000Z', 'text': '😊😊😊', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7263510507210245125', 'uniqueId': 'anyela1p', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/388bda02c957db9a4a0d8b463d9fb749~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=7eb01a6e&amp;x-expires=1761570000&amp;x-signature=x8oLK3IZ5b5tP1OLK3No3feeDw8%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555946787841164050', 'createTime': 1759255961, 'createTimeISO': '2025-09-30T18:12:41.000Z', 'text': '@Alpina 🐮 hola necesito un favor suyo 🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7314724628953121797', 'uniqueId': 'jan.cityzens', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5d6f3dd82f6da2bcac787ef22cb28684~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3506f19c&amp;x-expires=1761660000&amp;x-signature=lw%2BGqFOYRGrUA7sEJxz2tzeBE8M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
         </is>
       </c>
     </row>
@@ -9321,22 +9321,22 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>🔝</t>
+          <t>♥</t>
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>45927.01375</v>
+        <v>45946.82293981482</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>45927</v>
+        <v>45946</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>00:19:48</t>
+          <t>19:45:02</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554556989701325580', 'createTime': 1758932388, 'createTimeISO': '2025-09-27T00:19:48.000Z', 'text': '🔝', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6808343868984345606', 'uniqueId': 'isaacalejandrorueda', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/9521fa11b07506edc233d485d7408f43~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=9318afca&amp;x-expires=1761570000&amp;x-signature=vuOKTe6NBdJzzn2l%2FGqo1IGgWyM%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907909032067847', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=72ea30a5&amp;x-expires=1761660000&amp;x-signature=AJDdBo2z0ciCHfgXsGoRmILk2cQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9377,18 +9377,18 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>❤</t>
+          <t>♥</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>45946.82291666666</v>
+        <v>45946.82292824074</v>
       </c>
       <c r="H160" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:45:01</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907924650574600', 'createTime': 1760643900, 'createTimeISO': '2025-10-16T19:45:00.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907918385365768', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=72ea30a5&amp;x-expires=1761660000&amp;x-signature=AJDdBo2z0ciCHfgXsGoRmILk2cQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9433,18 +9433,18 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>❤</t>
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>45946.82292824074</v>
+        <v>45946.82293981482</v>
       </c>
       <c r="H161" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>19:45:01</t>
+          <t>19:45:02</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907918385365768', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907940182098696', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=72ea30a5&amp;x-expires=1761660000&amp;x-signature=AJDdBo2z0ciCHfgXsGoRmILk2cQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9489,18 +9489,18 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>💚</t>
+          <t>mochisssssss</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>45946.82292824074</v>
+        <v>45934.81753472222</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>45946</v>
+        <v>45934</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>19:45:01</t>
+          <t>19:37:15</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907925900821255', 'createTime': 1760643901, 'createTimeISO': '2025-10-16T19:45:01.000Z', 'text': '💚', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557452880204202770', 'createTime': 1759606635, 'createTimeISO': '2025-10-04T19:37:15.000Z', 'text': 'mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7329726761418753029', 'uniqueId': 'pipi.potato35', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0d01dfa969f5266b98420f02248fc885~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=0a7bb37d&amp;x-expires=1761660000&amp;x-signature=cvOMw5KQhAoLuMA2LBBt6SRR1t4%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast8', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9545,18 +9545,18 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>aquí esperando el video donde hablen de los gatos de alpin</t>
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>45946.82295138889</v>
+        <v>45941.26355324074</v>
       </c>
       <c r="H163" s="3" t="n">
-        <v>45946</v>
+        <v>45941</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>19:45:03</t>
+          <t>06:19:31</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907930460537607', 'createTime': 1760643903, 'createTimeISO': '2025-10-16T19:45:03.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7559844927899992849', 'createTime': 1760163571, 'createTimeISO': '2025-10-11T06:19:31.000Z', 'text': 'aquí esperando el video donde hablen de los gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7001651876342055942', 'uniqueId': 'm1mundo_lu', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/9fc0ed9938dca78c9455e0317e1e289b~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=84d4f804&amp;x-expires=1761660000&amp;x-signature=%2FExCLd%2FLRdlzaRI7VPnfdxAMQHU%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9601,25 +9601,25 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>♥</t>
+          <t>Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>45946.82293981482</v>
+        <v>45927.79994212963</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>45946</v>
+        <v>45927</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>19:45:02</t>
+          <t>19:11:55</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907909032067847', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554848766027121426', 'createTime': 1759000315, 'createTimeISO': '2025-09-27T19:11:55.000Z', 'text': 'Gabi sube la segunda parte de los Mochi saurios plis🙏🙏🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7505793601163674642', 'uniqueId': 'mariangel6169', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/399d2e2b90810396c3ec41de01efcf36~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=0f741dae&amp;x-expires=1761660000&amp;x-signature=qnPhwMa1tyGrxSugaq318lMO71w%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9657,22 +9657,22 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>@Alpina 🐮 hola necesito un favor suyo 🙏</t>
+          <t>¿alpina que paso con los gatos del alpin?</t>
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>45930.75880787037</v>
+        <v>45927.02045138889</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>45930</v>
+        <v>45927</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>18:12:41</t>
+          <t>00:29:27</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555946787841164050', 'createTime': 1759255961, 'createTimeISO': '2025-09-30T18:12:41.000Z', 'text': '@Alpina 🐮 hola necesito un favor suyo 🙏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7314724628953121797', 'uniqueId': 'jan.cityzens', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/5d6f3dd82f6da2bcac787ef22cb28684~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=47273fa9&amp;x-expires=1761570000&amp;x-signature=I8ubyIepd0u8GeVYs5Iw0rhYNiw%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': ['@Alpina 🐮'], 'detailedMentions': [{'userId': '7104365507802039302', 'nickName': 'Alpina 🐮', 'profileUrl': 'https://www.tiktok.com/@7104365507802039302', 'secUid': 'MS4wLjABAAAAhVHJ_4YoWtjsb-ppI1tP9-jNJT-8YzbXw-Vuk4Y6Yl0s6Wro7Kt4qB6jp8arD-9S'}]}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554559487220663058', 'createTime': 1758932967, 'createTimeISO': '2025-09-27T00:29:27.000Z', 'text': '¿alpina que paso con los gatos del alpin?', 'diggCount': 9, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7384592401019339781', 'uniqueId': 'el.pepe.joel', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/340ccdf36a548c49ba15c1f1d4f94a5a~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=bea12cf4&amp;x-expires=1761660000&amp;x-signature=ZAAEx01GkBdjpC8lqNJvB%2BgiBuE%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9713,18 +9713,18 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>💙💙💙</t>
+          <t>que paso con los gatos de alpin?</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>45951.07341435185</v>
+        <v>45930.19638888889</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>45951</v>
+        <v>45930</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>01:45:43</t>
+          <t>04:42:48</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7563485230247002888', 'createTime': 1761011143, 'createTimeISO': '2025-10-21T01:45:43.000Z', 'text': '💙💙💙', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6851669436614001669', 'uniqueId': 'villamil2.4', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/39e44d37d75d07c80dfacb9dc52dc087~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5aab5636&amp;x-expires=1761570000&amp;x-signature=TvjECkAg%2F6m9KcviqnxjNUleMQc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7555738077466821394', 'createTime': 1759207368, 'createTimeISO': '2025-09-30T04:42:48.000Z', 'text': 'que paso con los gatos de alpin?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6926927885060621317', 'uniqueId': 'josep3473', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/7d60822ca9bd29b9cf211e0122ccbfab~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=cf0f2597&amp;x-expires=1761660000&amp;x-signature=DHeRNnUl9An%2F5tawvdgZ8XPR0nQ%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9769,18 +9769,18 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>❤</t>
+          <t>♥</t>
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>45946.82293981482</v>
+        <v>45946.82295138889</v>
       </c>
       <c r="H167" s="3" t="n">
         <v>45946</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>19:45:02</t>
+          <t>19:45:03</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907940182098696', 'createTime': 1760643902, 'createTimeISO': '2025-10-16T19:45:02.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=908d877b&amp;x-expires=1761570000&amp;x-signature=q2hFYOxO%2FqE9WhZYcSFEKQrCH3M%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907930460537607', 'createTime': 1760643903, 'createTimeISO': '2025-10-16T19:45:03.000Z', 'text': '♥', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=0f41afbb&amp;x-expires=1761660000&amp;x-signature=vOA0b%2FwckPYacchn8vG7FEwy64I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9825,18 +9825,18 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>mochisssssss</t>
+          <t>❤</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>45934.81753472222</v>
+        <v>45946.82291666666</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>45934</v>
+        <v>45946</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>19:37:15</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7557452880204202770', 'createTime': 1759606635, 'createTimeISO': '2025-10-04T19:37:15.000Z', 'text': 'mochisssssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7329726761418753029', 'uniqueId': 'pipi.potato35', 'avatarThumbnail': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/0d01dfa969f5266b98420f02248fc885~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=a266c36d&amp;x-expires=1761570000&amp;x-signature=meB0uyufeqrY%2BBKDTZro%2B4foDps%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=useast5', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7561907924650574600', 'createTime': 1760643900, 'createTimeISO': '2025-10-16T19:45:00.000Z', 'text': '❤', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7157738821881988102', 'uniqueId': 'milvia575', 'avatarThumbnail': 'https://p16-sign-va.tiktokcdn.com/tos-maliva-avt-0068/7330866131660046341~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=0f41afbb&amp;x-expires=1761660000&amp;x-signature=vOA0b%2FwckPYacchn8vG7FEwy64I%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
@@ -9881,22 +9881,22 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>aquí esperando el video donde hablen de los gatos de alpin</t>
+          <t>primerooo alpina me regalas mochisauros porfiss</t>
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>45941.26355324074</v>
+        <v>45926.99771990741</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>45941</v>
+        <v>45926</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>06:19:31</t>
+          <t>23:56:43</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7559844927899992849', 'createTime': 1760163571, 'createTimeISO': '2025-10-11T06:19:31.000Z', 'text': 'aquí esperando el video donde hablen de los gatos de alpin', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7001651876342055942', 'uniqueId': 'm1mundo_lu', 'avatarThumbnail': 'https://p77-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/1f167436074f22f5e92f6246fd53543d~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=008e230b&amp;x-expires=1761570000&amp;x-signature=gGq55MztIVwVpN%2F4Mbrpg54qYqc%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=my', 'mentions': [], 'detailedMentions': []}</t>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'submittedVideoUrl': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'input': 'https://www.tiktok.com/@alpinacol/video/7554549968778825016', 'cid': '7554551041196770066', 'createTime': 1758931003, 'createTimeISO': '2025-09-26T23:56:43.000Z', 'text': 'primerooo alpina me regalas mochisauros porfiss', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7547457761526137864', 'uniqueId': 'camisetas.de.futbol1', 'avatarThumbnail': 'https://p16-sign-sg.tiktokcdn.com/tos-alisg-avt-0068/a6c21b0befe49f100b71b7cf8f2e5652~tplv-tiktokx-cropcenter:100:100.jpg?dr=14579&amp;refresh_token=93ee1368&amp;x-expires=1761660000&amp;x-signature=0%2BxYWyE46L1E7hRGsDUauBJruzg%3D&amp;t=4d5b0474&amp;ps=13740610&amp;shp=30310797&amp;shcp=ff37627b&amp;idc=maliva', 'mentions': [], 'detailedMentions': []}</t>
         </is>
       </c>
     </row>
